--- a/РАБОЧИЙ СТОЛ/расчеты Останкино КИ и ЗПФ/расчеты Останкино ЗПФ/дв 28,09,26 мррсч ост зпф.xlsx
+++ b/РАБОЧИЙ СТОЛ/расчеты Останкино КИ и ЗПФ/расчеты Останкино ЗПФ/дв 28,09,26 мррсч ост зпф.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчеты Останкино ЗПФ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчеты Останкино КИ и ЗПФ\расчеты Останкино ЗПФ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80ADE974-64EE-496D-93D2-A59D380F0475}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A16B523-4545-4B11-98B6-9722CD9F519D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="42">
   <si>
     <t>Номенклатура</t>
   </si>
@@ -142,6 +142,18 @@
   </si>
   <si>
     <t>нет</t>
+  </si>
+  <si>
+    <t>ТК</t>
+  </si>
+  <si>
+    <t>Титенок</t>
+  </si>
+  <si>
+    <t>заказ</t>
+  </si>
+  <si>
+    <t>05,10,</t>
   </si>
 </sst>
 </file>
@@ -542,7 +554,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AL500"/>
+  <dimension ref="A1:AN500"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
@@ -556,15 +568,15 @@
     <col min="11" max="12" width="7" customWidth="1"/>
     <col min="13" max="14" width="0.5703125" customWidth="1"/>
     <col min="15" max="15" width="0.42578125" customWidth="1"/>
-    <col min="16" max="17" width="7" customWidth="1"/>
-    <col min="18" max="19" width="5" customWidth="1"/>
-    <col min="20" max="20" width="6" customWidth="1"/>
-    <col min="21" max="21" width="25" customWidth="1"/>
-    <col min="22" max="22" width="7" customWidth="1"/>
-    <col min="23" max="38" width="8" customWidth="1"/>
+    <col min="16" max="19" width="7" customWidth="1"/>
+    <col min="20" max="21" width="5" customWidth="1"/>
+    <col min="22" max="22" width="6" customWidth="1"/>
+    <col min="23" max="23" width="25" customWidth="1"/>
+    <col min="24" max="24" width="7" customWidth="1"/>
+    <col min="25" max="40" width="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -603,8 +615,10 @@
       <c r="AJ1" s="1"/>
       <c r="AK1" s="1"/>
       <c r="AL1" s="1"/>
-    </row>
-    <row r="2" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM1" s="1"/>
+      <c r="AN1" s="1"/>
+    </row>
+    <row r="2" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -643,8 +657,10 @@
       <c r="AJ2" s="1"/>
       <c r="AK2" s="1"/>
       <c r="AL2" s="1"/>
-    </row>
-    <row r="3" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM2" s="1"/>
+      <c r="AN2" s="1"/>
+    </row>
+    <row r="3" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
@@ -696,23 +712,27 @@
       <c r="Q3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R3" s="2" t="s">
+      <c r="R3" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="S3" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="T3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="S3" s="2" t="s">
+      <c r="U3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="T3" s="2" t="s">
+      <c r="V3" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="U3" s="2" t="s">
+      <c r="W3" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="V3" s="2" t="s">
+      <c r="X3" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="W3" s="1"/>
-      <c r="X3" s="1"/>
       <c r="Y3" s="1"/>
       <c r="Z3" s="1"/>
       <c r="AA3" s="1"/>
@@ -727,8 +747,10 @@
       <c r="AJ3" s="1"/>
       <c r="AK3" s="1"/>
       <c r="AL3" s="1"/>
-    </row>
-    <row r="4" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM3" s="1"/>
+      <c r="AN3" s="1"/>
+    </row>
+    <row r="4" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -750,13 +772,17 @@
         <v>22</v>
       </c>
       <c r="Q4" s="1"/>
-      <c r="R4" s="1"/>
-      <c r="S4" s="1"/>
-      <c r="T4" s="1" t="s">
+      <c r="R4" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="S4" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="T4" s="1"/>
+      <c r="U4" s="1"/>
+      <c r="V4" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="U4" s="1"/>
-      <c r="V4" s="1"/>
       <c r="W4" s="1"/>
       <c r="X4" s="1"/>
       <c r="Y4" s="1"/>
@@ -773,8 +799,10 @@
       <c r="AJ4" s="1"/>
       <c r="AK4" s="1"/>
       <c r="AL4" s="1"/>
-    </row>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM4" s="1"/>
+      <c r="AN4" s="1"/>
+    </row>
+    <row r="5" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
@@ -792,7 +820,7 @@
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
       <c r="K5" s="4">
-        <f t="shared" ref="K5:Q5" si="0">SUM(K6:K500)</f>
+        <f t="shared" ref="K5:R5" si="0">SUM(K6:K500)</f>
         <v>35</v>
       </c>
       <c r="L5" s="4">
@@ -819,19 +847,22 @@
         <f t="shared" si="0"/>
         <v>150</v>
       </c>
-      <c r="R5" s="1"/>
-      <c r="S5" s="1"/>
-      <c r="T5" s="4">
-        <f t="shared" ref="T5" si="1">SUM(T6:T500)</f>
+      <c r="R5" s="4">
+        <f t="shared" si="0"/>
+        <v>870</v>
+      </c>
+      <c r="S5" s="4"/>
+      <c r="T5" s="1"/>
+      <c r="U5" s="1"/>
+      <c r="V5" s="4">
+        <f t="shared" ref="V5" si="1">SUM(V6:V500)</f>
         <v>0</v>
       </c>
-      <c r="U5" s="1"/>
-      <c r="V5" s="4">
-        <f>SUM(V6:V500)</f>
-        <v>66.900000000000006</v>
+      <c r="W5" s="1"/>
+      <c r="X5" s="4">
+        <f>SUM(X6:X500)</f>
+        <v>415.2</v>
       </c>
-      <c r="W5" s="1"/>
-      <c r="X5" s="1"/>
       <c r="Y5" s="1"/>
       <c r="Z5" s="1"/>
       <c r="AA5" s="1"/>
@@ -846,8 +877,10 @@
       <c r="AJ5" s="1"/>
       <c r="AK5" s="1"/>
       <c r="AL5" s="1"/>
-    </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM5" s="1"/>
+      <c r="AN5" s="1"/>
+    </row>
+    <row r="6" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
         <v>23</v>
       </c>
@@ -883,24 +916,28 @@
       <c r="Q6" s="5">
         <v>10</v>
       </c>
-      <c r="R6" s="1" t="e">
+      <c r="R6" s="5">
+        <v>50</v>
+      </c>
+      <c r="S6" s="1">
+        <v>50</v>
+      </c>
+      <c r="T6" s="1" t="e">
         <f>F6/P6</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="S6" s="1" t="e">
+      <c r="U6" s="1" t="e">
         <f>F6/P6</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="T6" s="1">
+      <c r="V6" s="1">
         <v>0</v>
       </c>
-      <c r="U6" s="1"/>
-      <c r="V6" s="1">
-        <f>G6*Q6</f>
-        <v>4.2</v>
+      <c r="W6" s="1"/>
+      <c r="X6" s="1">
+        <f>G6*R6</f>
+        <v>21</v>
       </c>
-      <c r="W6" s="1"/>
-      <c r="X6" s="1"/>
       <c r="Y6" s="1"/>
       <c r="Z6" s="1"/>
       <c r="AA6" s="1"/>
@@ -915,8 +952,10 @@
       <c r="AJ6" s="1"/>
       <c r="AK6" s="1"/>
       <c r="AL6" s="1"/>
-    </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM6" s="1"/>
+      <c r="AN6" s="1"/>
+    </row>
+    <row r="7" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
         <v>26</v>
       </c>
@@ -952,24 +991,28 @@
       <c r="Q7" s="5">
         <v>10</v>
       </c>
-      <c r="R7" s="1" t="e">
-        <f t="shared" ref="R7:R16" si="4">F7/P7</f>
+      <c r="R7" s="5">
+        <v>100</v>
+      </c>
+      <c r="S7" s="1">
+        <v>150</v>
+      </c>
+      <c r="T7" s="1" t="e">
+        <f t="shared" ref="T7:T16" si="4">F7/P7</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="S7" s="1" t="e">
-        <f t="shared" ref="S7:S16" si="5">F7/P7</f>
+      <c r="U7" s="1" t="e">
+        <f t="shared" ref="U7:U16" si="5">F7/P7</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="T7" s="1">
+      <c r="V7" s="1">
         <v>0</v>
       </c>
-      <c r="U7" s="1"/>
-      <c r="V7" s="1">
-        <f>G7*Q7</f>
-        <v>10</v>
+      <c r="W7" s="1"/>
+      <c r="X7" s="1">
+        <f t="shared" ref="X7:X16" si="6">G7*R7</f>
+        <v>100</v>
       </c>
-      <c r="W7" s="1"/>
-      <c r="X7" s="1"/>
       <c r="Y7" s="1"/>
       <c r="Z7" s="1"/>
       <c r="AA7" s="1"/>
@@ -984,8 +1027,10 @@
       <c r="AJ7" s="1"/>
       <c r="AK7" s="1"/>
       <c r="AL7" s="1"/>
-    </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM7" s="1"/>
+      <c r="AN7" s="1"/>
+    </row>
+    <row r="8" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
         <v>28</v>
       </c>
@@ -1021,24 +1066,27 @@
       <c r="Q8" s="5">
         <v>10</v>
       </c>
-      <c r="R8" s="1" t="e">
+      <c r="R8" s="5">
+        <f t="shared" ref="R7:R16" si="7">Q8</f>
+        <v>10</v>
+      </c>
+      <c r="S8" s="1"/>
+      <c r="T8" s="1" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="S8" s="1" t="e">
+      <c r="U8" s="1" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="T8" s="1">
+      <c r="V8" s="1">
         <v>0</v>
       </c>
-      <c r="U8" s="1"/>
-      <c r="V8" s="1">
-        <f>G8*Q8</f>
+      <c r="W8" s="1"/>
+      <c r="X8" s="1">
+        <f t="shared" si="6"/>
         <v>10</v>
       </c>
-      <c r="W8" s="1"/>
-      <c r="X8" s="1"/>
       <c r="Y8" s="1"/>
       <c r="Z8" s="1"/>
       <c r="AA8" s="1"/>
@@ -1053,8 +1101,10 @@
       <c r="AJ8" s="1"/>
       <c r="AK8" s="1"/>
       <c r="AL8" s="1"/>
-    </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM8" s="1"/>
+      <c r="AN8" s="1"/>
+    </row>
+    <row r="9" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
         <v>29</v>
       </c>
@@ -1090,24 +1140,27 @@
       <c r="Q9" s="5">
         <v>10</v>
       </c>
-      <c r="R9" s="1" t="e">
+      <c r="R9" s="5">
+        <f t="shared" si="7"/>
+        <v>10</v>
+      </c>
+      <c r="S9" s="1"/>
+      <c r="T9" s="1" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="S9" s="1" t="e">
+      <c r="U9" s="1" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="T9" s="1">
+      <c r="V9" s="1">
         <v>0</v>
       </c>
-      <c r="U9" s="1"/>
-      <c r="V9" s="1">
-        <f>G9*Q9</f>
+      <c r="W9" s="1"/>
+      <c r="X9" s="1">
+        <f t="shared" si="6"/>
         <v>4.2</v>
       </c>
-      <c r="W9" s="1"/>
-      <c r="X9" s="1"/>
       <c r="Y9" s="1"/>
       <c r="Z9" s="1"/>
       <c r="AA9" s="1"/>
@@ -1122,8 +1175,10 @@
       <c r="AJ9" s="1"/>
       <c r="AK9" s="1"/>
       <c r="AL9" s="1"/>
-    </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM9" s="1"/>
+      <c r="AN9" s="1"/>
+    </row>
+    <row r="10" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
         <v>30</v>
       </c>
@@ -1161,24 +1216,28 @@
       <c r="Q10" s="5">
         <v>20</v>
       </c>
-      <c r="R10" s="1" t="e">
+      <c r="R10" s="5">
+        <v>100</v>
+      </c>
+      <c r="S10" s="1">
+        <v>150</v>
+      </c>
+      <c r="T10" s="1" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="S10" s="1" t="e">
+      <c r="U10" s="1" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="T10" s="1">
+      <c r="V10" s="1">
         <v>0</v>
       </c>
-      <c r="U10" s="1"/>
-      <c r="V10" s="1">
-        <f>G10*Q10</f>
-        <v>6</v>
+      <c r="W10" s="1"/>
+      <c r="X10" s="1">
+        <f t="shared" si="6"/>
+        <v>30</v>
       </c>
-      <c r="W10" s="1"/>
-      <c r="X10" s="1"/>
       <c r="Y10" s="1"/>
       <c r="Z10" s="1"/>
       <c r="AA10" s="1"/>
@@ -1193,8 +1252,10 @@
       <c r="AJ10" s="1"/>
       <c r="AK10" s="1"/>
       <c r="AL10" s="1"/>
-    </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM10" s="1"/>
+      <c r="AN10" s="1"/>
+    </row>
+    <row r="11" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
         <v>31</v>
       </c>
@@ -1232,24 +1293,28 @@
       <c r="Q11" s="5">
         <v>20</v>
       </c>
-      <c r="R11" s="1" t="e">
+      <c r="R11" s="5">
+        <v>100</v>
+      </c>
+      <c r="S11" s="1">
+        <v>150</v>
+      </c>
+      <c r="T11" s="1" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="S11" s="1" t="e">
+      <c r="U11" s="1" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="T11" s="1">
+      <c r="V11" s="1">
         <v>0</v>
       </c>
-      <c r="U11" s="1"/>
-      <c r="V11" s="1">
-        <f>G11*Q11</f>
-        <v>6</v>
+      <c r="W11" s="1"/>
+      <c r="X11" s="1">
+        <f t="shared" si="6"/>
+        <v>30</v>
       </c>
-      <c r="W11" s="1"/>
-      <c r="X11" s="1"/>
       <c r="Y11" s="1"/>
       <c r="Z11" s="1"/>
       <c r="AA11" s="1"/>
@@ -1264,8 +1329,10 @@
       <c r="AJ11" s="1"/>
       <c r="AK11" s="1"/>
       <c r="AL11" s="1"/>
-    </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM11" s="1"/>
+      <c r="AN11" s="1"/>
+    </row>
+    <row r="12" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
         <v>32</v>
       </c>
@@ -1303,24 +1370,28 @@
       <c r="Q12" s="5">
         <v>10</v>
       </c>
-      <c r="R12" s="1" t="e">
+      <c r="R12" s="5">
+        <v>100</v>
+      </c>
+      <c r="S12" s="1">
+        <v>150</v>
+      </c>
+      <c r="T12" s="1" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="S12" s="1" t="e">
+      <c r="U12" s="1" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="T12" s="1">
+      <c r="V12" s="1">
         <v>0</v>
       </c>
-      <c r="U12" s="1"/>
-      <c r="V12" s="1">
-        <f>G12*Q12</f>
-        <v>3.5</v>
+      <c r="W12" s="1"/>
+      <c r="X12" s="1">
+        <f t="shared" si="6"/>
+        <v>35</v>
       </c>
-      <c r="W12" s="1"/>
-      <c r="X12" s="1"/>
       <c r="Y12" s="1"/>
       <c r="Z12" s="1"/>
       <c r="AA12" s="1"/>
@@ -1335,8 +1406,10 @@
       <c r="AJ12" s="1"/>
       <c r="AK12" s="1"/>
       <c r="AL12" s="1"/>
-    </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM12" s="1"/>
+      <c r="AN12" s="1"/>
+    </row>
+    <row r="13" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
         <v>33</v>
       </c>
@@ -1374,24 +1447,28 @@
       <c r="Q13" s="5">
         <v>20</v>
       </c>
-      <c r="R13" s="1" t="e">
+      <c r="R13" s="5">
+        <v>100</v>
+      </c>
+      <c r="S13" s="1">
+        <v>150</v>
+      </c>
+      <c r="T13" s="1" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="S13" s="1" t="e">
+      <c r="U13" s="1" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="T13" s="1">
+      <c r="V13" s="1">
         <v>0</v>
       </c>
-      <c r="U13" s="1"/>
-      <c r="V13" s="1">
-        <f>G13*Q13</f>
-        <v>6</v>
+      <c r="W13" s="1"/>
+      <c r="X13" s="1">
+        <f t="shared" si="6"/>
+        <v>30</v>
       </c>
-      <c r="W13" s="1"/>
-      <c r="X13" s="1"/>
       <c r="Y13" s="1"/>
       <c r="Z13" s="1"/>
       <c r="AA13" s="1"/>
@@ -1406,8 +1483,10 @@
       <c r="AJ13" s="1"/>
       <c r="AK13" s="1"/>
       <c r="AL13" s="1"/>
-    </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM13" s="1"/>
+      <c r="AN13" s="1"/>
+    </row>
+    <row r="14" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
         <v>34</v>
       </c>
@@ -1445,24 +1524,28 @@
       <c r="Q14" s="5">
         <v>20</v>
       </c>
-      <c r="R14" s="1" t="e">
+      <c r="R14" s="5">
+        <v>100</v>
+      </c>
+      <c r="S14" s="1">
+        <v>150</v>
+      </c>
+      <c r="T14" s="1" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="S14" s="1" t="e">
+      <c r="U14" s="1" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="T14" s="1">
+      <c r="V14" s="1">
         <v>0</v>
       </c>
-      <c r="U14" s="1"/>
-      <c r="V14" s="1">
-        <f>G14*Q14</f>
-        <v>7</v>
+      <c r="W14" s="1"/>
+      <c r="X14" s="1">
+        <f t="shared" si="6"/>
+        <v>35</v>
       </c>
-      <c r="W14" s="1"/>
-      <c r="X14" s="1"/>
       <c r="Y14" s="1"/>
       <c r="Z14" s="1"/>
       <c r="AA14" s="1"/>
@@ -1477,8 +1560,10 @@
       <c r="AJ14" s="1"/>
       <c r="AK14" s="1"/>
       <c r="AL14" s="1"/>
-    </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM14" s="1"/>
+      <c r="AN14" s="1"/>
+    </row>
+    <row r="15" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
         <v>35</v>
       </c>
@@ -1514,24 +1599,28 @@
       <c r="Q15" s="5">
         <v>10</v>
       </c>
-      <c r="R15" s="1" t="e">
+      <c r="R15" s="5">
+        <v>50</v>
+      </c>
+      <c r="S15" s="1">
+        <v>50</v>
+      </c>
+      <c r="T15" s="1" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="S15" s="1" t="e">
+      <c r="U15" s="1" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="T15" s="1">
+      <c r="V15" s="1">
         <v>0</v>
       </c>
-      <c r="U15" s="1"/>
-      <c r="V15" s="1">
-        <f>G15*Q15</f>
-        <v>3</v>
+      <c r="W15" s="1"/>
+      <c r="X15" s="1">
+        <f t="shared" si="6"/>
+        <v>15</v>
       </c>
-      <c r="W15" s="1"/>
-      <c r="X15" s="1"/>
       <c r="Y15" s="1"/>
       <c r="Z15" s="1"/>
       <c r="AA15" s="1"/>
@@ -1546,8 +1635,10 @@
       <c r="AJ15" s="1"/>
       <c r="AK15" s="1"/>
       <c r="AL15" s="1"/>
-    </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM15" s="1"/>
+      <c r="AN15" s="1"/>
+    </row>
+    <row r="16" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
         <v>36</v>
       </c>
@@ -1583,24 +1674,28 @@
       <c r="Q16" s="5">
         <v>10</v>
       </c>
-      <c r="R16" s="1" t="e">
+      <c r="R16" s="5">
+        <v>150</v>
+      </c>
+      <c r="S16" s="1">
+        <v>200</v>
+      </c>
+      <c r="T16" s="1" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="S16" s="1" t="e">
+      <c r="U16" s="1" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="T16" s="1">
+      <c r="V16" s="1">
         <v>0</v>
       </c>
-      <c r="U16" s="1"/>
-      <c r="V16" s="1">
-        <f>G16*Q16</f>
-        <v>7</v>
+      <c r="W16" s="1"/>
+      <c r="X16" s="1">
+        <f t="shared" si="6"/>
+        <v>105</v>
       </c>
-      <c r="W16" s="1"/>
-      <c r="X16" s="1"/>
       <c r="Y16" s="1"/>
       <c r="Z16" s="1"/>
       <c r="AA16" s="1"/>
@@ -1615,8 +1710,10 @@
       <c r="AJ16" s="1"/>
       <c r="AK16" s="1"/>
       <c r="AL16" s="1"/>
-    </row>
-    <row r="17" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM16" s="1"/>
+      <c r="AN16" s="1"/>
+    </row>
+    <row r="17" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -1655,8 +1752,10 @@
       <c r="AJ17" s="1"/>
       <c r="AK17" s="1"/>
       <c r="AL17" s="1"/>
-    </row>
-    <row r="18" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM17" s="1"/>
+      <c r="AN17" s="1"/>
+    </row>
+    <row r="18" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -1695,8 +1794,10 @@
       <c r="AJ18" s="1"/>
       <c r="AK18" s="1"/>
       <c r="AL18" s="1"/>
-    </row>
-    <row r="19" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM18" s="1"/>
+      <c r="AN18" s="1"/>
+    </row>
+    <row r="19" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -1735,8 +1836,10 @@
       <c r="AJ19" s="1"/>
       <c r="AK19" s="1"/>
       <c r="AL19" s="1"/>
-    </row>
-    <row r="20" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM19" s="1"/>
+      <c r="AN19" s="1"/>
+    </row>
+    <row r="20" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
@@ -1775,8 +1878,10 @@
       <c r="AJ20" s="1"/>
       <c r="AK20" s="1"/>
       <c r="AL20" s="1"/>
-    </row>
-    <row r="21" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM20" s="1"/>
+      <c r="AN20" s="1"/>
+    </row>
+    <row r="21" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -1815,8 +1920,10 @@
       <c r="AJ21" s="1"/>
       <c r="AK21" s="1"/>
       <c r="AL21" s="1"/>
-    </row>
-    <row r="22" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM21" s="1"/>
+      <c r="AN21" s="1"/>
+    </row>
+    <row r="22" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -1855,8 +1962,10 @@
       <c r="AJ22" s="1"/>
       <c r="AK22" s="1"/>
       <c r="AL22" s="1"/>
-    </row>
-    <row r="23" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM22" s="1"/>
+      <c r="AN22" s="1"/>
+    </row>
+    <row r="23" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
@@ -1895,8 +2004,10 @@
       <c r="AJ23" s="1"/>
       <c r="AK23" s="1"/>
       <c r="AL23" s="1"/>
-    </row>
-    <row r="24" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM23" s="1"/>
+      <c r="AN23" s="1"/>
+    </row>
+    <row r="24" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -1935,8 +2046,10 @@
       <c r="AJ24" s="1"/>
       <c r="AK24" s="1"/>
       <c r="AL24" s="1"/>
-    </row>
-    <row r="25" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM24" s="1"/>
+      <c r="AN24" s="1"/>
+    </row>
+    <row r="25" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -1975,8 +2088,10 @@
       <c r="AJ25" s="1"/>
       <c r="AK25" s="1"/>
       <c r="AL25" s="1"/>
-    </row>
-    <row r="26" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM25" s="1"/>
+      <c r="AN25" s="1"/>
+    </row>
+    <row r="26" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -2015,8 +2130,10 @@
       <c r="AJ26" s="1"/>
       <c r="AK26" s="1"/>
       <c r="AL26" s="1"/>
-    </row>
-    <row r="27" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM26" s="1"/>
+      <c r="AN26" s="1"/>
+    </row>
+    <row r="27" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -2055,8 +2172,10 @@
       <c r="AJ27" s="1"/>
       <c r="AK27" s="1"/>
       <c r="AL27" s="1"/>
-    </row>
-    <row r="28" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM27" s="1"/>
+      <c r="AN27" s="1"/>
+    </row>
+    <row r="28" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -2095,8 +2214,10 @@
       <c r="AJ28" s="1"/>
       <c r="AK28" s="1"/>
       <c r="AL28" s="1"/>
-    </row>
-    <row r="29" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM28" s="1"/>
+      <c r="AN28" s="1"/>
+    </row>
+    <row r="29" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -2135,8 +2256,10 @@
       <c r="AJ29" s="1"/>
       <c r="AK29" s="1"/>
       <c r="AL29" s="1"/>
-    </row>
-    <row r="30" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM29" s="1"/>
+      <c r="AN29" s="1"/>
+    </row>
+    <row r="30" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -2175,8 +2298,10 @@
       <c r="AJ30" s="1"/>
       <c r="AK30" s="1"/>
       <c r="AL30" s="1"/>
-    </row>
-    <row r="31" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM30" s="1"/>
+      <c r="AN30" s="1"/>
+    </row>
+    <row r="31" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -2215,8 +2340,10 @@
       <c r="AJ31" s="1"/>
       <c r="AK31" s="1"/>
       <c r="AL31" s="1"/>
-    </row>
-    <row r="32" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM31" s="1"/>
+      <c r="AN31" s="1"/>
+    </row>
+    <row r="32" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -2255,8 +2382,10 @@
       <c r="AJ32" s="1"/>
       <c r="AK32" s="1"/>
       <c r="AL32" s="1"/>
-    </row>
-    <row r="33" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM32" s="1"/>
+      <c r="AN32" s="1"/>
+    </row>
+    <row r="33" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
@@ -2295,8 +2424,10 @@
       <c r="AJ33" s="1"/>
       <c r="AK33" s="1"/>
       <c r="AL33" s="1"/>
-    </row>
-    <row r="34" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM33" s="1"/>
+      <c r="AN33" s="1"/>
+    </row>
+    <row r="34" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
@@ -2335,8 +2466,10 @@
       <c r="AJ34" s="1"/>
       <c r="AK34" s="1"/>
       <c r="AL34" s="1"/>
-    </row>
-    <row r="35" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM34" s="1"/>
+      <c r="AN34" s="1"/>
+    </row>
+    <row r="35" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
@@ -2375,8 +2508,10 @@
       <c r="AJ35" s="1"/>
       <c r="AK35" s="1"/>
       <c r="AL35" s="1"/>
-    </row>
-    <row r="36" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM35" s="1"/>
+      <c r="AN35" s="1"/>
+    </row>
+    <row r="36" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
@@ -2415,8 +2550,10 @@
       <c r="AJ36" s="1"/>
       <c r="AK36" s="1"/>
       <c r="AL36" s="1"/>
-    </row>
-    <row r="37" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM36" s="1"/>
+      <c r="AN36" s="1"/>
+    </row>
+    <row r="37" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
@@ -2455,8 +2592,10 @@
       <c r="AJ37" s="1"/>
       <c r="AK37" s="1"/>
       <c r="AL37" s="1"/>
-    </row>
-    <row r="38" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM37" s="1"/>
+      <c r="AN37" s="1"/>
+    </row>
+    <row r="38" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
@@ -2495,8 +2634,10 @@
       <c r="AJ38" s="1"/>
       <c r="AK38" s="1"/>
       <c r="AL38" s="1"/>
-    </row>
-    <row r="39" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM38" s="1"/>
+      <c r="AN38" s="1"/>
+    </row>
+    <row r="39" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
@@ -2535,8 +2676,10 @@
       <c r="AJ39" s="1"/>
       <c r="AK39" s="1"/>
       <c r="AL39" s="1"/>
-    </row>
-    <row r="40" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM39" s="1"/>
+      <c r="AN39" s="1"/>
+    </row>
+    <row r="40" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
@@ -2575,8 +2718,10 @@
       <c r="AJ40" s="1"/>
       <c r="AK40" s="1"/>
       <c r="AL40" s="1"/>
-    </row>
-    <row r="41" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM40" s="1"/>
+      <c r="AN40" s="1"/>
+    </row>
+    <row r="41" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
@@ -2615,8 +2760,10 @@
       <c r="AJ41" s="1"/>
       <c r="AK41" s="1"/>
       <c r="AL41" s="1"/>
-    </row>
-    <row r="42" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM41" s="1"/>
+      <c r="AN41" s="1"/>
+    </row>
+    <row r="42" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A42" s="1"/>
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
@@ -2655,8 +2802,10 @@
       <c r="AJ42" s="1"/>
       <c r="AK42" s="1"/>
       <c r="AL42" s="1"/>
-    </row>
-    <row r="43" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM42" s="1"/>
+      <c r="AN42" s="1"/>
+    </row>
+    <row r="43" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A43" s="1"/>
       <c r="B43" s="1"/>
       <c r="C43" s="1"/>
@@ -2695,8 +2844,10 @@
       <c r="AJ43" s="1"/>
       <c r="AK43" s="1"/>
       <c r="AL43" s="1"/>
-    </row>
-    <row r="44" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM43" s="1"/>
+      <c r="AN43" s="1"/>
+    </row>
+    <row r="44" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A44" s="1"/>
       <c r="B44" s="1"/>
       <c r="C44" s="1"/>
@@ -2735,8 +2886,10 @@
       <c r="AJ44" s="1"/>
       <c r="AK44" s="1"/>
       <c r="AL44" s="1"/>
-    </row>
-    <row r="45" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM44" s="1"/>
+      <c r="AN44" s="1"/>
+    </row>
+    <row r="45" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A45" s="1"/>
       <c r="B45" s="1"/>
       <c r="C45" s="1"/>
@@ -2775,8 +2928,10 @@
       <c r="AJ45" s="1"/>
       <c r="AK45" s="1"/>
       <c r="AL45" s="1"/>
-    </row>
-    <row r="46" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM45" s="1"/>
+      <c r="AN45" s="1"/>
+    </row>
+    <row r="46" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A46" s="1"/>
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
@@ -2815,8 +2970,10 @@
       <c r="AJ46" s="1"/>
       <c r="AK46" s="1"/>
       <c r="AL46" s="1"/>
-    </row>
-    <row r="47" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM46" s="1"/>
+      <c r="AN46" s="1"/>
+    </row>
+    <row r="47" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
@@ -2855,8 +3012,10 @@
       <c r="AJ47" s="1"/>
       <c r="AK47" s="1"/>
       <c r="AL47" s="1"/>
-    </row>
-    <row r="48" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM47" s="1"/>
+      <c r="AN47" s="1"/>
+    </row>
+    <row r="48" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
@@ -2895,8 +3054,10 @@
       <c r="AJ48" s="1"/>
       <c r="AK48" s="1"/>
       <c r="AL48" s="1"/>
-    </row>
-    <row r="49" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM48" s="1"/>
+      <c r="AN48" s="1"/>
+    </row>
+    <row r="49" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A49" s="1"/>
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
@@ -2935,8 +3096,10 @@
       <c r="AJ49" s="1"/>
       <c r="AK49" s="1"/>
       <c r="AL49" s="1"/>
-    </row>
-    <row r="50" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM49" s="1"/>
+      <c r="AN49" s="1"/>
+    </row>
+    <row r="50" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A50" s="1"/>
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
@@ -2975,8 +3138,10 @@
       <c r="AJ50" s="1"/>
       <c r="AK50" s="1"/>
       <c r="AL50" s="1"/>
-    </row>
-    <row r="51" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM50" s="1"/>
+      <c r="AN50" s="1"/>
+    </row>
+    <row r="51" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A51" s="1"/>
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
@@ -3015,8 +3180,10 @@
       <c r="AJ51" s="1"/>
       <c r="AK51" s="1"/>
       <c r="AL51" s="1"/>
-    </row>
-    <row r="52" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM51" s="1"/>
+      <c r="AN51" s="1"/>
+    </row>
+    <row r="52" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A52" s="1"/>
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
@@ -3055,8 +3222,10 @@
       <c r="AJ52" s="1"/>
       <c r="AK52" s="1"/>
       <c r="AL52" s="1"/>
-    </row>
-    <row r="53" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM52" s="1"/>
+      <c r="AN52" s="1"/>
+    </row>
+    <row r="53" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A53" s="1"/>
       <c r="B53" s="1"/>
       <c r="C53" s="1"/>
@@ -3095,8 +3264,10 @@
       <c r="AJ53" s="1"/>
       <c r="AK53" s="1"/>
       <c r="AL53" s="1"/>
-    </row>
-    <row r="54" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM53" s="1"/>
+      <c r="AN53" s="1"/>
+    </row>
+    <row r="54" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
@@ -3135,8 +3306,10 @@
       <c r="AJ54" s="1"/>
       <c r="AK54" s="1"/>
       <c r="AL54" s="1"/>
-    </row>
-    <row r="55" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM54" s="1"/>
+      <c r="AN54" s="1"/>
+    </row>
+    <row r="55" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A55" s="1"/>
       <c r="B55" s="1"/>
       <c r="C55" s="1"/>
@@ -3175,8 +3348,10 @@
       <c r="AJ55" s="1"/>
       <c r="AK55" s="1"/>
       <c r="AL55" s="1"/>
-    </row>
-    <row r="56" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM55" s="1"/>
+      <c r="AN55" s="1"/>
+    </row>
+    <row r="56" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A56" s="1"/>
       <c r="B56" s="1"/>
       <c r="C56" s="1"/>
@@ -3215,8 +3390,10 @@
       <c r="AJ56" s="1"/>
       <c r="AK56" s="1"/>
       <c r="AL56" s="1"/>
-    </row>
-    <row r="57" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM56" s="1"/>
+      <c r="AN56" s="1"/>
+    </row>
+    <row r="57" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A57" s="1"/>
       <c r="B57" s="1"/>
       <c r="C57" s="1"/>
@@ -3255,8 +3432,10 @@
       <c r="AJ57" s="1"/>
       <c r="AK57" s="1"/>
       <c r="AL57" s="1"/>
-    </row>
-    <row r="58" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM57" s="1"/>
+      <c r="AN57" s="1"/>
+    </row>
+    <row r="58" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A58" s="1"/>
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
@@ -3295,8 +3474,10 @@
       <c r="AJ58" s="1"/>
       <c r="AK58" s="1"/>
       <c r="AL58" s="1"/>
-    </row>
-    <row r="59" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM58" s="1"/>
+      <c r="AN58" s="1"/>
+    </row>
+    <row r="59" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A59" s="1"/>
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
@@ -3335,8 +3516,10 @@
       <c r="AJ59" s="1"/>
       <c r="AK59" s="1"/>
       <c r="AL59" s="1"/>
-    </row>
-    <row r="60" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM59" s="1"/>
+      <c r="AN59" s="1"/>
+    </row>
+    <row r="60" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A60" s="1"/>
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
@@ -3375,8 +3558,10 @@
       <c r="AJ60" s="1"/>
       <c r="AK60" s="1"/>
       <c r="AL60" s="1"/>
-    </row>
-    <row r="61" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM60" s="1"/>
+      <c r="AN60" s="1"/>
+    </row>
+    <row r="61" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A61" s="1"/>
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
@@ -3415,8 +3600,10 @@
       <c r="AJ61" s="1"/>
       <c r="AK61" s="1"/>
       <c r="AL61" s="1"/>
-    </row>
-    <row r="62" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM61" s="1"/>
+      <c r="AN61" s="1"/>
+    </row>
+    <row r="62" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A62" s="1"/>
       <c r="B62" s="1"/>
       <c r="C62" s="1"/>
@@ -3455,8 +3642,10 @@
       <c r="AJ62" s="1"/>
       <c r="AK62" s="1"/>
       <c r="AL62" s="1"/>
-    </row>
-    <row r="63" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM62" s="1"/>
+      <c r="AN62" s="1"/>
+    </row>
+    <row r="63" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A63" s="1"/>
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
@@ -3495,8 +3684,10 @@
       <c r="AJ63" s="1"/>
       <c r="AK63" s="1"/>
       <c r="AL63" s="1"/>
-    </row>
-    <row r="64" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM63" s="1"/>
+      <c r="AN63" s="1"/>
+    </row>
+    <row r="64" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A64" s="1"/>
       <c r="B64" s="1"/>
       <c r="C64" s="1"/>
@@ -3535,8 +3726,10 @@
       <c r="AJ64" s="1"/>
       <c r="AK64" s="1"/>
       <c r="AL64" s="1"/>
-    </row>
-    <row r="65" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM64" s="1"/>
+      <c r="AN64" s="1"/>
+    </row>
+    <row r="65" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A65" s="1"/>
       <c r="B65" s="1"/>
       <c r="C65" s="1"/>
@@ -3575,8 +3768,10 @@
       <c r="AJ65" s="1"/>
       <c r="AK65" s="1"/>
       <c r="AL65" s="1"/>
-    </row>
-    <row r="66" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM65" s="1"/>
+      <c r="AN65" s="1"/>
+    </row>
+    <row r="66" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A66" s="1"/>
       <c r="B66" s="1"/>
       <c r="C66" s="1"/>
@@ -3615,8 +3810,10 @@
       <c r="AJ66" s="1"/>
       <c r="AK66" s="1"/>
       <c r="AL66" s="1"/>
-    </row>
-    <row r="67" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM66" s="1"/>
+      <c r="AN66" s="1"/>
+    </row>
+    <row r="67" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A67" s="1"/>
       <c r="B67" s="1"/>
       <c r="C67" s="1"/>
@@ -3655,8 +3852,10 @@
       <c r="AJ67" s="1"/>
       <c r="AK67" s="1"/>
       <c r="AL67" s="1"/>
-    </row>
-    <row r="68" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM67" s="1"/>
+      <c r="AN67" s="1"/>
+    </row>
+    <row r="68" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A68" s="1"/>
       <c r="B68" s="1"/>
       <c r="C68" s="1"/>
@@ -3695,8 +3894,10 @@
       <c r="AJ68" s="1"/>
       <c r="AK68" s="1"/>
       <c r="AL68" s="1"/>
-    </row>
-    <row r="69" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM68" s="1"/>
+      <c r="AN68" s="1"/>
+    </row>
+    <row r="69" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A69" s="1"/>
       <c r="B69" s="1"/>
       <c r="C69" s="1"/>
@@ -3735,8 +3936,10 @@
       <c r="AJ69" s="1"/>
       <c r="AK69" s="1"/>
       <c r="AL69" s="1"/>
-    </row>
-    <row r="70" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM69" s="1"/>
+      <c r="AN69" s="1"/>
+    </row>
+    <row r="70" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A70" s="1"/>
       <c r="B70" s="1"/>
       <c r="C70" s="1"/>
@@ -3775,8 +3978,10 @@
       <c r="AJ70" s="1"/>
       <c r="AK70" s="1"/>
       <c r="AL70" s="1"/>
-    </row>
-    <row r="71" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM70" s="1"/>
+      <c r="AN70" s="1"/>
+    </row>
+    <row r="71" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A71" s="1"/>
       <c r="B71" s="1"/>
       <c r="C71" s="1"/>
@@ -3815,8 +4020,10 @@
       <c r="AJ71" s="1"/>
       <c r="AK71" s="1"/>
       <c r="AL71" s="1"/>
-    </row>
-    <row r="72" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM71" s="1"/>
+      <c r="AN71" s="1"/>
+    </row>
+    <row r="72" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A72" s="1"/>
       <c r="B72" s="1"/>
       <c r="C72" s="1"/>
@@ -3855,8 +4062,10 @@
       <c r="AJ72" s="1"/>
       <c r="AK72" s="1"/>
       <c r="AL72" s="1"/>
-    </row>
-    <row r="73" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM72" s="1"/>
+      <c r="AN72" s="1"/>
+    </row>
+    <row r="73" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A73" s="1"/>
       <c r="B73" s="1"/>
       <c r="C73" s="1"/>
@@ -3895,8 +4104,10 @@
       <c r="AJ73" s="1"/>
       <c r="AK73" s="1"/>
       <c r="AL73" s="1"/>
-    </row>
-    <row r="74" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM73" s="1"/>
+      <c r="AN73" s="1"/>
+    </row>
+    <row r="74" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A74" s="1"/>
       <c r="B74" s="1"/>
       <c r="C74" s="1"/>
@@ -3935,8 +4146,10 @@
       <c r="AJ74" s="1"/>
       <c r="AK74" s="1"/>
       <c r="AL74" s="1"/>
-    </row>
-    <row r="75" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM74" s="1"/>
+      <c r="AN74" s="1"/>
+    </row>
+    <row r="75" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A75" s="1"/>
       <c r="B75" s="1"/>
       <c r="C75" s="1"/>
@@ -3975,8 +4188,10 @@
       <c r="AJ75" s="1"/>
       <c r="AK75" s="1"/>
       <c r="AL75" s="1"/>
-    </row>
-    <row r="76" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM75" s="1"/>
+      <c r="AN75" s="1"/>
+    </row>
+    <row r="76" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A76" s="1"/>
       <c r="B76" s="1"/>
       <c r="C76" s="1"/>
@@ -4015,8 +4230,10 @@
       <c r="AJ76" s="1"/>
       <c r="AK76" s="1"/>
       <c r="AL76" s="1"/>
-    </row>
-    <row r="77" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM76" s="1"/>
+      <c r="AN76" s="1"/>
+    </row>
+    <row r="77" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A77" s="1"/>
       <c r="B77" s="1"/>
       <c r="C77" s="1"/>
@@ -4055,8 +4272,10 @@
       <c r="AJ77" s="1"/>
       <c r="AK77" s="1"/>
       <c r="AL77" s="1"/>
-    </row>
-    <row r="78" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM77" s="1"/>
+      <c r="AN77" s="1"/>
+    </row>
+    <row r="78" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A78" s="1"/>
       <c r="B78" s="1"/>
       <c r="C78" s="1"/>
@@ -4095,8 +4314,10 @@
       <c r="AJ78" s="1"/>
       <c r="AK78" s="1"/>
       <c r="AL78" s="1"/>
-    </row>
-    <row r="79" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM78" s="1"/>
+      <c r="AN78" s="1"/>
+    </row>
+    <row r="79" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A79" s="1"/>
       <c r="B79" s="1"/>
       <c r="C79" s="1"/>
@@ -4135,8 +4356,10 @@
       <c r="AJ79" s="1"/>
       <c r="AK79" s="1"/>
       <c r="AL79" s="1"/>
-    </row>
-    <row r="80" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM79" s="1"/>
+      <c r="AN79" s="1"/>
+    </row>
+    <row r="80" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A80" s="1"/>
       <c r="B80" s="1"/>
       <c r="C80" s="1"/>
@@ -4175,8 +4398,10 @@
       <c r="AJ80" s="1"/>
       <c r="AK80" s="1"/>
       <c r="AL80" s="1"/>
-    </row>
-    <row r="81" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM80" s="1"/>
+      <c r="AN80" s="1"/>
+    </row>
+    <row r="81" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A81" s="1"/>
       <c r="B81" s="1"/>
       <c r="C81" s="1"/>
@@ -4215,8 +4440,10 @@
       <c r="AJ81" s="1"/>
       <c r="AK81" s="1"/>
       <c r="AL81" s="1"/>
-    </row>
-    <row r="82" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM81" s="1"/>
+      <c r="AN81" s="1"/>
+    </row>
+    <row r="82" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A82" s="1"/>
       <c r="B82" s="1"/>
       <c r="C82" s="1"/>
@@ -4255,8 +4482,10 @@
       <c r="AJ82" s="1"/>
       <c r="AK82" s="1"/>
       <c r="AL82" s="1"/>
-    </row>
-    <row r="83" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM82" s="1"/>
+      <c r="AN82" s="1"/>
+    </row>
+    <row r="83" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A83" s="1"/>
       <c r="B83" s="1"/>
       <c r="C83" s="1"/>
@@ -4295,8 +4524,10 @@
       <c r="AJ83" s="1"/>
       <c r="AK83" s="1"/>
       <c r="AL83" s="1"/>
-    </row>
-    <row r="84" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM83" s="1"/>
+      <c r="AN83" s="1"/>
+    </row>
+    <row r="84" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A84" s="1"/>
       <c r="B84" s="1"/>
       <c r="C84" s="1"/>
@@ -4335,8 +4566,10 @@
       <c r="AJ84" s="1"/>
       <c r="AK84" s="1"/>
       <c r="AL84" s="1"/>
-    </row>
-    <row r="85" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM84" s="1"/>
+      <c r="AN84" s="1"/>
+    </row>
+    <row r="85" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A85" s="1"/>
       <c r="B85" s="1"/>
       <c r="C85" s="1"/>
@@ -4375,8 +4608,10 @@
       <c r="AJ85" s="1"/>
       <c r="AK85" s="1"/>
       <c r="AL85" s="1"/>
-    </row>
-    <row r="86" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM85" s="1"/>
+      <c r="AN85" s="1"/>
+    </row>
+    <row r="86" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A86" s="1"/>
       <c r="B86" s="1"/>
       <c r="C86" s="1"/>
@@ -4415,8 +4650,10 @@
       <c r="AJ86" s="1"/>
       <c r="AK86" s="1"/>
       <c r="AL86" s="1"/>
-    </row>
-    <row r="87" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM86" s="1"/>
+      <c r="AN86" s="1"/>
+    </row>
+    <row r="87" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A87" s="1"/>
       <c r="B87" s="1"/>
       <c r="C87" s="1"/>
@@ -4455,8 +4692,10 @@
       <c r="AJ87" s="1"/>
       <c r="AK87" s="1"/>
       <c r="AL87" s="1"/>
-    </row>
-    <row r="88" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM87" s="1"/>
+      <c r="AN87" s="1"/>
+    </row>
+    <row r="88" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A88" s="1"/>
       <c r="B88" s="1"/>
       <c r="C88" s="1"/>
@@ -4495,8 +4734,10 @@
       <c r="AJ88" s="1"/>
       <c r="AK88" s="1"/>
       <c r="AL88" s="1"/>
-    </row>
-    <row r="89" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM88" s="1"/>
+      <c r="AN88" s="1"/>
+    </row>
+    <row r="89" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A89" s="1"/>
       <c r="B89" s="1"/>
       <c r="C89" s="1"/>
@@ -4535,8 +4776,10 @@
       <c r="AJ89" s="1"/>
       <c r="AK89" s="1"/>
       <c r="AL89" s="1"/>
-    </row>
-    <row r="90" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM89" s="1"/>
+      <c r="AN89" s="1"/>
+    </row>
+    <row r="90" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A90" s="1"/>
       <c r="B90" s="1"/>
       <c r="C90" s="1"/>
@@ -4575,8 +4818,10 @@
       <c r="AJ90" s="1"/>
       <c r="AK90" s="1"/>
       <c r="AL90" s="1"/>
-    </row>
-    <row r="91" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM90" s="1"/>
+      <c r="AN90" s="1"/>
+    </row>
+    <row r="91" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A91" s="1"/>
       <c r="B91" s="1"/>
       <c r="C91" s="1"/>
@@ -4615,8 +4860,10 @@
       <c r="AJ91" s="1"/>
       <c r="AK91" s="1"/>
       <c r="AL91" s="1"/>
-    </row>
-    <row r="92" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM91" s="1"/>
+      <c r="AN91" s="1"/>
+    </row>
+    <row r="92" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A92" s="1"/>
       <c r="B92" s="1"/>
       <c r="C92" s="1"/>
@@ -4655,8 +4902,10 @@
       <c r="AJ92" s="1"/>
       <c r="AK92" s="1"/>
       <c r="AL92" s="1"/>
-    </row>
-    <row r="93" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM92" s="1"/>
+      <c r="AN92" s="1"/>
+    </row>
+    <row r="93" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A93" s="1"/>
       <c r="B93" s="1"/>
       <c r="C93" s="1"/>
@@ -4695,8 +4944,10 @@
       <c r="AJ93" s="1"/>
       <c r="AK93" s="1"/>
       <c r="AL93" s="1"/>
-    </row>
-    <row r="94" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM93" s="1"/>
+      <c r="AN93" s="1"/>
+    </row>
+    <row r="94" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A94" s="1"/>
       <c r="B94" s="1"/>
       <c r="C94" s="1"/>
@@ -4735,8 +4986,10 @@
       <c r="AJ94" s="1"/>
       <c r="AK94" s="1"/>
       <c r="AL94" s="1"/>
-    </row>
-    <row r="95" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM94" s="1"/>
+      <c r="AN94" s="1"/>
+    </row>
+    <row r="95" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A95" s="1"/>
       <c r="B95" s="1"/>
       <c r="C95" s="1"/>
@@ -4775,8 +5028,10 @@
       <c r="AJ95" s="1"/>
       <c r="AK95" s="1"/>
       <c r="AL95" s="1"/>
-    </row>
-    <row r="96" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM95" s="1"/>
+      <c r="AN95" s="1"/>
+    </row>
+    <row r="96" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A96" s="1"/>
       <c r="B96" s="1"/>
       <c r="C96" s="1"/>
@@ -4815,8 +5070,10 @@
       <c r="AJ96" s="1"/>
       <c r="AK96" s="1"/>
       <c r="AL96" s="1"/>
-    </row>
-    <row r="97" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM96" s="1"/>
+      <c r="AN96" s="1"/>
+    </row>
+    <row r="97" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A97" s="1"/>
       <c r="B97" s="1"/>
       <c r="C97" s="1"/>
@@ -4855,8 +5112,10 @@
       <c r="AJ97" s="1"/>
       <c r="AK97" s="1"/>
       <c r="AL97" s="1"/>
-    </row>
-    <row r="98" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM97" s="1"/>
+      <c r="AN97" s="1"/>
+    </row>
+    <row r="98" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A98" s="1"/>
       <c r="B98" s="1"/>
       <c r="C98" s="1"/>
@@ -4895,8 +5154,10 @@
       <c r="AJ98" s="1"/>
       <c r="AK98" s="1"/>
       <c r="AL98" s="1"/>
-    </row>
-    <row r="99" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM98" s="1"/>
+      <c r="AN98" s="1"/>
+    </row>
+    <row r="99" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A99" s="1"/>
       <c r="B99" s="1"/>
       <c r="C99" s="1"/>
@@ -4935,8 +5196,10 @@
       <c r="AJ99" s="1"/>
       <c r="AK99" s="1"/>
       <c r="AL99" s="1"/>
-    </row>
-    <row r="100" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM99" s="1"/>
+      <c r="AN99" s="1"/>
+    </row>
+    <row r="100" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A100" s="1"/>
       <c r="B100" s="1"/>
       <c r="C100" s="1"/>
@@ -4975,8 +5238,10 @@
       <c r="AJ100" s="1"/>
       <c r="AK100" s="1"/>
       <c r="AL100" s="1"/>
-    </row>
-    <row r="101" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM100" s="1"/>
+      <c r="AN100" s="1"/>
+    </row>
+    <row r="101" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A101" s="1"/>
       <c r="B101" s="1"/>
       <c r="C101" s="1"/>
@@ -5015,8 +5280,10 @@
       <c r="AJ101" s="1"/>
       <c r="AK101" s="1"/>
       <c r="AL101" s="1"/>
-    </row>
-    <row r="102" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM101" s="1"/>
+      <c r="AN101" s="1"/>
+    </row>
+    <row r="102" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A102" s="1"/>
       <c r="B102" s="1"/>
       <c r="C102" s="1"/>
@@ -5055,8 +5322,10 @@
       <c r="AJ102" s="1"/>
       <c r="AK102" s="1"/>
       <c r="AL102" s="1"/>
-    </row>
-    <row r="103" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM102" s="1"/>
+      <c r="AN102" s="1"/>
+    </row>
+    <row r="103" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A103" s="1"/>
       <c r="B103" s="1"/>
       <c r="C103" s="1"/>
@@ -5095,8 +5364,10 @@
       <c r="AJ103" s="1"/>
       <c r="AK103" s="1"/>
       <c r="AL103" s="1"/>
-    </row>
-    <row r="104" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM103" s="1"/>
+      <c r="AN103" s="1"/>
+    </row>
+    <row r="104" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A104" s="1"/>
       <c r="B104" s="1"/>
       <c r="C104" s="1"/>
@@ -5135,8 +5406,10 @@
       <c r="AJ104" s="1"/>
       <c r="AK104" s="1"/>
       <c r="AL104" s="1"/>
-    </row>
-    <row r="105" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM104" s="1"/>
+      <c r="AN104" s="1"/>
+    </row>
+    <row r="105" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A105" s="1"/>
       <c r="B105" s="1"/>
       <c r="C105" s="1"/>
@@ -5175,8 +5448,10 @@
       <c r="AJ105" s="1"/>
       <c r="AK105" s="1"/>
       <c r="AL105" s="1"/>
-    </row>
-    <row r="106" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM105" s="1"/>
+      <c r="AN105" s="1"/>
+    </row>
+    <row r="106" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A106" s="1"/>
       <c r="B106" s="1"/>
       <c r="C106" s="1"/>
@@ -5215,8 +5490,10 @@
       <c r="AJ106" s="1"/>
       <c r="AK106" s="1"/>
       <c r="AL106" s="1"/>
-    </row>
-    <row r="107" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM106" s="1"/>
+      <c r="AN106" s="1"/>
+    </row>
+    <row r="107" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A107" s="1"/>
       <c r="B107" s="1"/>
       <c r="C107" s="1"/>
@@ -5255,8 +5532,10 @@
       <c r="AJ107" s="1"/>
       <c r="AK107" s="1"/>
       <c r="AL107" s="1"/>
-    </row>
-    <row r="108" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM107" s="1"/>
+      <c r="AN107" s="1"/>
+    </row>
+    <row r="108" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A108" s="1"/>
       <c r="B108" s="1"/>
       <c r="C108" s="1"/>
@@ -5295,8 +5574,10 @@
       <c r="AJ108" s="1"/>
       <c r="AK108" s="1"/>
       <c r="AL108" s="1"/>
-    </row>
-    <row r="109" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM108" s="1"/>
+      <c r="AN108" s="1"/>
+    </row>
+    <row r="109" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A109" s="1"/>
       <c r="B109" s="1"/>
       <c r="C109" s="1"/>
@@ -5335,8 +5616,10 @@
       <c r="AJ109" s="1"/>
       <c r="AK109" s="1"/>
       <c r="AL109" s="1"/>
-    </row>
-    <row r="110" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM109" s="1"/>
+      <c r="AN109" s="1"/>
+    </row>
+    <row r="110" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A110" s="1"/>
       <c r="B110" s="1"/>
       <c r="C110" s="1"/>
@@ -5375,8 +5658,10 @@
       <c r="AJ110" s="1"/>
       <c r="AK110" s="1"/>
       <c r="AL110" s="1"/>
-    </row>
-    <row r="111" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM110" s="1"/>
+      <c r="AN110" s="1"/>
+    </row>
+    <row r="111" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A111" s="1"/>
       <c r="B111" s="1"/>
       <c r="C111" s="1"/>
@@ -5415,8 +5700,10 @@
       <c r="AJ111" s="1"/>
       <c r="AK111" s="1"/>
       <c r="AL111" s="1"/>
-    </row>
-    <row r="112" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM111" s="1"/>
+      <c r="AN111" s="1"/>
+    </row>
+    <row r="112" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A112" s="1"/>
       <c r="B112" s="1"/>
       <c r="C112" s="1"/>
@@ -5455,8 +5742,10 @@
       <c r="AJ112" s="1"/>
       <c r="AK112" s="1"/>
       <c r="AL112" s="1"/>
-    </row>
-    <row r="113" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM112" s="1"/>
+      <c r="AN112" s="1"/>
+    </row>
+    <row r="113" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A113" s="1"/>
       <c r="B113" s="1"/>
       <c r="C113" s="1"/>
@@ -5495,8 +5784,10 @@
       <c r="AJ113" s="1"/>
       <c r="AK113" s="1"/>
       <c r="AL113" s="1"/>
-    </row>
-    <row r="114" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM113" s="1"/>
+      <c r="AN113" s="1"/>
+    </row>
+    <row r="114" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A114" s="1"/>
       <c r="B114" s="1"/>
       <c r="C114" s="1"/>
@@ -5535,8 +5826,10 @@
       <c r="AJ114" s="1"/>
       <c r="AK114" s="1"/>
       <c r="AL114" s="1"/>
-    </row>
-    <row r="115" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM114" s="1"/>
+      <c r="AN114" s="1"/>
+    </row>
+    <row r="115" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A115" s="1"/>
       <c r="B115" s="1"/>
       <c r="C115" s="1"/>
@@ -5575,8 +5868,10 @@
       <c r="AJ115" s="1"/>
       <c r="AK115" s="1"/>
       <c r="AL115" s="1"/>
-    </row>
-    <row r="116" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM115" s="1"/>
+      <c r="AN115" s="1"/>
+    </row>
+    <row r="116" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A116" s="1"/>
       <c r="B116" s="1"/>
       <c r="C116" s="1"/>
@@ -5615,8 +5910,10 @@
       <c r="AJ116" s="1"/>
       <c r="AK116" s="1"/>
       <c r="AL116" s="1"/>
-    </row>
-    <row r="117" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM116" s="1"/>
+      <c r="AN116" s="1"/>
+    </row>
+    <row r="117" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A117" s="1"/>
       <c r="B117" s="1"/>
       <c r="C117" s="1"/>
@@ -5655,8 +5952,10 @@
       <c r="AJ117" s="1"/>
       <c r="AK117" s="1"/>
       <c r="AL117" s="1"/>
-    </row>
-    <row r="118" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM117" s="1"/>
+      <c r="AN117" s="1"/>
+    </row>
+    <row r="118" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A118" s="1"/>
       <c r="B118" s="1"/>
       <c r="C118" s="1"/>
@@ -5695,8 +5994,10 @@
       <c r="AJ118" s="1"/>
       <c r="AK118" s="1"/>
       <c r="AL118" s="1"/>
-    </row>
-    <row r="119" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM118" s="1"/>
+      <c r="AN118" s="1"/>
+    </row>
+    <row r="119" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A119" s="1"/>
       <c r="B119" s="1"/>
       <c r="C119" s="1"/>
@@ -5735,8 +6036,10 @@
       <c r="AJ119" s="1"/>
       <c r="AK119" s="1"/>
       <c r="AL119" s="1"/>
-    </row>
-    <row r="120" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM119" s="1"/>
+      <c r="AN119" s="1"/>
+    </row>
+    <row r="120" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A120" s="1"/>
       <c r="B120" s="1"/>
       <c r="C120" s="1"/>
@@ -5775,8 +6078,10 @@
       <c r="AJ120" s="1"/>
       <c r="AK120" s="1"/>
       <c r="AL120" s="1"/>
-    </row>
-    <row r="121" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM120" s="1"/>
+      <c r="AN120" s="1"/>
+    </row>
+    <row r="121" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A121" s="1"/>
       <c r="B121" s="1"/>
       <c r="C121" s="1"/>
@@ -5815,8 +6120,10 @@
       <c r="AJ121" s="1"/>
       <c r="AK121" s="1"/>
       <c r="AL121" s="1"/>
-    </row>
-    <row r="122" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM121" s="1"/>
+      <c r="AN121" s="1"/>
+    </row>
+    <row r="122" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A122" s="1"/>
       <c r="B122" s="1"/>
       <c r="C122" s="1"/>
@@ -5855,8 +6162,10 @@
       <c r="AJ122" s="1"/>
       <c r="AK122" s="1"/>
       <c r="AL122" s="1"/>
-    </row>
-    <row r="123" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM122" s="1"/>
+      <c r="AN122" s="1"/>
+    </row>
+    <row r="123" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A123" s="1"/>
       <c r="B123" s="1"/>
       <c r="C123" s="1"/>
@@ -5895,8 +6204,10 @@
       <c r="AJ123" s="1"/>
       <c r="AK123" s="1"/>
       <c r="AL123" s="1"/>
-    </row>
-    <row r="124" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM123" s="1"/>
+      <c r="AN123" s="1"/>
+    </row>
+    <row r="124" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A124" s="1"/>
       <c r="B124" s="1"/>
       <c r="C124" s="1"/>
@@ -5935,8 +6246,10 @@
       <c r="AJ124" s="1"/>
       <c r="AK124" s="1"/>
       <c r="AL124" s="1"/>
-    </row>
-    <row r="125" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM124" s="1"/>
+      <c r="AN124" s="1"/>
+    </row>
+    <row r="125" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A125" s="1"/>
       <c r="B125" s="1"/>
       <c r="C125" s="1"/>
@@ -5975,8 +6288,10 @@
       <c r="AJ125" s="1"/>
       <c r="AK125" s="1"/>
       <c r="AL125" s="1"/>
-    </row>
-    <row r="126" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM125" s="1"/>
+      <c r="AN125" s="1"/>
+    </row>
+    <row r="126" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A126" s="1"/>
       <c r="B126" s="1"/>
       <c r="C126" s="1"/>
@@ -6015,8 +6330,10 @@
       <c r="AJ126" s="1"/>
       <c r="AK126" s="1"/>
       <c r="AL126" s="1"/>
-    </row>
-    <row r="127" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM126" s="1"/>
+      <c r="AN126" s="1"/>
+    </row>
+    <row r="127" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A127" s="1"/>
       <c r="B127" s="1"/>
       <c r="C127" s="1"/>
@@ -6055,8 +6372,10 @@
       <c r="AJ127" s="1"/>
       <c r="AK127" s="1"/>
       <c r="AL127" s="1"/>
-    </row>
-    <row r="128" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM127" s="1"/>
+      <c r="AN127" s="1"/>
+    </row>
+    <row r="128" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A128" s="1"/>
       <c r="B128" s="1"/>
       <c r="C128" s="1"/>
@@ -6095,8 +6414,10 @@
       <c r="AJ128" s="1"/>
       <c r="AK128" s="1"/>
       <c r="AL128" s="1"/>
-    </row>
-    <row r="129" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM128" s="1"/>
+      <c r="AN128" s="1"/>
+    </row>
+    <row r="129" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A129" s="1"/>
       <c r="B129" s="1"/>
       <c r="C129" s="1"/>
@@ -6135,8 +6456,10 @@
       <c r="AJ129" s="1"/>
       <c r="AK129" s="1"/>
       <c r="AL129" s="1"/>
-    </row>
-    <row r="130" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM129" s="1"/>
+      <c r="AN129" s="1"/>
+    </row>
+    <row r="130" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A130" s="1"/>
       <c r="B130" s="1"/>
       <c r="C130" s="1"/>
@@ -6175,8 +6498,10 @@
       <c r="AJ130" s="1"/>
       <c r="AK130" s="1"/>
       <c r="AL130" s="1"/>
-    </row>
-    <row r="131" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM130" s="1"/>
+      <c r="AN130" s="1"/>
+    </row>
+    <row r="131" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A131" s="1"/>
       <c r="B131" s="1"/>
       <c r="C131" s="1"/>
@@ -6215,8 +6540,10 @@
       <c r="AJ131" s="1"/>
       <c r="AK131" s="1"/>
       <c r="AL131" s="1"/>
-    </row>
-    <row r="132" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM131" s="1"/>
+      <c r="AN131" s="1"/>
+    </row>
+    <row r="132" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A132" s="1"/>
       <c r="B132" s="1"/>
       <c r="C132" s="1"/>
@@ -6255,8 +6582,10 @@
       <c r="AJ132" s="1"/>
       <c r="AK132" s="1"/>
       <c r="AL132" s="1"/>
-    </row>
-    <row r="133" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM132" s="1"/>
+      <c r="AN132" s="1"/>
+    </row>
+    <row r="133" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A133" s="1"/>
       <c r="B133" s="1"/>
       <c r="C133" s="1"/>
@@ -6295,8 +6624,10 @@
       <c r="AJ133" s="1"/>
       <c r="AK133" s="1"/>
       <c r="AL133" s="1"/>
-    </row>
-    <row r="134" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM133" s="1"/>
+      <c r="AN133" s="1"/>
+    </row>
+    <row r="134" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A134" s="1"/>
       <c r="B134" s="1"/>
       <c r="C134" s="1"/>
@@ -6335,8 +6666,10 @@
       <c r="AJ134" s="1"/>
       <c r="AK134" s="1"/>
       <c r="AL134" s="1"/>
-    </row>
-    <row r="135" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM134" s="1"/>
+      <c r="AN134" s="1"/>
+    </row>
+    <row r="135" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A135" s="1"/>
       <c r="B135" s="1"/>
       <c r="C135" s="1"/>
@@ -6375,8 +6708,10 @@
       <c r="AJ135" s="1"/>
       <c r="AK135" s="1"/>
       <c r="AL135" s="1"/>
-    </row>
-    <row r="136" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM135" s="1"/>
+      <c r="AN135" s="1"/>
+    </row>
+    <row r="136" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A136" s="1"/>
       <c r="B136" s="1"/>
       <c r="C136" s="1"/>
@@ -6415,8 +6750,10 @@
       <c r="AJ136" s="1"/>
       <c r="AK136" s="1"/>
       <c r="AL136" s="1"/>
-    </row>
-    <row r="137" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM136" s="1"/>
+      <c r="AN136" s="1"/>
+    </row>
+    <row r="137" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A137" s="1"/>
       <c r="B137" s="1"/>
       <c r="C137" s="1"/>
@@ -6455,8 +6792,10 @@
       <c r="AJ137" s="1"/>
       <c r="AK137" s="1"/>
       <c r="AL137" s="1"/>
-    </row>
-    <row r="138" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM137" s="1"/>
+      <c r="AN137" s="1"/>
+    </row>
+    <row r="138" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A138" s="1"/>
       <c r="B138" s="1"/>
       <c r="C138" s="1"/>
@@ -6495,8 +6834,10 @@
       <c r="AJ138" s="1"/>
       <c r="AK138" s="1"/>
       <c r="AL138" s="1"/>
-    </row>
-    <row r="139" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM138" s="1"/>
+      <c r="AN138" s="1"/>
+    </row>
+    <row r="139" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A139" s="1"/>
       <c r="B139" s="1"/>
       <c r="C139" s="1"/>
@@ -6535,8 +6876,10 @@
       <c r="AJ139" s="1"/>
       <c r="AK139" s="1"/>
       <c r="AL139" s="1"/>
-    </row>
-    <row r="140" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM139" s="1"/>
+      <c r="AN139" s="1"/>
+    </row>
+    <row r="140" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A140" s="1"/>
       <c r="B140" s="1"/>
       <c r="C140" s="1"/>
@@ -6575,8 +6918,10 @@
       <c r="AJ140" s="1"/>
       <c r="AK140" s="1"/>
       <c r="AL140" s="1"/>
-    </row>
-    <row r="141" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM140" s="1"/>
+      <c r="AN140" s="1"/>
+    </row>
+    <row r="141" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A141" s="1"/>
       <c r="B141" s="1"/>
       <c r="C141" s="1"/>
@@ -6615,8 +6960,10 @@
       <c r="AJ141" s="1"/>
       <c r="AK141" s="1"/>
       <c r="AL141" s="1"/>
-    </row>
-    <row r="142" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM141" s="1"/>
+      <c r="AN141" s="1"/>
+    </row>
+    <row r="142" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A142" s="1"/>
       <c r="B142" s="1"/>
       <c r="C142" s="1"/>
@@ -6655,8 +7002,10 @@
       <c r="AJ142" s="1"/>
       <c r="AK142" s="1"/>
       <c r="AL142" s="1"/>
-    </row>
-    <row r="143" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM142" s="1"/>
+      <c r="AN142" s="1"/>
+    </row>
+    <row r="143" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A143" s="1"/>
       <c r="B143" s="1"/>
       <c r="C143" s="1"/>
@@ -6695,8 +7044,10 @@
       <c r="AJ143" s="1"/>
       <c r="AK143" s="1"/>
       <c r="AL143" s="1"/>
-    </row>
-    <row r="144" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM143" s="1"/>
+      <c r="AN143" s="1"/>
+    </row>
+    <row r="144" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A144" s="1"/>
       <c r="B144" s="1"/>
       <c r="C144" s="1"/>
@@ -6735,8 +7086,10 @@
       <c r="AJ144" s="1"/>
       <c r="AK144" s="1"/>
       <c r="AL144" s="1"/>
-    </row>
-    <row r="145" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM144" s="1"/>
+      <c r="AN144" s="1"/>
+    </row>
+    <row r="145" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A145" s="1"/>
       <c r="B145" s="1"/>
       <c r="C145" s="1"/>
@@ -6775,8 +7128,10 @@
       <c r="AJ145" s="1"/>
       <c r="AK145" s="1"/>
       <c r="AL145" s="1"/>
-    </row>
-    <row r="146" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM145" s="1"/>
+      <c r="AN145" s="1"/>
+    </row>
+    <row r="146" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A146" s="1"/>
       <c r="B146" s="1"/>
       <c r="C146" s="1"/>
@@ -6815,8 +7170,10 @@
       <c r="AJ146" s="1"/>
       <c r="AK146" s="1"/>
       <c r="AL146" s="1"/>
-    </row>
-    <row r="147" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM146" s="1"/>
+      <c r="AN146" s="1"/>
+    </row>
+    <row r="147" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A147" s="1"/>
       <c r="B147" s="1"/>
       <c r="C147" s="1"/>
@@ -6855,8 +7212,10 @@
       <c r="AJ147" s="1"/>
       <c r="AK147" s="1"/>
       <c r="AL147" s="1"/>
-    </row>
-    <row r="148" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM147" s="1"/>
+      <c r="AN147" s="1"/>
+    </row>
+    <row r="148" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A148" s="1"/>
       <c r="B148" s="1"/>
       <c r="C148" s="1"/>
@@ -6895,8 +7254,10 @@
       <c r="AJ148" s="1"/>
       <c r="AK148" s="1"/>
       <c r="AL148" s="1"/>
-    </row>
-    <row r="149" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM148" s="1"/>
+      <c r="AN148" s="1"/>
+    </row>
+    <row r="149" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A149" s="1"/>
       <c r="B149" s="1"/>
       <c r="C149" s="1"/>
@@ -6935,8 +7296,10 @@
       <c r="AJ149" s="1"/>
       <c r="AK149" s="1"/>
       <c r="AL149" s="1"/>
-    </row>
-    <row r="150" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM149" s="1"/>
+      <c r="AN149" s="1"/>
+    </row>
+    <row r="150" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A150" s="1"/>
       <c r="B150" s="1"/>
       <c r="C150" s="1"/>
@@ -6975,8 +7338,10 @@
       <c r="AJ150" s="1"/>
       <c r="AK150" s="1"/>
       <c r="AL150" s="1"/>
-    </row>
-    <row r="151" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM150" s="1"/>
+      <c r="AN150" s="1"/>
+    </row>
+    <row r="151" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A151" s="1"/>
       <c r="B151" s="1"/>
       <c r="C151" s="1"/>
@@ -7015,8 +7380,10 @@
       <c r="AJ151" s="1"/>
       <c r="AK151" s="1"/>
       <c r="AL151" s="1"/>
-    </row>
-    <row r="152" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM151" s="1"/>
+      <c r="AN151" s="1"/>
+    </row>
+    <row r="152" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A152" s="1"/>
       <c r="B152" s="1"/>
       <c r="C152" s="1"/>
@@ -7055,8 +7422,10 @@
       <c r="AJ152" s="1"/>
       <c r="AK152" s="1"/>
       <c r="AL152" s="1"/>
-    </row>
-    <row r="153" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM152" s="1"/>
+      <c r="AN152" s="1"/>
+    </row>
+    <row r="153" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A153" s="1"/>
       <c r="B153" s="1"/>
       <c r="C153" s="1"/>
@@ -7095,8 +7464,10 @@
       <c r="AJ153" s="1"/>
       <c r="AK153" s="1"/>
       <c r="AL153" s="1"/>
-    </row>
-    <row r="154" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM153" s="1"/>
+      <c r="AN153" s="1"/>
+    </row>
+    <row r="154" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A154" s="1"/>
       <c r="B154" s="1"/>
       <c r="C154" s="1"/>
@@ -7135,8 +7506,10 @@
       <c r="AJ154" s="1"/>
       <c r="AK154" s="1"/>
       <c r="AL154" s="1"/>
-    </row>
-    <row r="155" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM154" s="1"/>
+      <c r="AN154" s="1"/>
+    </row>
+    <row r="155" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A155" s="1"/>
       <c r="B155" s="1"/>
       <c r="C155" s="1"/>
@@ -7175,8 +7548,10 @@
       <c r="AJ155" s="1"/>
       <c r="AK155" s="1"/>
       <c r="AL155" s="1"/>
-    </row>
-    <row r="156" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM155" s="1"/>
+      <c r="AN155" s="1"/>
+    </row>
+    <row r="156" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A156" s="1"/>
       <c r="B156" s="1"/>
       <c r="C156" s="1"/>
@@ -7215,8 +7590,10 @@
       <c r="AJ156" s="1"/>
       <c r="AK156" s="1"/>
       <c r="AL156" s="1"/>
-    </row>
-    <row r="157" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM156" s="1"/>
+      <c r="AN156" s="1"/>
+    </row>
+    <row r="157" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A157" s="1"/>
       <c r="B157" s="1"/>
       <c r="C157" s="1"/>
@@ -7255,8 +7632,10 @@
       <c r="AJ157" s="1"/>
       <c r="AK157" s="1"/>
       <c r="AL157" s="1"/>
-    </row>
-    <row r="158" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM157" s="1"/>
+      <c r="AN157" s="1"/>
+    </row>
+    <row r="158" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A158" s="1"/>
       <c r="B158" s="1"/>
       <c r="C158" s="1"/>
@@ -7295,8 +7674,10 @@
       <c r="AJ158" s="1"/>
       <c r="AK158" s="1"/>
       <c r="AL158" s="1"/>
-    </row>
-    <row r="159" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM158" s="1"/>
+      <c r="AN158" s="1"/>
+    </row>
+    <row r="159" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A159" s="1"/>
       <c r="B159" s="1"/>
       <c r="C159" s="1"/>
@@ -7335,8 +7716,10 @@
       <c r="AJ159" s="1"/>
       <c r="AK159" s="1"/>
       <c r="AL159" s="1"/>
-    </row>
-    <row r="160" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM159" s="1"/>
+      <c r="AN159" s="1"/>
+    </row>
+    <row r="160" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A160" s="1"/>
       <c r="B160" s="1"/>
       <c r="C160" s="1"/>
@@ -7375,8 +7758,10 @@
       <c r="AJ160" s="1"/>
       <c r="AK160" s="1"/>
       <c r="AL160" s="1"/>
-    </row>
-    <row r="161" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM160" s="1"/>
+      <c r="AN160" s="1"/>
+    </row>
+    <row r="161" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A161" s="1"/>
       <c r="B161" s="1"/>
       <c r="C161" s="1"/>
@@ -7415,8 +7800,10 @@
       <c r="AJ161" s="1"/>
       <c r="AK161" s="1"/>
       <c r="AL161" s="1"/>
-    </row>
-    <row r="162" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM161" s="1"/>
+      <c r="AN161" s="1"/>
+    </row>
+    <row r="162" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A162" s="1"/>
       <c r="B162" s="1"/>
       <c r="C162" s="1"/>
@@ -7455,8 +7842,10 @@
       <c r="AJ162" s="1"/>
       <c r="AK162" s="1"/>
       <c r="AL162" s="1"/>
-    </row>
-    <row r="163" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM162" s="1"/>
+      <c r="AN162" s="1"/>
+    </row>
+    <row r="163" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A163" s="1"/>
       <c r="B163" s="1"/>
       <c r="C163" s="1"/>
@@ -7495,8 +7884,10 @@
       <c r="AJ163" s="1"/>
       <c r="AK163" s="1"/>
       <c r="AL163" s="1"/>
-    </row>
-    <row r="164" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM163" s="1"/>
+      <c r="AN163" s="1"/>
+    </row>
+    <row r="164" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A164" s="1"/>
       <c r="B164" s="1"/>
       <c r="C164" s="1"/>
@@ -7535,8 +7926,10 @@
       <c r="AJ164" s="1"/>
       <c r="AK164" s="1"/>
       <c r="AL164" s="1"/>
-    </row>
-    <row r="165" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM164" s="1"/>
+      <c r="AN164" s="1"/>
+    </row>
+    <row r="165" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A165" s="1"/>
       <c r="B165" s="1"/>
       <c r="C165" s="1"/>
@@ -7575,8 +7968,10 @@
       <c r="AJ165" s="1"/>
       <c r="AK165" s="1"/>
       <c r="AL165" s="1"/>
-    </row>
-    <row r="166" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM165" s="1"/>
+      <c r="AN165" s="1"/>
+    </row>
+    <row r="166" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A166" s="1"/>
       <c r="B166" s="1"/>
       <c r="C166" s="1"/>
@@ -7615,8 +8010,10 @@
       <c r="AJ166" s="1"/>
       <c r="AK166" s="1"/>
       <c r="AL166" s="1"/>
-    </row>
-    <row r="167" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM166" s="1"/>
+      <c r="AN166" s="1"/>
+    </row>
+    <row r="167" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A167" s="1"/>
       <c r="B167" s="1"/>
       <c r="C167" s="1"/>
@@ -7655,8 +8052,10 @@
       <c r="AJ167" s="1"/>
       <c r="AK167" s="1"/>
       <c r="AL167" s="1"/>
-    </row>
-    <row r="168" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM167" s="1"/>
+      <c r="AN167" s="1"/>
+    </row>
+    <row r="168" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A168" s="1"/>
       <c r="B168" s="1"/>
       <c r="C168" s="1"/>
@@ -7695,8 +8094,10 @@
       <c r="AJ168" s="1"/>
       <c r="AK168" s="1"/>
       <c r="AL168" s="1"/>
-    </row>
-    <row r="169" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM168" s="1"/>
+      <c r="AN168" s="1"/>
+    </row>
+    <row r="169" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A169" s="1"/>
       <c r="B169" s="1"/>
       <c r="C169" s="1"/>
@@ -7735,8 +8136,10 @@
       <c r="AJ169" s="1"/>
       <c r="AK169" s="1"/>
       <c r="AL169" s="1"/>
-    </row>
-    <row r="170" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM169" s="1"/>
+      <c r="AN169" s="1"/>
+    </row>
+    <row r="170" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A170" s="1"/>
       <c r="B170" s="1"/>
       <c r="C170" s="1"/>
@@ -7775,8 +8178,10 @@
       <c r="AJ170" s="1"/>
       <c r="AK170" s="1"/>
       <c r="AL170" s="1"/>
-    </row>
-    <row r="171" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM170" s="1"/>
+      <c r="AN170" s="1"/>
+    </row>
+    <row r="171" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A171" s="1"/>
       <c r="B171" s="1"/>
       <c r="C171" s="1"/>
@@ -7815,8 +8220,10 @@
       <c r="AJ171" s="1"/>
       <c r="AK171" s="1"/>
       <c r="AL171" s="1"/>
-    </row>
-    <row r="172" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM171" s="1"/>
+      <c r="AN171" s="1"/>
+    </row>
+    <row r="172" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A172" s="1"/>
       <c r="B172" s="1"/>
       <c r="C172" s="1"/>
@@ -7855,8 +8262,10 @@
       <c r="AJ172" s="1"/>
       <c r="AK172" s="1"/>
       <c r="AL172" s="1"/>
-    </row>
-    <row r="173" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM172" s="1"/>
+      <c r="AN172" s="1"/>
+    </row>
+    <row r="173" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A173" s="1"/>
       <c r="B173" s="1"/>
       <c r="C173" s="1"/>
@@ -7895,8 +8304,10 @@
       <c r="AJ173" s="1"/>
       <c r="AK173" s="1"/>
       <c r="AL173" s="1"/>
-    </row>
-    <row r="174" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM173" s="1"/>
+      <c r="AN173" s="1"/>
+    </row>
+    <row r="174" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A174" s="1"/>
       <c r="B174" s="1"/>
       <c r="C174" s="1"/>
@@ -7935,8 +8346,10 @@
       <c r="AJ174" s="1"/>
       <c r="AK174" s="1"/>
       <c r="AL174" s="1"/>
-    </row>
-    <row r="175" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM174" s="1"/>
+      <c r="AN174" s="1"/>
+    </row>
+    <row r="175" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A175" s="1"/>
       <c r="B175" s="1"/>
       <c r="C175" s="1"/>
@@ -7975,8 +8388,10 @@
       <c r="AJ175" s="1"/>
       <c r="AK175" s="1"/>
       <c r="AL175" s="1"/>
-    </row>
-    <row r="176" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM175" s="1"/>
+      <c r="AN175" s="1"/>
+    </row>
+    <row r="176" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A176" s="1"/>
       <c r="B176" s="1"/>
       <c r="C176" s="1"/>
@@ -8015,8 +8430,10 @@
       <c r="AJ176" s="1"/>
       <c r="AK176" s="1"/>
       <c r="AL176" s="1"/>
-    </row>
-    <row r="177" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM176" s="1"/>
+      <c r="AN176" s="1"/>
+    </row>
+    <row r="177" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A177" s="1"/>
       <c r="B177" s="1"/>
       <c r="C177" s="1"/>
@@ -8055,8 +8472,10 @@
       <c r="AJ177" s="1"/>
       <c r="AK177" s="1"/>
       <c r="AL177" s="1"/>
-    </row>
-    <row r="178" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM177" s="1"/>
+      <c r="AN177" s="1"/>
+    </row>
+    <row r="178" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A178" s="1"/>
       <c r="B178" s="1"/>
       <c r="C178" s="1"/>
@@ -8095,8 +8514,10 @@
       <c r="AJ178" s="1"/>
       <c r="AK178" s="1"/>
       <c r="AL178" s="1"/>
-    </row>
-    <row r="179" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM178" s="1"/>
+      <c r="AN178" s="1"/>
+    </row>
+    <row r="179" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A179" s="1"/>
       <c r="B179" s="1"/>
       <c r="C179" s="1"/>
@@ -8135,8 +8556,10 @@
       <c r="AJ179" s="1"/>
       <c r="AK179" s="1"/>
       <c r="AL179" s="1"/>
-    </row>
-    <row r="180" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM179" s="1"/>
+      <c r="AN179" s="1"/>
+    </row>
+    <row r="180" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A180" s="1"/>
       <c r="B180" s="1"/>
       <c r="C180" s="1"/>
@@ -8175,8 +8598,10 @@
       <c r="AJ180" s="1"/>
       <c r="AK180" s="1"/>
       <c r="AL180" s="1"/>
-    </row>
-    <row r="181" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM180" s="1"/>
+      <c r="AN180" s="1"/>
+    </row>
+    <row r="181" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A181" s="1"/>
       <c r="B181" s="1"/>
       <c r="C181" s="1"/>
@@ -8215,8 +8640,10 @@
       <c r="AJ181" s="1"/>
       <c r="AK181" s="1"/>
       <c r="AL181" s="1"/>
-    </row>
-    <row r="182" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM181" s="1"/>
+      <c r="AN181" s="1"/>
+    </row>
+    <row r="182" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A182" s="1"/>
       <c r="B182" s="1"/>
       <c r="C182" s="1"/>
@@ -8255,8 +8682,10 @@
       <c r="AJ182" s="1"/>
       <c r="AK182" s="1"/>
       <c r="AL182" s="1"/>
-    </row>
-    <row r="183" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM182" s="1"/>
+      <c r="AN182" s="1"/>
+    </row>
+    <row r="183" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A183" s="1"/>
       <c r="B183" s="1"/>
       <c r="C183" s="1"/>
@@ -8295,8 +8724,10 @@
       <c r="AJ183" s="1"/>
       <c r="AK183" s="1"/>
       <c r="AL183" s="1"/>
-    </row>
-    <row r="184" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM183" s="1"/>
+      <c r="AN183" s="1"/>
+    </row>
+    <row r="184" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A184" s="1"/>
       <c r="B184" s="1"/>
       <c r="C184" s="1"/>
@@ -8335,8 +8766,10 @@
       <c r="AJ184" s="1"/>
       <c r="AK184" s="1"/>
       <c r="AL184" s="1"/>
-    </row>
-    <row r="185" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM184" s="1"/>
+      <c r="AN184" s="1"/>
+    </row>
+    <row r="185" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A185" s="1"/>
       <c r="B185" s="1"/>
       <c r="C185" s="1"/>
@@ -8375,8 +8808,10 @@
       <c r="AJ185" s="1"/>
       <c r="AK185" s="1"/>
       <c r="AL185" s="1"/>
-    </row>
-    <row r="186" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM185" s="1"/>
+      <c r="AN185" s="1"/>
+    </row>
+    <row r="186" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A186" s="1"/>
       <c r="B186" s="1"/>
       <c r="C186" s="1"/>
@@ -8415,8 +8850,10 @@
       <c r="AJ186" s="1"/>
       <c r="AK186" s="1"/>
       <c r="AL186" s="1"/>
-    </row>
-    <row r="187" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM186" s="1"/>
+      <c r="AN186" s="1"/>
+    </row>
+    <row r="187" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A187" s="1"/>
       <c r="B187" s="1"/>
       <c r="C187" s="1"/>
@@ -8455,8 +8892,10 @@
       <c r="AJ187" s="1"/>
       <c r="AK187" s="1"/>
       <c r="AL187" s="1"/>
-    </row>
-    <row r="188" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM187" s="1"/>
+      <c r="AN187" s="1"/>
+    </row>
+    <row r="188" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A188" s="1"/>
       <c r="B188" s="1"/>
       <c r="C188" s="1"/>
@@ -8495,8 +8934,10 @@
       <c r="AJ188" s="1"/>
       <c r="AK188" s="1"/>
       <c r="AL188" s="1"/>
-    </row>
-    <row r="189" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM188" s="1"/>
+      <c r="AN188" s="1"/>
+    </row>
+    <row r="189" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A189" s="1"/>
       <c r="B189" s="1"/>
       <c r="C189" s="1"/>
@@ -8535,8 +8976,10 @@
       <c r="AJ189" s="1"/>
       <c r="AK189" s="1"/>
       <c r="AL189" s="1"/>
-    </row>
-    <row r="190" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM189" s="1"/>
+      <c r="AN189" s="1"/>
+    </row>
+    <row r="190" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A190" s="1"/>
       <c r="B190" s="1"/>
       <c r="C190" s="1"/>
@@ -8575,8 +9018,10 @@
       <c r="AJ190" s="1"/>
       <c r="AK190" s="1"/>
       <c r="AL190" s="1"/>
-    </row>
-    <row r="191" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM190" s="1"/>
+      <c r="AN190" s="1"/>
+    </row>
+    <row r="191" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A191" s="1"/>
       <c r="B191" s="1"/>
       <c r="C191" s="1"/>
@@ -8615,8 +9060,10 @@
       <c r="AJ191" s="1"/>
       <c r="AK191" s="1"/>
       <c r="AL191" s="1"/>
-    </row>
-    <row r="192" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM191" s="1"/>
+      <c r="AN191" s="1"/>
+    </row>
+    <row r="192" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A192" s="1"/>
       <c r="B192" s="1"/>
       <c r="C192" s="1"/>
@@ -8655,8 +9102,10 @@
       <c r="AJ192" s="1"/>
       <c r="AK192" s="1"/>
       <c r="AL192" s="1"/>
-    </row>
-    <row r="193" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM192" s="1"/>
+      <c r="AN192" s="1"/>
+    </row>
+    <row r="193" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A193" s="1"/>
       <c r="B193" s="1"/>
       <c r="C193" s="1"/>
@@ -8695,8 +9144,10 @@
       <c r="AJ193" s="1"/>
       <c r="AK193" s="1"/>
       <c r="AL193" s="1"/>
-    </row>
-    <row r="194" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM193" s="1"/>
+      <c r="AN193" s="1"/>
+    </row>
+    <row r="194" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A194" s="1"/>
       <c r="B194" s="1"/>
       <c r="C194" s="1"/>
@@ -8735,8 +9186,10 @@
       <c r="AJ194" s="1"/>
       <c r="AK194" s="1"/>
       <c r="AL194" s="1"/>
-    </row>
-    <row r="195" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM194" s="1"/>
+      <c r="AN194" s="1"/>
+    </row>
+    <row r="195" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A195" s="1"/>
       <c r="B195" s="1"/>
       <c r="C195" s="1"/>
@@ -8775,8 +9228,10 @@
       <c r="AJ195" s="1"/>
       <c r="AK195" s="1"/>
       <c r="AL195" s="1"/>
-    </row>
-    <row r="196" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM195" s="1"/>
+      <c r="AN195" s="1"/>
+    </row>
+    <row r="196" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A196" s="1"/>
       <c r="B196" s="1"/>
       <c r="C196" s="1"/>
@@ -8815,8 +9270,10 @@
       <c r="AJ196" s="1"/>
       <c r="AK196" s="1"/>
       <c r="AL196" s="1"/>
-    </row>
-    <row r="197" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM196" s="1"/>
+      <c r="AN196" s="1"/>
+    </row>
+    <row r="197" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A197" s="1"/>
       <c r="B197" s="1"/>
       <c r="C197" s="1"/>
@@ -8855,8 +9312,10 @@
       <c r="AJ197" s="1"/>
       <c r="AK197" s="1"/>
       <c r="AL197" s="1"/>
-    </row>
-    <row r="198" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM197" s="1"/>
+      <c r="AN197" s="1"/>
+    </row>
+    <row r="198" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A198" s="1"/>
       <c r="B198" s="1"/>
       <c r="C198" s="1"/>
@@ -8895,8 +9354,10 @@
       <c r="AJ198" s="1"/>
       <c r="AK198" s="1"/>
       <c r="AL198" s="1"/>
-    </row>
-    <row r="199" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM198" s="1"/>
+      <c r="AN198" s="1"/>
+    </row>
+    <row r="199" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A199" s="1"/>
       <c r="B199" s="1"/>
       <c r="C199" s="1"/>
@@ -8935,8 +9396,10 @@
       <c r="AJ199" s="1"/>
       <c r="AK199" s="1"/>
       <c r="AL199" s="1"/>
-    </row>
-    <row r="200" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM199" s="1"/>
+      <c r="AN199" s="1"/>
+    </row>
+    <row r="200" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A200" s="1"/>
       <c r="B200" s="1"/>
       <c r="C200" s="1"/>
@@ -8975,8 +9438,10 @@
       <c r="AJ200" s="1"/>
       <c r="AK200" s="1"/>
       <c r="AL200" s="1"/>
-    </row>
-    <row r="201" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM200" s="1"/>
+      <c r="AN200" s="1"/>
+    </row>
+    <row r="201" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A201" s="1"/>
       <c r="B201" s="1"/>
       <c r="C201" s="1"/>
@@ -9015,8 +9480,10 @@
       <c r="AJ201" s="1"/>
       <c r="AK201" s="1"/>
       <c r="AL201" s="1"/>
-    </row>
-    <row r="202" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM201" s="1"/>
+      <c r="AN201" s="1"/>
+    </row>
+    <row r="202" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A202" s="1"/>
       <c r="B202" s="1"/>
       <c r="C202" s="1"/>
@@ -9055,8 +9522,10 @@
       <c r="AJ202" s="1"/>
       <c r="AK202" s="1"/>
       <c r="AL202" s="1"/>
-    </row>
-    <row r="203" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM202" s="1"/>
+      <c r="AN202" s="1"/>
+    </row>
+    <row r="203" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A203" s="1"/>
       <c r="B203" s="1"/>
       <c r="C203" s="1"/>
@@ -9095,8 +9564,10 @@
       <c r="AJ203" s="1"/>
       <c r="AK203" s="1"/>
       <c r="AL203" s="1"/>
-    </row>
-    <row r="204" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM203" s="1"/>
+      <c r="AN203" s="1"/>
+    </row>
+    <row r="204" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A204" s="1"/>
       <c r="B204" s="1"/>
       <c r="C204" s="1"/>
@@ -9135,8 +9606,10 @@
       <c r="AJ204" s="1"/>
       <c r="AK204" s="1"/>
       <c r="AL204" s="1"/>
-    </row>
-    <row r="205" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM204" s="1"/>
+      <c r="AN204" s="1"/>
+    </row>
+    <row r="205" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A205" s="1"/>
       <c r="B205" s="1"/>
       <c r="C205" s="1"/>
@@ -9175,8 +9648,10 @@
       <c r="AJ205" s="1"/>
       <c r="AK205" s="1"/>
       <c r="AL205" s="1"/>
-    </row>
-    <row r="206" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM205" s="1"/>
+      <c r="AN205" s="1"/>
+    </row>
+    <row r="206" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A206" s="1"/>
       <c r="B206" s="1"/>
       <c r="C206" s="1"/>
@@ -9215,8 +9690,10 @@
       <c r="AJ206" s="1"/>
       <c r="AK206" s="1"/>
       <c r="AL206" s="1"/>
-    </row>
-    <row r="207" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM206" s="1"/>
+      <c r="AN206" s="1"/>
+    </row>
+    <row r="207" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A207" s="1"/>
       <c r="B207" s="1"/>
       <c r="C207" s="1"/>
@@ -9255,8 +9732,10 @@
       <c r="AJ207" s="1"/>
       <c r="AK207" s="1"/>
       <c r="AL207" s="1"/>
-    </row>
-    <row r="208" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM207" s="1"/>
+      <c r="AN207" s="1"/>
+    </row>
+    <row r="208" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A208" s="1"/>
       <c r="B208" s="1"/>
       <c r="C208" s="1"/>
@@ -9295,8 +9774,10 @@
       <c r="AJ208" s="1"/>
       <c r="AK208" s="1"/>
       <c r="AL208" s="1"/>
-    </row>
-    <row r="209" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM208" s="1"/>
+      <c r="AN208" s="1"/>
+    </row>
+    <row r="209" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A209" s="1"/>
       <c r="B209" s="1"/>
       <c r="C209" s="1"/>
@@ -9335,8 +9816,10 @@
       <c r="AJ209" s="1"/>
       <c r="AK209" s="1"/>
       <c r="AL209" s="1"/>
-    </row>
-    <row r="210" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM209" s="1"/>
+      <c r="AN209" s="1"/>
+    </row>
+    <row r="210" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A210" s="1"/>
       <c r="B210" s="1"/>
       <c r="C210" s="1"/>
@@ -9375,8 +9858,10 @@
       <c r="AJ210" s="1"/>
       <c r="AK210" s="1"/>
       <c r="AL210" s="1"/>
-    </row>
-    <row r="211" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM210" s="1"/>
+      <c r="AN210" s="1"/>
+    </row>
+    <row r="211" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A211" s="1"/>
       <c r="B211" s="1"/>
       <c r="C211" s="1"/>
@@ -9415,8 +9900,10 @@
       <c r="AJ211" s="1"/>
       <c r="AK211" s="1"/>
       <c r="AL211" s="1"/>
-    </row>
-    <row r="212" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM211" s="1"/>
+      <c r="AN211" s="1"/>
+    </row>
+    <row r="212" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A212" s="1"/>
       <c r="B212" s="1"/>
       <c r="C212" s="1"/>
@@ -9455,8 +9942,10 @@
       <c r="AJ212" s="1"/>
       <c r="AK212" s="1"/>
       <c r="AL212" s="1"/>
-    </row>
-    <row r="213" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM212" s="1"/>
+      <c r="AN212" s="1"/>
+    </row>
+    <row r="213" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A213" s="1"/>
       <c r="B213" s="1"/>
       <c r="C213" s="1"/>
@@ -9495,8 +9984,10 @@
       <c r="AJ213" s="1"/>
       <c r="AK213" s="1"/>
       <c r="AL213" s="1"/>
-    </row>
-    <row r="214" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM213" s="1"/>
+      <c r="AN213" s="1"/>
+    </row>
+    <row r="214" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A214" s="1"/>
       <c r="B214" s="1"/>
       <c r="C214" s="1"/>
@@ -9535,8 +10026,10 @@
       <c r="AJ214" s="1"/>
       <c r="AK214" s="1"/>
       <c r="AL214" s="1"/>
-    </row>
-    <row r="215" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM214" s="1"/>
+      <c r="AN214" s="1"/>
+    </row>
+    <row r="215" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A215" s="1"/>
       <c r="B215" s="1"/>
       <c r="C215" s="1"/>
@@ -9575,8 +10068,10 @@
       <c r="AJ215" s="1"/>
       <c r="AK215" s="1"/>
       <c r="AL215" s="1"/>
-    </row>
-    <row r="216" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM215" s="1"/>
+      <c r="AN215" s="1"/>
+    </row>
+    <row r="216" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A216" s="1"/>
       <c r="B216" s="1"/>
       <c r="C216" s="1"/>
@@ -9615,8 +10110,10 @@
       <c r="AJ216" s="1"/>
       <c r="AK216" s="1"/>
       <c r="AL216" s="1"/>
-    </row>
-    <row r="217" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM216" s="1"/>
+      <c r="AN216" s="1"/>
+    </row>
+    <row r="217" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A217" s="1"/>
       <c r="B217" s="1"/>
       <c r="C217" s="1"/>
@@ -9655,8 +10152,10 @@
       <c r="AJ217" s="1"/>
       <c r="AK217" s="1"/>
       <c r="AL217" s="1"/>
-    </row>
-    <row r="218" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM217" s="1"/>
+      <c r="AN217" s="1"/>
+    </row>
+    <row r="218" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A218" s="1"/>
       <c r="B218" s="1"/>
       <c r="C218" s="1"/>
@@ -9695,8 +10194,10 @@
       <c r="AJ218" s="1"/>
       <c r="AK218" s="1"/>
       <c r="AL218" s="1"/>
-    </row>
-    <row r="219" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM218" s="1"/>
+      <c r="AN218" s="1"/>
+    </row>
+    <row r="219" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A219" s="1"/>
       <c r="B219" s="1"/>
       <c r="C219" s="1"/>
@@ -9735,8 +10236,10 @@
       <c r="AJ219" s="1"/>
       <c r="AK219" s="1"/>
       <c r="AL219" s="1"/>
-    </row>
-    <row r="220" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM219" s="1"/>
+      <c r="AN219" s="1"/>
+    </row>
+    <row r="220" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A220" s="1"/>
       <c r="B220" s="1"/>
       <c r="C220" s="1"/>
@@ -9775,8 +10278,10 @@
       <c r="AJ220" s="1"/>
       <c r="AK220" s="1"/>
       <c r="AL220" s="1"/>
-    </row>
-    <row r="221" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM220" s="1"/>
+      <c r="AN220" s="1"/>
+    </row>
+    <row r="221" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A221" s="1"/>
       <c r="B221" s="1"/>
       <c r="C221" s="1"/>
@@ -9815,8 +10320,10 @@
       <c r="AJ221" s="1"/>
       <c r="AK221" s="1"/>
       <c r="AL221" s="1"/>
-    </row>
-    <row r="222" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM221" s="1"/>
+      <c r="AN221" s="1"/>
+    </row>
+    <row r="222" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A222" s="1"/>
       <c r="B222" s="1"/>
       <c r="C222" s="1"/>
@@ -9855,8 +10362,10 @@
       <c r="AJ222" s="1"/>
       <c r="AK222" s="1"/>
       <c r="AL222" s="1"/>
-    </row>
-    <row r="223" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM222" s="1"/>
+      <c r="AN222" s="1"/>
+    </row>
+    <row r="223" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A223" s="1"/>
       <c r="B223" s="1"/>
       <c r="C223" s="1"/>
@@ -9895,8 +10404,10 @@
       <c r="AJ223" s="1"/>
       <c r="AK223" s="1"/>
       <c r="AL223" s="1"/>
-    </row>
-    <row r="224" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM223" s="1"/>
+      <c r="AN223" s="1"/>
+    </row>
+    <row r="224" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A224" s="1"/>
       <c r="B224" s="1"/>
       <c r="C224" s="1"/>
@@ -9935,8 +10446,10 @@
       <c r="AJ224" s="1"/>
       <c r="AK224" s="1"/>
       <c r="AL224" s="1"/>
-    </row>
-    <row r="225" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM224" s="1"/>
+      <c r="AN224" s="1"/>
+    </row>
+    <row r="225" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A225" s="1"/>
       <c r="B225" s="1"/>
       <c r="C225" s="1"/>
@@ -9975,8 +10488,10 @@
       <c r="AJ225" s="1"/>
       <c r="AK225" s="1"/>
       <c r="AL225" s="1"/>
-    </row>
-    <row r="226" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM225" s="1"/>
+      <c r="AN225" s="1"/>
+    </row>
+    <row r="226" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A226" s="1"/>
       <c r="B226" s="1"/>
       <c r="C226" s="1"/>
@@ -10015,8 +10530,10 @@
       <c r="AJ226" s="1"/>
       <c r="AK226" s="1"/>
       <c r="AL226" s="1"/>
-    </row>
-    <row r="227" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM226" s="1"/>
+      <c r="AN226" s="1"/>
+    </row>
+    <row r="227" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A227" s="1"/>
       <c r="B227" s="1"/>
       <c r="C227" s="1"/>
@@ -10055,8 +10572,10 @@
       <c r="AJ227" s="1"/>
       <c r="AK227" s="1"/>
       <c r="AL227" s="1"/>
-    </row>
-    <row r="228" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM227" s="1"/>
+      <c r="AN227" s="1"/>
+    </row>
+    <row r="228" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A228" s="1"/>
       <c r="B228" s="1"/>
       <c r="C228" s="1"/>
@@ -10095,8 +10614,10 @@
       <c r="AJ228" s="1"/>
       <c r="AK228" s="1"/>
       <c r="AL228" s="1"/>
-    </row>
-    <row r="229" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM228" s="1"/>
+      <c r="AN228" s="1"/>
+    </row>
+    <row r="229" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A229" s="1"/>
       <c r="B229" s="1"/>
       <c r="C229" s="1"/>
@@ -10135,8 +10656,10 @@
       <c r="AJ229" s="1"/>
       <c r="AK229" s="1"/>
       <c r="AL229" s="1"/>
-    </row>
-    <row r="230" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM229" s="1"/>
+      <c r="AN229" s="1"/>
+    </row>
+    <row r="230" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A230" s="1"/>
       <c r="B230" s="1"/>
       <c r="C230" s="1"/>
@@ -10175,8 +10698,10 @@
       <c r="AJ230" s="1"/>
       <c r="AK230" s="1"/>
       <c r="AL230" s="1"/>
-    </row>
-    <row r="231" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM230" s="1"/>
+      <c r="AN230" s="1"/>
+    </row>
+    <row r="231" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A231" s="1"/>
       <c r="B231" s="1"/>
       <c r="C231" s="1"/>
@@ -10215,8 +10740,10 @@
       <c r="AJ231" s="1"/>
       <c r="AK231" s="1"/>
       <c r="AL231" s="1"/>
-    </row>
-    <row r="232" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM231" s="1"/>
+      <c r="AN231" s="1"/>
+    </row>
+    <row r="232" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A232" s="1"/>
       <c r="B232" s="1"/>
       <c r="C232" s="1"/>
@@ -10255,8 +10782,10 @@
       <c r="AJ232" s="1"/>
       <c r="AK232" s="1"/>
       <c r="AL232" s="1"/>
-    </row>
-    <row r="233" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM232" s="1"/>
+      <c r="AN232" s="1"/>
+    </row>
+    <row r="233" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A233" s="1"/>
       <c r="B233" s="1"/>
       <c r="C233" s="1"/>
@@ -10295,8 +10824,10 @@
       <c r="AJ233" s="1"/>
       <c r="AK233" s="1"/>
       <c r="AL233" s="1"/>
-    </row>
-    <row r="234" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM233" s="1"/>
+      <c r="AN233" s="1"/>
+    </row>
+    <row r="234" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A234" s="1"/>
       <c r="B234" s="1"/>
       <c r="C234" s="1"/>
@@ -10335,8 +10866,10 @@
       <c r="AJ234" s="1"/>
       <c r="AK234" s="1"/>
       <c r="AL234" s="1"/>
-    </row>
-    <row r="235" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM234" s="1"/>
+      <c r="AN234" s="1"/>
+    </row>
+    <row r="235" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A235" s="1"/>
       <c r="B235" s="1"/>
       <c r="C235" s="1"/>
@@ -10375,8 +10908,10 @@
       <c r="AJ235" s="1"/>
       <c r="AK235" s="1"/>
       <c r="AL235" s="1"/>
-    </row>
-    <row r="236" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM235" s="1"/>
+      <c r="AN235" s="1"/>
+    </row>
+    <row r="236" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A236" s="1"/>
       <c r="B236" s="1"/>
       <c r="C236" s="1"/>
@@ -10415,8 +10950,10 @@
       <c r="AJ236" s="1"/>
       <c r="AK236" s="1"/>
       <c r="AL236" s="1"/>
-    </row>
-    <row r="237" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM236" s="1"/>
+      <c r="AN236" s="1"/>
+    </row>
+    <row r="237" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A237" s="1"/>
       <c r="B237" s="1"/>
       <c r="C237" s="1"/>
@@ -10455,8 +10992,10 @@
       <c r="AJ237" s="1"/>
       <c r="AK237" s="1"/>
       <c r="AL237" s="1"/>
-    </row>
-    <row r="238" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM237" s="1"/>
+      <c r="AN237" s="1"/>
+    </row>
+    <row r="238" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A238" s="1"/>
       <c r="B238" s="1"/>
       <c r="C238" s="1"/>
@@ -10495,8 +11034,10 @@
       <c r="AJ238" s="1"/>
       <c r="AK238" s="1"/>
       <c r="AL238" s="1"/>
-    </row>
-    <row r="239" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM238" s="1"/>
+      <c r="AN238" s="1"/>
+    </row>
+    <row r="239" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A239" s="1"/>
       <c r="B239" s="1"/>
       <c r="C239" s="1"/>
@@ -10535,8 +11076,10 @@
       <c r="AJ239" s="1"/>
       <c r="AK239" s="1"/>
       <c r="AL239" s="1"/>
-    </row>
-    <row r="240" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM239" s="1"/>
+      <c r="AN239" s="1"/>
+    </row>
+    <row r="240" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A240" s="1"/>
       <c r="B240" s="1"/>
       <c r="C240" s="1"/>
@@ -10575,8 +11118,10 @@
       <c r="AJ240" s="1"/>
       <c r="AK240" s="1"/>
       <c r="AL240" s="1"/>
-    </row>
-    <row r="241" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM240" s="1"/>
+      <c r="AN240" s="1"/>
+    </row>
+    <row r="241" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A241" s="1"/>
       <c r="B241" s="1"/>
       <c r="C241" s="1"/>
@@ -10615,8 +11160,10 @@
       <c r="AJ241" s="1"/>
       <c r="AK241" s="1"/>
       <c r="AL241" s="1"/>
-    </row>
-    <row r="242" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM241" s="1"/>
+      <c r="AN241" s="1"/>
+    </row>
+    <row r="242" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A242" s="1"/>
       <c r="B242" s="1"/>
       <c r="C242" s="1"/>
@@ -10655,8 +11202,10 @@
       <c r="AJ242" s="1"/>
       <c r="AK242" s="1"/>
       <c r="AL242" s="1"/>
-    </row>
-    <row r="243" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM242" s="1"/>
+      <c r="AN242" s="1"/>
+    </row>
+    <row r="243" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A243" s="1"/>
       <c r="B243" s="1"/>
       <c r="C243" s="1"/>
@@ -10695,8 +11244,10 @@
       <c r="AJ243" s="1"/>
       <c r="AK243" s="1"/>
       <c r="AL243" s="1"/>
-    </row>
-    <row r="244" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM243" s="1"/>
+      <c r="AN243" s="1"/>
+    </row>
+    <row r="244" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A244" s="1"/>
       <c r="B244" s="1"/>
       <c r="C244" s="1"/>
@@ -10735,8 +11286,10 @@
       <c r="AJ244" s="1"/>
       <c r="AK244" s="1"/>
       <c r="AL244" s="1"/>
-    </row>
-    <row r="245" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM244" s="1"/>
+      <c r="AN244" s="1"/>
+    </row>
+    <row r="245" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A245" s="1"/>
       <c r="B245" s="1"/>
       <c r="C245" s="1"/>
@@ -10775,8 +11328,10 @@
       <c r="AJ245" s="1"/>
       <c r="AK245" s="1"/>
       <c r="AL245" s="1"/>
-    </row>
-    <row r="246" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM245" s="1"/>
+      <c r="AN245" s="1"/>
+    </row>
+    <row r="246" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A246" s="1"/>
       <c r="B246" s="1"/>
       <c r="C246" s="1"/>
@@ -10815,8 +11370,10 @@
       <c r="AJ246" s="1"/>
       <c r="AK246" s="1"/>
       <c r="AL246" s="1"/>
-    </row>
-    <row r="247" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM246" s="1"/>
+      <c r="AN246" s="1"/>
+    </row>
+    <row r="247" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A247" s="1"/>
       <c r="B247" s="1"/>
       <c r="C247" s="1"/>
@@ -10855,8 +11412,10 @@
       <c r="AJ247" s="1"/>
       <c r="AK247" s="1"/>
       <c r="AL247" s="1"/>
-    </row>
-    <row r="248" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM247" s="1"/>
+      <c r="AN247" s="1"/>
+    </row>
+    <row r="248" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A248" s="1"/>
       <c r="B248" s="1"/>
       <c r="C248" s="1"/>
@@ -10895,8 +11454,10 @@
       <c r="AJ248" s="1"/>
       <c r="AK248" s="1"/>
       <c r="AL248" s="1"/>
-    </row>
-    <row r="249" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM248" s="1"/>
+      <c r="AN248" s="1"/>
+    </row>
+    <row r="249" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A249" s="1"/>
       <c r="B249" s="1"/>
       <c r="C249" s="1"/>
@@ -10935,8 +11496,10 @@
       <c r="AJ249" s="1"/>
       <c r="AK249" s="1"/>
       <c r="AL249" s="1"/>
-    </row>
-    <row r="250" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM249" s="1"/>
+      <c r="AN249" s="1"/>
+    </row>
+    <row r="250" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A250" s="1"/>
       <c r="B250" s="1"/>
       <c r="C250" s="1"/>
@@ -10975,8 +11538,10 @@
       <c r="AJ250" s="1"/>
       <c r="AK250" s="1"/>
       <c r="AL250" s="1"/>
-    </row>
-    <row r="251" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM250" s="1"/>
+      <c r="AN250" s="1"/>
+    </row>
+    <row r="251" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A251" s="1"/>
       <c r="B251" s="1"/>
       <c r="C251" s="1"/>
@@ -11015,8 +11580,10 @@
       <c r="AJ251" s="1"/>
       <c r="AK251" s="1"/>
       <c r="AL251" s="1"/>
-    </row>
-    <row r="252" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM251" s="1"/>
+      <c r="AN251" s="1"/>
+    </row>
+    <row r="252" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A252" s="1"/>
       <c r="B252" s="1"/>
       <c r="C252" s="1"/>
@@ -11055,8 +11622,10 @@
       <c r="AJ252" s="1"/>
       <c r="AK252" s="1"/>
       <c r="AL252" s="1"/>
-    </row>
-    <row r="253" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM252" s="1"/>
+      <c r="AN252" s="1"/>
+    </row>
+    <row r="253" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A253" s="1"/>
       <c r="B253" s="1"/>
       <c r="C253" s="1"/>
@@ -11095,8 +11664,10 @@
       <c r="AJ253" s="1"/>
       <c r="AK253" s="1"/>
       <c r="AL253" s="1"/>
-    </row>
-    <row r="254" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM253" s="1"/>
+      <c r="AN253" s="1"/>
+    </row>
+    <row r="254" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A254" s="1"/>
       <c r="B254" s="1"/>
       <c r="C254" s="1"/>
@@ -11135,8 +11706,10 @@
       <c r="AJ254" s="1"/>
       <c r="AK254" s="1"/>
       <c r="AL254" s="1"/>
-    </row>
-    <row r="255" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM254" s="1"/>
+      <c r="AN254" s="1"/>
+    </row>
+    <row r="255" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A255" s="1"/>
       <c r="B255" s="1"/>
       <c r="C255" s="1"/>
@@ -11175,8 +11748,10 @@
       <c r="AJ255" s="1"/>
       <c r="AK255" s="1"/>
       <c r="AL255" s="1"/>
-    </row>
-    <row r="256" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM255" s="1"/>
+      <c r="AN255" s="1"/>
+    </row>
+    <row r="256" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A256" s="1"/>
       <c r="B256" s="1"/>
       <c r="C256" s="1"/>
@@ -11215,8 +11790,10 @@
       <c r="AJ256" s="1"/>
       <c r="AK256" s="1"/>
       <c r="AL256" s="1"/>
-    </row>
-    <row r="257" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM256" s="1"/>
+      <c r="AN256" s="1"/>
+    </row>
+    <row r="257" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A257" s="1"/>
       <c r="B257" s="1"/>
       <c r="C257" s="1"/>
@@ -11255,8 +11832,10 @@
       <c r="AJ257" s="1"/>
       <c r="AK257" s="1"/>
       <c r="AL257" s="1"/>
-    </row>
-    <row r="258" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM257" s="1"/>
+      <c r="AN257" s="1"/>
+    </row>
+    <row r="258" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A258" s="1"/>
       <c r="B258" s="1"/>
       <c r="C258" s="1"/>
@@ -11295,8 +11874,10 @@
       <c r="AJ258" s="1"/>
       <c r="AK258" s="1"/>
       <c r="AL258" s="1"/>
-    </row>
-    <row r="259" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM258" s="1"/>
+      <c r="AN258" s="1"/>
+    </row>
+    <row r="259" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A259" s="1"/>
       <c r="B259" s="1"/>
       <c r="C259" s="1"/>
@@ -11335,8 +11916,10 @@
       <c r="AJ259" s="1"/>
       <c r="AK259" s="1"/>
       <c r="AL259" s="1"/>
-    </row>
-    <row r="260" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM259" s="1"/>
+      <c r="AN259" s="1"/>
+    </row>
+    <row r="260" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A260" s="1"/>
       <c r="B260" s="1"/>
       <c r="C260" s="1"/>
@@ -11375,8 +11958,10 @@
       <c r="AJ260" s="1"/>
       <c r="AK260" s="1"/>
       <c r="AL260" s="1"/>
-    </row>
-    <row r="261" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM260" s="1"/>
+      <c r="AN260" s="1"/>
+    </row>
+    <row r="261" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A261" s="1"/>
       <c r="B261" s="1"/>
       <c r="C261" s="1"/>
@@ -11415,8 +12000,10 @@
       <c r="AJ261" s="1"/>
       <c r="AK261" s="1"/>
       <c r="AL261" s="1"/>
-    </row>
-    <row r="262" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM261" s="1"/>
+      <c r="AN261" s="1"/>
+    </row>
+    <row r="262" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A262" s="1"/>
       <c r="B262" s="1"/>
       <c r="C262" s="1"/>
@@ -11455,8 +12042,10 @@
       <c r="AJ262" s="1"/>
       <c r="AK262" s="1"/>
       <c r="AL262" s="1"/>
-    </row>
-    <row r="263" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM262" s="1"/>
+      <c r="AN262" s="1"/>
+    </row>
+    <row r="263" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A263" s="1"/>
       <c r="B263" s="1"/>
       <c r="C263" s="1"/>
@@ -11495,8 +12084,10 @@
       <c r="AJ263" s="1"/>
       <c r="AK263" s="1"/>
       <c r="AL263" s="1"/>
-    </row>
-    <row r="264" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM263" s="1"/>
+      <c r="AN263" s="1"/>
+    </row>
+    <row r="264" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A264" s="1"/>
       <c r="B264" s="1"/>
       <c r="C264" s="1"/>
@@ -11535,8 +12126,10 @@
       <c r="AJ264" s="1"/>
       <c r="AK264" s="1"/>
       <c r="AL264" s="1"/>
-    </row>
-    <row r="265" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM264" s="1"/>
+      <c r="AN264" s="1"/>
+    </row>
+    <row r="265" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A265" s="1"/>
       <c r="B265" s="1"/>
       <c r="C265" s="1"/>
@@ -11575,8 +12168,10 @@
       <c r="AJ265" s="1"/>
       <c r="AK265" s="1"/>
       <c r="AL265" s="1"/>
-    </row>
-    <row r="266" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM265" s="1"/>
+      <c r="AN265" s="1"/>
+    </row>
+    <row r="266" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A266" s="1"/>
       <c r="B266" s="1"/>
       <c r="C266" s="1"/>
@@ -11615,8 +12210,10 @@
       <c r="AJ266" s="1"/>
       <c r="AK266" s="1"/>
       <c r="AL266" s="1"/>
-    </row>
-    <row r="267" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM266" s="1"/>
+      <c r="AN266" s="1"/>
+    </row>
+    <row r="267" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A267" s="1"/>
       <c r="B267" s="1"/>
       <c r="C267" s="1"/>
@@ -11655,8 +12252,10 @@
       <c r="AJ267" s="1"/>
       <c r="AK267" s="1"/>
       <c r="AL267" s="1"/>
-    </row>
-    <row r="268" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM267" s="1"/>
+      <c r="AN267" s="1"/>
+    </row>
+    <row r="268" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A268" s="1"/>
       <c r="B268" s="1"/>
       <c r="C268" s="1"/>
@@ -11695,8 +12294,10 @@
       <c r="AJ268" s="1"/>
       <c r="AK268" s="1"/>
       <c r="AL268" s="1"/>
-    </row>
-    <row r="269" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM268" s="1"/>
+      <c r="AN268" s="1"/>
+    </row>
+    <row r="269" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A269" s="1"/>
       <c r="B269" s="1"/>
       <c r="C269" s="1"/>
@@ -11735,8 +12336,10 @@
       <c r="AJ269" s="1"/>
       <c r="AK269" s="1"/>
       <c r="AL269" s="1"/>
-    </row>
-    <row r="270" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM269" s="1"/>
+      <c r="AN269" s="1"/>
+    </row>
+    <row r="270" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A270" s="1"/>
       <c r="B270" s="1"/>
       <c r="C270" s="1"/>
@@ -11775,8 +12378,10 @@
       <c r="AJ270" s="1"/>
       <c r="AK270" s="1"/>
       <c r="AL270" s="1"/>
-    </row>
-    <row r="271" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM270" s="1"/>
+      <c r="AN270" s="1"/>
+    </row>
+    <row r="271" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A271" s="1"/>
       <c r="B271" s="1"/>
       <c r="C271" s="1"/>
@@ -11815,8 +12420,10 @@
       <c r="AJ271" s="1"/>
       <c r="AK271" s="1"/>
       <c r="AL271" s="1"/>
-    </row>
-    <row r="272" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM271" s="1"/>
+      <c r="AN271" s="1"/>
+    </row>
+    <row r="272" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A272" s="1"/>
       <c r="B272" s="1"/>
       <c r="C272" s="1"/>
@@ -11855,8 +12462,10 @@
       <c r="AJ272" s="1"/>
       <c r="AK272" s="1"/>
       <c r="AL272" s="1"/>
-    </row>
-    <row r="273" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM272" s="1"/>
+      <c r="AN272" s="1"/>
+    </row>
+    <row r="273" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A273" s="1"/>
       <c r="B273" s="1"/>
       <c r="C273" s="1"/>
@@ -11895,8 +12504,10 @@
       <c r="AJ273" s="1"/>
       <c r="AK273" s="1"/>
       <c r="AL273" s="1"/>
-    </row>
-    <row r="274" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM273" s="1"/>
+      <c r="AN273" s="1"/>
+    </row>
+    <row r="274" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A274" s="1"/>
       <c r="B274" s="1"/>
       <c r="C274" s="1"/>
@@ -11935,8 +12546,10 @@
       <c r="AJ274" s="1"/>
       <c r="AK274" s="1"/>
       <c r="AL274" s="1"/>
-    </row>
-    <row r="275" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM274" s="1"/>
+      <c r="AN274" s="1"/>
+    </row>
+    <row r="275" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A275" s="1"/>
       <c r="B275" s="1"/>
       <c r="C275" s="1"/>
@@ -11975,8 +12588,10 @@
       <c r="AJ275" s="1"/>
       <c r="AK275" s="1"/>
       <c r="AL275" s="1"/>
-    </row>
-    <row r="276" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM275" s="1"/>
+      <c r="AN275" s="1"/>
+    </row>
+    <row r="276" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A276" s="1"/>
       <c r="B276" s="1"/>
       <c r="C276" s="1"/>
@@ -12015,8 +12630,10 @@
       <c r="AJ276" s="1"/>
       <c r="AK276" s="1"/>
       <c r="AL276" s="1"/>
-    </row>
-    <row r="277" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM276" s="1"/>
+      <c r="AN276" s="1"/>
+    </row>
+    <row r="277" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A277" s="1"/>
       <c r="B277" s="1"/>
       <c r="C277" s="1"/>
@@ -12055,8 +12672,10 @@
       <c r="AJ277" s="1"/>
       <c r="AK277" s="1"/>
       <c r="AL277" s="1"/>
-    </row>
-    <row r="278" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM277" s="1"/>
+      <c r="AN277" s="1"/>
+    </row>
+    <row r="278" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A278" s="1"/>
       <c r="B278" s="1"/>
       <c r="C278" s="1"/>
@@ -12095,8 +12714,10 @@
       <c r="AJ278" s="1"/>
       <c r="AK278" s="1"/>
       <c r="AL278" s="1"/>
-    </row>
-    <row r="279" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM278" s="1"/>
+      <c r="AN278" s="1"/>
+    </row>
+    <row r="279" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A279" s="1"/>
       <c r="B279" s="1"/>
       <c r="C279" s="1"/>
@@ -12135,8 +12756,10 @@
       <c r="AJ279" s="1"/>
       <c r="AK279" s="1"/>
       <c r="AL279" s="1"/>
-    </row>
-    <row r="280" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM279" s="1"/>
+      <c r="AN279" s="1"/>
+    </row>
+    <row r="280" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A280" s="1"/>
       <c r="B280" s="1"/>
       <c r="C280" s="1"/>
@@ -12175,8 +12798,10 @@
       <c r="AJ280" s="1"/>
       <c r="AK280" s="1"/>
       <c r="AL280" s="1"/>
-    </row>
-    <row r="281" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM280" s="1"/>
+      <c r="AN280" s="1"/>
+    </row>
+    <row r="281" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A281" s="1"/>
       <c r="B281" s="1"/>
       <c r="C281" s="1"/>
@@ -12215,8 +12840,10 @@
       <c r="AJ281" s="1"/>
       <c r="AK281" s="1"/>
       <c r="AL281" s="1"/>
-    </row>
-    <row r="282" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM281" s="1"/>
+      <c r="AN281" s="1"/>
+    </row>
+    <row r="282" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A282" s="1"/>
       <c r="B282" s="1"/>
       <c r="C282" s="1"/>
@@ -12255,8 +12882,10 @@
       <c r="AJ282" s="1"/>
       <c r="AK282" s="1"/>
       <c r="AL282" s="1"/>
-    </row>
-    <row r="283" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM282" s="1"/>
+      <c r="AN282" s="1"/>
+    </row>
+    <row r="283" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A283" s="1"/>
       <c r="B283" s="1"/>
       <c r="C283" s="1"/>
@@ -12295,8 +12924,10 @@
       <c r="AJ283" s="1"/>
       <c r="AK283" s="1"/>
       <c r="AL283" s="1"/>
-    </row>
-    <row r="284" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM283" s="1"/>
+      <c r="AN283" s="1"/>
+    </row>
+    <row r="284" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A284" s="1"/>
       <c r="B284" s="1"/>
       <c r="C284" s="1"/>
@@ -12335,8 +12966,10 @@
       <c r="AJ284" s="1"/>
       <c r="AK284" s="1"/>
       <c r="AL284" s="1"/>
-    </row>
-    <row r="285" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM284" s="1"/>
+      <c r="AN284" s="1"/>
+    </row>
+    <row r="285" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A285" s="1"/>
       <c r="B285" s="1"/>
       <c r="C285" s="1"/>
@@ -12375,8 +13008,10 @@
       <c r="AJ285" s="1"/>
       <c r="AK285" s="1"/>
       <c r="AL285" s="1"/>
-    </row>
-    <row r="286" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM285" s="1"/>
+      <c r="AN285" s="1"/>
+    </row>
+    <row r="286" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A286" s="1"/>
       <c r="B286" s="1"/>
       <c r="C286" s="1"/>
@@ -12415,8 +13050,10 @@
       <c r="AJ286" s="1"/>
       <c r="AK286" s="1"/>
       <c r="AL286" s="1"/>
-    </row>
-    <row r="287" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM286" s="1"/>
+      <c r="AN286" s="1"/>
+    </row>
+    <row r="287" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A287" s="1"/>
       <c r="B287" s="1"/>
       <c r="C287" s="1"/>
@@ -12455,8 +13092,10 @@
       <c r="AJ287" s="1"/>
       <c r="AK287" s="1"/>
       <c r="AL287" s="1"/>
-    </row>
-    <row r="288" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM287" s="1"/>
+      <c r="AN287" s="1"/>
+    </row>
+    <row r="288" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A288" s="1"/>
       <c r="B288" s="1"/>
       <c r="C288" s="1"/>
@@ -12495,8 +13134,10 @@
       <c r="AJ288" s="1"/>
       <c r="AK288" s="1"/>
       <c r="AL288" s="1"/>
-    </row>
-    <row r="289" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM288" s="1"/>
+      <c r="AN288" s="1"/>
+    </row>
+    <row r="289" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A289" s="1"/>
       <c r="B289" s="1"/>
       <c r="C289" s="1"/>
@@ -12535,8 +13176,10 @@
       <c r="AJ289" s="1"/>
       <c r="AK289" s="1"/>
       <c r="AL289" s="1"/>
-    </row>
-    <row r="290" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM289" s="1"/>
+      <c r="AN289" s="1"/>
+    </row>
+    <row r="290" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A290" s="1"/>
       <c r="B290" s="1"/>
       <c r="C290" s="1"/>
@@ -12575,8 +13218,10 @@
       <c r="AJ290" s="1"/>
       <c r="AK290" s="1"/>
       <c r="AL290" s="1"/>
-    </row>
-    <row r="291" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM290" s="1"/>
+      <c r="AN290" s="1"/>
+    </row>
+    <row r="291" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A291" s="1"/>
       <c r="B291" s="1"/>
       <c r="C291" s="1"/>
@@ -12615,8 +13260,10 @@
       <c r="AJ291" s="1"/>
       <c r="AK291" s="1"/>
       <c r="AL291" s="1"/>
-    </row>
-    <row r="292" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM291" s="1"/>
+      <c r="AN291" s="1"/>
+    </row>
+    <row r="292" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A292" s="1"/>
       <c r="B292" s="1"/>
       <c r="C292" s="1"/>
@@ -12655,8 +13302,10 @@
       <c r="AJ292" s="1"/>
       <c r="AK292" s="1"/>
       <c r="AL292" s="1"/>
-    </row>
-    <row r="293" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM292" s="1"/>
+      <c r="AN292" s="1"/>
+    </row>
+    <row r="293" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A293" s="1"/>
       <c r="B293" s="1"/>
       <c r="C293" s="1"/>
@@ -12695,8 +13344,10 @@
       <c r="AJ293" s="1"/>
       <c r="AK293" s="1"/>
       <c r="AL293" s="1"/>
-    </row>
-    <row r="294" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM293" s="1"/>
+      <c r="AN293" s="1"/>
+    </row>
+    <row r="294" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A294" s="1"/>
       <c r="B294" s="1"/>
       <c r="C294" s="1"/>
@@ -12735,8 +13386,10 @@
       <c r="AJ294" s="1"/>
       <c r="AK294" s="1"/>
       <c r="AL294" s="1"/>
-    </row>
-    <row r="295" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM294" s="1"/>
+      <c r="AN294" s="1"/>
+    </row>
+    <row r="295" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A295" s="1"/>
       <c r="B295" s="1"/>
       <c r="C295" s="1"/>
@@ -12775,8 +13428,10 @@
       <c r="AJ295" s="1"/>
       <c r="AK295" s="1"/>
       <c r="AL295" s="1"/>
-    </row>
-    <row r="296" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM295" s="1"/>
+      <c r="AN295" s="1"/>
+    </row>
+    <row r="296" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A296" s="1"/>
       <c r="B296" s="1"/>
       <c r="C296" s="1"/>
@@ -12815,8 +13470,10 @@
       <c r="AJ296" s="1"/>
       <c r="AK296" s="1"/>
       <c r="AL296" s="1"/>
-    </row>
-    <row r="297" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM296" s="1"/>
+      <c r="AN296" s="1"/>
+    </row>
+    <row r="297" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A297" s="1"/>
       <c r="B297" s="1"/>
       <c r="C297" s="1"/>
@@ -12855,8 +13512,10 @@
       <c r="AJ297" s="1"/>
       <c r="AK297" s="1"/>
       <c r="AL297" s="1"/>
-    </row>
-    <row r="298" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM297" s="1"/>
+      <c r="AN297" s="1"/>
+    </row>
+    <row r="298" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A298" s="1"/>
       <c r="B298" s="1"/>
       <c r="C298" s="1"/>
@@ -12895,8 +13554,10 @@
       <c r="AJ298" s="1"/>
       <c r="AK298" s="1"/>
       <c r="AL298" s="1"/>
-    </row>
-    <row r="299" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM298" s="1"/>
+      <c r="AN298" s="1"/>
+    </row>
+    <row r="299" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A299" s="1"/>
       <c r="B299" s="1"/>
       <c r="C299" s="1"/>
@@ -12935,8 +13596,10 @@
       <c r="AJ299" s="1"/>
       <c r="AK299" s="1"/>
       <c r="AL299" s="1"/>
-    </row>
-    <row r="300" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM299" s="1"/>
+      <c r="AN299" s="1"/>
+    </row>
+    <row r="300" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A300" s="1"/>
       <c r="B300" s="1"/>
       <c r="C300" s="1"/>
@@ -12975,8 +13638,10 @@
       <c r="AJ300" s="1"/>
       <c r="AK300" s="1"/>
       <c r="AL300" s="1"/>
-    </row>
-    <row r="301" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM300" s="1"/>
+      <c r="AN300" s="1"/>
+    </row>
+    <row r="301" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A301" s="1"/>
       <c r="B301" s="1"/>
       <c r="C301" s="1"/>
@@ -13015,8 +13680,10 @@
       <c r="AJ301" s="1"/>
       <c r="AK301" s="1"/>
       <c r="AL301" s="1"/>
-    </row>
-    <row r="302" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM301" s="1"/>
+      <c r="AN301" s="1"/>
+    </row>
+    <row r="302" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A302" s="1"/>
       <c r="B302" s="1"/>
       <c r="C302" s="1"/>
@@ -13055,8 +13722,10 @@
       <c r="AJ302" s="1"/>
       <c r="AK302" s="1"/>
       <c r="AL302" s="1"/>
-    </row>
-    <row r="303" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM302" s="1"/>
+      <c r="AN302" s="1"/>
+    </row>
+    <row r="303" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A303" s="1"/>
       <c r="B303" s="1"/>
       <c r="C303" s="1"/>
@@ -13095,8 +13764,10 @@
       <c r="AJ303" s="1"/>
       <c r="AK303" s="1"/>
       <c r="AL303" s="1"/>
-    </row>
-    <row r="304" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM303" s="1"/>
+      <c r="AN303" s="1"/>
+    </row>
+    <row r="304" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A304" s="1"/>
       <c r="B304" s="1"/>
       <c r="C304" s="1"/>
@@ -13135,8 +13806,10 @@
       <c r="AJ304" s="1"/>
       <c r="AK304" s="1"/>
       <c r="AL304" s="1"/>
-    </row>
-    <row r="305" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM304" s="1"/>
+      <c r="AN304" s="1"/>
+    </row>
+    <row r="305" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A305" s="1"/>
       <c r="B305" s="1"/>
       <c r="C305" s="1"/>
@@ -13175,8 +13848,10 @@
       <c r="AJ305" s="1"/>
       <c r="AK305" s="1"/>
       <c r="AL305" s="1"/>
-    </row>
-    <row r="306" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM305" s="1"/>
+      <c r="AN305" s="1"/>
+    </row>
+    <row r="306" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A306" s="1"/>
       <c r="B306" s="1"/>
       <c r="C306" s="1"/>
@@ -13215,8 +13890,10 @@
       <c r="AJ306" s="1"/>
       <c r="AK306" s="1"/>
       <c r="AL306" s="1"/>
-    </row>
-    <row r="307" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM306" s="1"/>
+      <c r="AN306" s="1"/>
+    </row>
+    <row r="307" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A307" s="1"/>
       <c r="B307" s="1"/>
       <c r="C307" s="1"/>
@@ -13255,8 +13932,10 @@
       <c r="AJ307" s="1"/>
       <c r="AK307" s="1"/>
       <c r="AL307" s="1"/>
-    </row>
-    <row r="308" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM307" s="1"/>
+      <c r="AN307" s="1"/>
+    </row>
+    <row r="308" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A308" s="1"/>
       <c r="B308" s="1"/>
       <c r="C308" s="1"/>
@@ -13295,8 +13974,10 @@
       <c r="AJ308" s="1"/>
       <c r="AK308" s="1"/>
       <c r="AL308" s="1"/>
-    </row>
-    <row r="309" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM308" s="1"/>
+      <c r="AN308" s="1"/>
+    </row>
+    <row r="309" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A309" s="1"/>
       <c r="B309" s="1"/>
       <c r="C309" s="1"/>
@@ -13335,8 +14016,10 @@
       <c r="AJ309" s="1"/>
       <c r="AK309" s="1"/>
       <c r="AL309" s="1"/>
-    </row>
-    <row r="310" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM309" s="1"/>
+      <c r="AN309" s="1"/>
+    </row>
+    <row r="310" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A310" s="1"/>
       <c r="B310" s="1"/>
       <c r="C310" s="1"/>
@@ -13375,8 +14058,10 @@
       <c r="AJ310" s="1"/>
       <c r="AK310" s="1"/>
       <c r="AL310" s="1"/>
-    </row>
-    <row r="311" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM310" s="1"/>
+      <c r="AN310" s="1"/>
+    </row>
+    <row r="311" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A311" s="1"/>
       <c r="B311" s="1"/>
       <c r="C311" s="1"/>
@@ -13415,8 +14100,10 @@
       <c r="AJ311" s="1"/>
       <c r="AK311" s="1"/>
       <c r="AL311" s="1"/>
-    </row>
-    <row r="312" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM311" s="1"/>
+      <c r="AN311" s="1"/>
+    </row>
+    <row r="312" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A312" s="1"/>
       <c r="B312" s="1"/>
       <c r="C312" s="1"/>
@@ -13455,8 +14142,10 @@
       <c r="AJ312" s="1"/>
       <c r="AK312" s="1"/>
       <c r="AL312" s="1"/>
-    </row>
-    <row r="313" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM312" s="1"/>
+      <c r="AN312" s="1"/>
+    </row>
+    <row r="313" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A313" s="1"/>
       <c r="B313" s="1"/>
       <c r="C313" s="1"/>
@@ -13495,8 +14184,10 @@
       <c r="AJ313" s="1"/>
       <c r="AK313" s="1"/>
       <c r="AL313" s="1"/>
-    </row>
-    <row r="314" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM313" s="1"/>
+      <c r="AN313" s="1"/>
+    </row>
+    <row r="314" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A314" s="1"/>
       <c r="B314" s="1"/>
       <c r="C314" s="1"/>
@@ -13535,8 +14226,10 @@
       <c r="AJ314" s="1"/>
       <c r="AK314" s="1"/>
       <c r="AL314" s="1"/>
-    </row>
-    <row r="315" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM314" s="1"/>
+      <c r="AN314" s="1"/>
+    </row>
+    <row r="315" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A315" s="1"/>
       <c r="B315" s="1"/>
       <c r="C315" s="1"/>
@@ -13575,8 +14268,10 @@
       <c r="AJ315" s="1"/>
       <c r="AK315" s="1"/>
       <c r="AL315" s="1"/>
-    </row>
-    <row r="316" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM315" s="1"/>
+      <c r="AN315" s="1"/>
+    </row>
+    <row r="316" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A316" s="1"/>
       <c r="B316" s="1"/>
       <c r="C316" s="1"/>
@@ -13615,8 +14310,10 @@
       <c r="AJ316" s="1"/>
       <c r="AK316" s="1"/>
       <c r="AL316" s="1"/>
-    </row>
-    <row r="317" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM316" s="1"/>
+      <c r="AN316" s="1"/>
+    </row>
+    <row r="317" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A317" s="1"/>
       <c r="B317" s="1"/>
       <c r="C317" s="1"/>
@@ -13655,8 +14352,10 @@
       <c r="AJ317" s="1"/>
       <c r="AK317" s="1"/>
       <c r="AL317" s="1"/>
-    </row>
-    <row r="318" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM317" s="1"/>
+      <c r="AN317" s="1"/>
+    </row>
+    <row r="318" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A318" s="1"/>
       <c r="B318" s="1"/>
       <c r="C318" s="1"/>
@@ -13695,8 +14394,10 @@
       <c r="AJ318" s="1"/>
       <c r="AK318" s="1"/>
       <c r="AL318" s="1"/>
-    </row>
-    <row r="319" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM318" s="1"/>
+      <c r="AN318" s="1"/>
+    </row>
+    <row r="319" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A319" s="1"/>
       <c r="B319" s="1"/>
       <c r="C319" s="1"/>
@@ -13735,8 +14436,10 @@
       <c r="AJ319" s="1"/>
       <c r="AK319" s="1"/>
       <c r="AL319" s="1"/>
-    </row>
-    <row r="320" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM319" s="1"/>
+      <c r="AN319" s="1"/>
+    </row>
+    <row r="320" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A320" s="1"/>
       <c r="B320" s="1"/>
       <c r="C320" s="1"/>
@@ -13775,8 +14478,10 @@
       <c r="AJ320" s="1"/>
       <c r="AK320" s="1"/>
       <c r="AL320" s="1"/>
-    </row>
-    <row r="321" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM320" s="1"/>
+      <c r="AN320" s="1"/>
+    </row>
+    <row r="321" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A321" s="1"/>
       <c r="B321" s="1"/>
       <c r="C321" s="1"/>
@@ -13815,8 +14520,10 @@
       <c r="AJ321" s="1"/>
       <c r="AK321" s="1"/>
       <c r="AL321" s="1"/>
-    </row>
-    <row r="322" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM321" s="1"/>
+      <c r="AN321" s="1"/>
+    </row>
+    <row r="322" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A322" s="1"/>
       <c r="B322" s="1"/>
       <c r="C322" s="1"/>
@@ -13855,8 +14562,10 @@
       <c r="AJ322" s="1"/>
       <c r="AK322" s="1"/>
       <c r="AL322" s="1"/>
-    </row>
-    <row r="323" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM322" s="1"/>
+      <c r="AN322" s="1"/>
+    </row>
+    <row r="323" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A323" s="1"/>
       <c r="B323" s="1"/>
       <c r="C323" s="1"/>
@@ -13895,8 +14604,10 @@
       <c r="AJ323" s="1"/>
       <c r="AK323" s="1"/>
       <c r="AL323" s="1"/>
-    </row>
-    <row r="324" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM323" s="1"/>
+      <c r="AN323" s="1"/>
+    </row>
+    <row r="324" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A324" s="1"/>
       <c r="B324" s="1"/>
       <c r="C324" s="1"/>
@@ -13935,8 +14646,10 @@
       <c r="AJ324" s="1"/>
       <c r="AK324" s="1"/>
       <c r="AL324" s="1"/>
-    </row>
-    <row r="325" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM324" s="1"/>
+      <c r="AN324" s="1"/>
+    </row>
+    <row r="325" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A325" s="1"/>
       <c r="B325" s="1"/>
       <c r="C325" s="1"/>
@@ -13975,8 +14688,10 @@
       <c r="AJ325" s="1"/>
       <c r="AK325" s="1"/>
       <c r="AL325" s="1"/>
-    </row>
-    <row r="326" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM325" s="1"/>
+      <c r="AN325" s="1"/>
+    </row>
+    <row r="326" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A326" s="1"/>
       <c r="B326" s="1"/>
       <c r="C326" s="1"/>
@@ -14015,8 +14730,10 @@
       <c r="AJ326" s="1"/>
       <c r="AK326" s="1"/>
       <c r="AL326" s="1"/>
-    </row>
-    <row r="327" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM326" s="1"/>
+      <c r="AN326" s="1"/>
+    </row>
+    <row r="327" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A327" s="1"/>
       <c r="B327" s="1"/>
       <c r="C327" s="1"/>
@@ -14055,8 +14772,10 @@
       <c r="AJ327" s="1"/>
       <c r="AK327" s="1"/>
       <c r="AL327" s="1"/>
-    </row>
-    <row r="328" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM327" s="1"/>
+      <c r="AN327" s="1"/>
+    </row>
+    <row r="328" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A328" s="1"/>
       <c r="B328" s="1"/>
       <c r="C328" s="1"/>
@@ -14095,8 +14814,10 @@
       <c r="AJ328" s="1"/>
       <c r="AK328" s="1"/>
       <c r="AL328" s="1"/>
-    </row>
-    <row r="329" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM328" s="1"/>
+      <c r="AN328" s="1"/>
+    </row>
+    <row r="329" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A329" s="1"/>
       <c r="B329" s="1"/>
       <c r="C329" s="1"/>
@@ -14135,8 +14856,10 @@
       <c r="AJ329" s="1"/>
       <c r="AK329" s="1"/>
       <c r="AL329" s="1"/>
-    </row>
-    <row r="330" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM329" s="1"/>
+      <c r="AN329" s="1"/>
+    </row>
+    <row r="330" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A330" s="1"/>
       <c r="B330" s="1"/>
       <c r="C330" s="1"/>
@@ -14175,8 +14898,10 @@
       <c r="AJ330" s="1"/>
       <c r="AK330" s="1"/>
       <c r="AL330" s="1"/>
-    </row>
-    <row r="331" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM330" s="1"/>
+      <c r="AN330" s="1"/>
+    </row>
+    <row r="331" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A331" s="1"/>
       <c r="B331" s="1"/>
       <c r="C331" s="1"/>
@@ -14215,8 +14940,10 @@
       <c r="AJ331" s="1"/>
       <c r="AK331" s="1"/>
       <c r="AL331" s="1"/>
-    </row>
-    <row r="332" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM331" s="1"/>
+      <c r="AN331" s="1"/>
+    </row>
+    <row r="332" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A332" s="1"/>
       <c r="B332" s="1"/>
       <c r="C332" s="1"/>
@@ -14255,8 +14982,10 @@
       <c r="AJ332" s="1"/>
       <c r="AK332" s="1"/>
       <c r="AL332" s="1"/>
-    </row>
-    <row r="333" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM332" s="1"/>
+      <c r="AN332" s="1"/>
+    </row>
+    <row r="333" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A333" s="1"/>
       <c r="B333" s="1"/>
       <c r="C333" s="1"/>
@@ -14295,8 +15024,10 @@
       <c r="AJ333" s="1"/>
       <c r="AK333" s="1"/>
       <c r="AL333" s="1"/>
-    </row>
-    <row r="334" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM333" s="1"/>
+      <c r="AN333" s="1"/>
+    </row>
+    <row r="334" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A334" s="1"/>
       <c r="B334" s="1"/>
       <c r="C334" s="1"/>
@@ -14335,8 +15066,10 @@
       <c r="AJ334" s="1"/>
       <c r="AK334" s="1"/>
       <c r="AL334" s="1"/>
-    </row>
-    <row r="335" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM334" s="1"/>
+      <c r="AN334" s="1"/>
+    </row>
+    <row r="335" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A335" s="1"/>
       <c r="B335" s="1"/>
       <c r="C335" s="1"/>
@@ -14375,8 +15108,10 @@
       <c r="AJ335" s="1"/>
       <c r="AK335" s="1"/>
       <c r="AL335" s="1"/>
-    </row>
-    <row r="336" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM335" s="1"/>
+      <c r="AN335" s="1"/>
+    </row>
+    <row r="336" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A336" s="1"/>
       <c r="B336" s="1"/>
       <c r="C336" s="1"/>
@@ -14415,8 +15150,10 @@
       <c r="AJ336" s="1"/>
       <c r="AK336" s="1"/>
       <c r="AL336" s="1"/>
-    </row>
-    <row r="337" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM336" s="1"/>
+      <c r="AN336" s="1"/>
+    </row>
+    <row r="337" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A337" s="1"/>
       <c r="B337" s="1"/>
       <c r="C337" s="1"/>
@@ -14455,8 +15192,10 @@
       <c r="AJ337" s="1"/>
       <c r="AK337" s="1"/>
       <c r="AL337" s="1"/>
-    </row>
-    <row r="338" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM337" s="1"/>
+      <c r="AN337" s="1"/>
+    </row>
+    <row r="338" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A338" s="1"/>
       <c r="B338" s="1"/>
       <c r="C338" s="1"/>
@@ -14495,8 +15234,10 @@
       <c r="AJ338" s="1"/>
       <c r="AK338" s="1"/>
       <c r="AL338" s="1"/>
-    </row>
-    <row r="339" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM338" s="1"/>
+      <c r="AN338" s="1"/>
+    </row>
+    <row r="339" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A339" s="1"/>
       <c r="B339" s="1"/>
       <c r="C339" s="1"/>
@@ -14535,8 +15276,10 @@
       <c r="AJ339" s="1"/>
       <c r="AK339" s="1"/>
       <c r="AL339" s="1"/>
-    </row>
-    <row r="340" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM339" s="1"/>
+      <c r="AN339" s="1"/>
+    </row>
+    <row r="340" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A340" s="1"/>
       <c r="B340" s="1"/>
       <c r="C340" s="1"/>
@@ -14575,8 +15318,10 @@
       <c r="AJ340" s="1"/>
       <c r="AK340" s="1"/>
       <c r="AL340" s="1"/>
-    </row>
-    <row r="341" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM340" s="1"/>
+      <c r="AN340" s="1"/>
+    </row>
+    <row r="341" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A341" s="1"/>
       <c r="B341" s="1"/>
       <c r="C341" s="1"/>
@@ -14615,8 +15360,10 @@
       <c r="AJ341" s="1"/>
       <c r="AK341" s="1"/>
       <c r="AL341" s="1"/>
-    </row>
-    <row r="342" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM341" s="1"/>
+      <c r="AN341" s="1"/>
+    </row>
+    <row r="342" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A342" s="1"/>
       <c r="B342" s="1"/>
       <c r="C342" s="1"/>
@@ -14655,8 +15402,10 @@
       <c r="AJ342" s="1"/>
       <c r="AK342" s="1"/>
       <c r="AL342" s="1"/>
-    </row>
-    <row r="343" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM342" s="1"/>
+      <c r="AN342" s="1"/>
+    </row>
+    <row r="343" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A343" s="1"/>
       <c r="B343" s="1"/>
       <c r="C343" s="1"/>
@@ -14695,8 +15444,10 @@
       <c r="AJ343" s="1"/>
       <c r="AK343" s="1"/>
       <c r="AL343" s="1"/>
-    </row>
-    <row r="344" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM343" s="1"/>
+      <c r="AN343" s="1"/>
+    </row>
+    <row r="344" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A344" s="1"/>
       <c r="B344" s="1"/>
       <c r="C344" s="1"/>
@@ -14735,8 +15486,10 @@
       <c r="AJ344" s="1"/>
       <c r="AK344" s="1"/>
       <c r="AL344" s="1"/>
-    </row>
-    <row r="345" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM344" s="1"/>
+      <c r="AN344" s="1"/>
+    </row>
+    <row r="345" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A345" s="1"/>
       <c r="B345" s="1"/>
       <c r="C345" s="1"/>
@@ -14775,8 +15528,10 @@
       <c r="AJ345" s="1"/>
       <c r="AK345" s="1"/>
       <c r="AL345" s="1"/>
-    </row>
-    <row r="346" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM345" s="1"/>
+      <c r="AN345" s="1"/>
+    </row>
+    <row r="346" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A346" s="1"/>
       <c r="B346" s="1"/>
       <c r="C346" s="1"/>
@@ -14815,8 +15570,10 @@
       <c r="AJ346" s="1"/>
       <c r="AK346" s="1"/>
       <c r="AL346" s="1"/>
-    </row>
-    <row r="347" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM346" s="1"/>
+      <c r="AN346" s="1"/>
+    </row>
+    <row r="347" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A347" s="1"/>
       <c r="B347" s="1"/>
       <c r="C347" s="1"/>
@@ -14855,8 +15612,10 @@
       <c r="AJ347" s="1"/>
       <c r="AK347" s="1"/>
       <c r="AL347" s="1"/>
-    </row>
-    <row r="348" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM347" s="1"/>
+      <c r="AN347" s="1"/>
+    </row>
+    <row r="348" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A348" s="1"/>
       <c r="B348" s="1"/>
       <c r="C348" s="1"/>
@@ -14895,8 +15654,10 @@
       <c r="AJ348" s="1"/>
       <c r="AK348" s="1"/>
       <c r="AL348" s="1"/>
-    </row>
-    <row r="349" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM348" s="1"/>
+      <c r="AN348" s="1"/>
+    </row>
+    <row r="349" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A349" s="1"/>
       <c r="B349" s="1"/>
       <c r="C349" s="1"/>
@@ -14935,8 +15696,10 @@
       <c r="AJ349" s="1"/>
       <c r="AK349" s="1"/>
       <c r="AL349" s="1"/>
-    </row>
-    <row r="350" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM349" s="1"/>
+      <c r="AN349" s="1"/>
+    </row>
+    <row r="350" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A350" s="1"/>
       <c r="B350" s="1"/>
       <c r="C350" s="1"/>
@@ -14975,8 +15738,10 @@
       <c r="AJ350" s="1"/>
       <c r="AK350" s="1"/>
       <c r="AL350" s="1"/>
-    </row>
-    <row r="351" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM350" s="1"/>
+      <c r="AN350" s="1"/>
+    </row>
+    <row r="351" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A351" s="1"/>
       <c r="B351" s="1"/>
       <c r="C351" s="1"/>
@@ -15015,8 +15780,10 @@
       <c r="AJ351" s="1"/>
       <c r="AK351" s="1"/>
       <c r="AL351" s="1"/>
-    </row>
-    <row r="352" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM351" s="1"/>
+      <c r="AN351" s="1"/>
+    </row>
+    <row r="352" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A352" s="1"/>
       <c r="B352" s="1"/>
       <c r="C352" s="1"/>
@@ -15055,8 +15822,10 @@
       <c r="AJ352" s="1"/>
       <c r="AK352" s="1"/>
       <c r="AL352" s="1"/>
-    </row>
-    <row r="353" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM352" s="1"/>
+      <c r="AN352" s="1"/>
+    </row>
+    <row r="353" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A353" s="1"/>
       <c r="B353" s="1"/>
       <c r="C353" s="1"/>
@@ -15095,8 +15864,10 @@
       <c r="AJ353" s="1"/>
       <c r="AK353" s="1"/>
       <c r="AL353" s="1"/>
-    </row>
-    <row r="354" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM353" s="1"/>
+      <c r="AN353" s="1"/>
+    </row>
+    <row r="354" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A354" s="1"/>
       <c r="B354" s="1"/>
       <c r="C354" s="1"/>
@@ -15135,8 +15906,10 @@
       <c r="AJ354" s="1"/>
       <c r="AK354" s="1"/>
       <c r="AL354" s="1"/>
-    </row>
-    <row r="355" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM354" s="1"/>
+      <c r="AN354" s="1"/>
+    </row>
+    <row r="355" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A355" s="1"/>
       <c r="B355" s="1"/>
       <c r="C355" s="1"/>
@@ -15175,8 +15948,10 @@
       <c r="AJ355" s="1"/>
       <c r="AK355" s="1"/>
       <c r="AL355" s="1"/>
-    </row>
-    <row r="356" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM355" s="1"/>
+      <c r="AN355" s="1"/>
+    </row>
+    <row r="356" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A356" s="1"/>
       <c r="B356" s="1"/>
       <c r="C356" s="1"/>
@@ -15215,8 +15990,10 @@
       <c r="AJ356" s="1"/>
       <c r="AK356" s="1"/>
       <c r="AL356" s="1"/>
-    </row>
-    <row r="357" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM356" s="1"/>
+      <c r="AN356" s="1"/>
+    </row>
+    <row r="357" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A357" s="1"/>
       <c r="B357" s="1"/>
       <c r="C357" s="1"/>
@@ -15255,8 +16032,10 @@
       <c r="AJ357" s="1"/>
       <c r="AK357" s="1"/>
       <c r="AL357" s="1"/>
-    </row>
-    <row r="358" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM357" s="1"/>
+      <c r="AN357" s="1"/>
+    </row>
+    <row r="358" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A358" s="1"/>
       <c r="B358" s="1"/>
       <c r="C358" s="1"/>
@@ -15295,8 +16074,10 @@
       <c r="AJ358" s="1"/>
       <c r="AK358" s="1"/>
       <c r="AL358" s="1"/>
-    </row>
-    <row r="359" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM358" s="1"/>
+      <c r="AN358" s="1"/>
+    </row>
+    <row r="359" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A359" s="1"/>
       <c r="B359" s="1"/>
       <c r="C359" s="1"/>
@@ -15335,8 +16116,10 @@
       <c r="AJ359" s="1"/>
       <c r="AK359" s="1"/>
       <c r="AL359" s="1"/>
-    </row>
-    <row r="360" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM359" s="1"/>
+      <c r="AN359" s="1"/>
+    </row>
+    <row r="360" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A360" s="1"/>
       <c r="B360" s="1"/>
       <c r="C360" s="1"/>
@@ -15375,8 +16158,10 @@
       <c r="AJ360" s="1"/>
       <c r="AK360" s="1"/>
       <c r="AL360" s="1"/>
-    </row>
-    <row r="361" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM360" s="1"/>
+      <c r="AN360" s="1"/>
+    </row>
+    <row r="361" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A361" s="1"/>
       <c r="B361" s="1"/>
       <c r="C361" s="1"/>
@@ -15415,8 +16200,10 @@
       <c r="AJ361" s="1"/>
       <c r="AK361" s="1"/>
       <c r="AL361" s="1"/>
-    </row>
-    <row r="362" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM361" s="1"/>
+      <c r="AN361" s="1"/>
+    </row>
+    <row r="362" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A362" s="1"/>
       <c r="B362" s="1"/>
       <c r="C362" s="1"/>
@@ -15455,8 +16242,10 @@
       <c r="AJ362" s="1"/>
       <c r="AK362" s="1"/>
       <c r="AL362" s="1"/>
-    </row>
-    <row r="363" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM362" s="1"/>
+      <c r="AN362" s="1"/>
+    </row>
+    <row r="363" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A363" s="1"/>
       <c r="B363" s="1"/>
       <c r="C363" s="1"/>
@@ -15495,8 +16284,10 @@
       <c r="AJ363" s="1"/>
       <c r="AK363" s="1"/>
       <c r="AL363" s="1"/>
-    </row>
-    <row r="364" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM363" s="1"/>
+      <c r="AN363" s="1"/>
+    </row>
+    <row r="364" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A364" s="1"/>
       <c r="B364" s="1"/>
       <c r="C364" s="1"/>
@@ -15535,8 +16326,10 @@
       <c r="AJ364" s="1"/>
       <c r="AK364" s="1"/>
       <c r="AL364" s="1"/>
-    </row>
-    <row r="365" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM364" s="1"/>
+      <c r="AN364" s="1"/>
+    </row>
+    <row r="365" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A365" s="1"/>
       <c r="B365" s="1"/>
       <c r="C365" s="1"/>
@@ -15575,8 +16368,10 @@
       <c r="AJ365" s="1"/>
       <c r="AK365" s="1"/>
       <c r="AL365" s="1"/>
-    </row>
-    <row r="366" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM365" s="1"/>
+      <c r="AN365" s="1"/>
+    </row>
+    <row r="366" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A366" s="1"/>
       <c r="B366" s="1"/>
       <c r="C366" s="1"/>
@@ -15615,8 +16410,10 @@
       <c r="AJ366" s="1"/>
       <c r="AK366" s="1"/>
       <c r="AL366" s="1"/>
-    </row>
-    <row r="367" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM366" s="1"/>
+      <c r="AN366" s="1"/>
+    </row>
+    <row r="367" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A367" s="1"/>
       <c r="B367" s="1"/>
       <c r="C367" s="1"/>
@@ -15655,8 +16452,10 @@
       <c r="AJ367" s="1"/>
       <c r="AK367" s="1"/>
       <c r="AL367" s="1"/>
-    </row>
-    <row r="368" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM367" s="1"/>
+      <c r="AN367" s="1"/>
+    </row>
+    <row r="368" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A368" s="1"/>
       <c r="B368" s="1"/>
       <c r="C368" s="1"/>
@@ -15695,8 +16494,10 @@
       <c r="AJ368" s="1"/>
       <c r="AK368" s="1"/>
       <c r="AL368" s="1"/>
-    </row>
-    <row r="369" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM368" s="1"/>
+      <c r="AN368" s="1"/>
+    </row>
+    <row r="369" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A369" s="1"/>
       <c r="B369" s="1"/>
       <c r="C369" s="1"/>
@@ -15735,8 +16536,10 @@
       <c r="AJ369" s="1"/>
       <c r="AK369" s="1"/>
       <c r="AL369" s="1"/>
-    </row>
-    <row r="370" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM369" s="1"/>
+      <c r="AN369" s="1"/>
+    </row>
+    <row r="370" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A370" s="1"/>
       <c r="B370" s="1"/>
       <c r="C370" s="1"/>
@@ -15775,8 +16578,10 @@
       <c r="AJ370" s="1"/>
       <c r="AK370" s="1"/>
       <c r="AL370" s="1"/>
-    </row>
-    <row r="371" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM370" s="1"/>
+      <c r="AN370" s="1"/>
+    </row>
+    <row r="371" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A371" s="1"/>
       <c r="B371" s="1"/>
       <c r="C371" s="1"/>
@@ -15815,8 +16620,10 @@
       <c r="AJ371" s="1"/>
       <c r="AK371" s="1"/>
       <c r="AL371" s="1"/>
-    </row>
-    <row r="372" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM371" s="1"/>
+      <c r="AN371" s="1"/>
+    </row>
+    <row r="372" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A372" s="1"/>
       <c r="B372" s="1"/>
       <c r="C372" s="1"/>
@@ -15855,8 +16662,10 @@
       <c r="AJ372" s="1"/>
       <c r="AK372" s="1"/>
       <c r="AL372" s="1"/>
-    </row>
-    <row r="373" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM372" s="1"/>
+      <c r="AN372" s="1"/>
+    </row>
+    <row r="373" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A373" s="1"/>
       <c r="B373" s="1"/>
       <c r="C373" s="1"/>
@@ -15895,8 +16704,10 @@
       <c r="AJ373" s="1"/>
       <c r="AK373" s="1"/>
       <c r="AL373" s="1"/>
-    </row>
-    <row r="374" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM373" s="1"/>
+      <c r="AN373" s="1"/>
+    </row>
+    <row r="374" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A374" s="1"/>
       <c r="B374" s="1"/>
       <c r="C374" s="1"/>
@@ -15935,8 +16746,10 @@
       <c r="AJ374" s="1"/>
       <c r="AK374" s="1"/>
       <c r="AL374" s="1"/>
-    </row>
-    <row r="375" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM374" s="1"/>
+      <c r="AN374" s="1"/>
+    </row>
+    <row r="375" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A375" s="1"/>
       <c r="B375" s="1"/>
       <c r="C375" s="1"/>
@@ -15975,8 +16788,10 @@
       <c r="AJ375" s="1"/>
       <c r="AK375" s="1"/>
       <c r="AL375" s="1"/>
-    </row>
-    <row r="376" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM375" s="1"/>
+      <c r="AN375" s="1"/>
+    </row>
+    <row r="376" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A376" s="1"/>
       <c r="B376" s="1"/>
       <c r="C376" s="1"/>
@@ -16015,8 +16830,10 @@
       <c r="AJ376" s="1"/>
       <c r="AK376" s="1"/>
       <c r="AL376" s="1"/>
-    </row>
-    <row r="377" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM376" s="1"/>
+      <c r="AN376" s="1"/>
+    </row>
+    <row r="377" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A377" s="1"/>
       <c r="B377" s="1"/>
       <c r="C377" s="1"/>
@@ -16055,8 +16872,10 @@
       <c r="AJ377" s="1"/>
       <c r="AK377" s="1"/>
       <c r="AL377" s="1"/>
-    </row>
-    <row r="378" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM377" s="1"/>
+      <c r="AN377" s="1"/>
+    </row>
+    <row r="378" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A378" s="1"/>
       <c r="B378" s="1"/>
       <c r="C378" s="1"/>
@@ -16095,8 +16914,10 @@
       <c r="AJ378" s="1"/>
       <c r="AK378" s="1"/>
       <c r="AL378" s="1"/>
-    </row>
-    <row r="379" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM378" s="1"/>
+      <c r="AN378" s="1"/>
+    </row>
+    <row r="379" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A379" s="1"/>
       <c r="B379" s="1"/>
       <c r="C379" s="1"/>
@@ -16135,8 +16956,10 @@
       <c r="AJ379" s="1"/>
       <c r="AK379" s="1"/>
       <c r="AL379" s="1"/>
-    </row>
-    <row r="380" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM379" s="1"/>
+      <c r="AN379" s="1"/>
+    </row>
+    <row r="380" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A380" s="1"/>
       <c r="B380" s="1"/>
       <c r="C380" s="1"/>
@@ -16175,8 +16998,10 @@
       <c r="AJ380" s="1"/>
       <c r="AK380" s="1"/>
       <c r="AL380" s="1"/>
-    </row>
-    <row r="381" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM380" s="1"/>
+      <c r="AN380" s="1"/>
+    </row>
+    <row r="381" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A381" s="1"/>
       <c r="B381" s="1"/>
       <c r="C381" s="1"/>
@@ -16215,8 +17040,10 @@
       <c r="AJ381" s="1"/>
       <c r="AK381" s="1"/>
       <c r="AL381" s="1"/>
-    </row>
-    <row r="382" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM381" s="1"/>
+      <c r="AN381" s="1"/>
+    </row>
+    <row r="382" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A382" s="1"/>
       <c r="B382" s="1"/>
       <c r="C382" s="1"/>
@@ -16255,8 +17082,10 @@
       <c r="AJ382" s="1"/>
       <c r="AK382" s="1"/>
       <c r="AL382" s="1"/>
-    </row>
-    <row r="383" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM382" s="1"/>
+      <c r="AN382" s="1"/>
+    </row>
+    <row r="383" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A383" s="1"/>
       <c r="B383" s="1"/>
       <c r="C383" s="1"/>
@@ -16295,8 +17124,10 @@
       <c r="AJ383" s="1"/>
       <c r="AK383" s="1"/>
       <c r="AL383" s="1"/>
-    </row>
-    <row r="384" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM383" s="1"/>
+      <c r="AN383" s="1"/>
+    </row>
+    <row r="384" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A384" s="1"/>
       <c r="B384" s="1"/>
       <c r="C384" s="1"/>
@@ -16335,8 +17166,10 @@
       <c r="AJ384" s="1"/>
       <c r="AK384" s="1"/>
       <c r="AL384" s="1"/>
-    </row>
-    <row r="385" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM384" s="1"/>
+      <c r="AN384" s="1"/>
+    </row>
+    <row r="385" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A385" s="1"/>
       <c r="B385" s="1"/>
       <c r="C385" s="1"/>
@@ -16375,8 +17208,10 @@
       <c r="AJ385" s="1"/>
       <c r="AK385" s="1"/>
       <c r="AL385" s="1"/>
-    </row>
-    <row r="386" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM385" s="1"/>
+      <c r="AN385" s="1"/>
+    </row>
+    <row r="386" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A386" s="1"/>
       <c r="B386" s="1"/>
       <c r="C386" s="1"/>
@@ -16415,8 +17250,10 @@
       <c r="AJ386" s="1"/>
       <c r="AK386" s="1"/>
       <c r="AL386" s="1"/>
-    </row>
-    <row r="387" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM386" s="1"/>
+      <c r="AN386" s="1"/>
+    </row>
+    <row r="387" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A387" s="1"/>
       <c r="B387" s="1"/>
       <c r="C387" s="1"/>
@@ -16455,8 +17292,10 @@
       <c r="AJ387" s="1"/>
       <c r="AK387" s="1"/>
       <c r="AL387" s="1"/>
-    </row>
-    <row r="388" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM387" s="1"/>
+      <c r="AN387" s="1"/>
+    </row>
+    <row r="388" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A388" s="1"/>
       <c r="B388" s="1"/>
       <c r="C388" s="1"/>
@@ -16495,8 +17334,10 @@
       <c r="AJ388" s="1"/>
       <c r="AK388" s="1"/>
       <c r="AL388" s="1"/>
-    </row>
-    <row r="389" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM388" s="1"/>
+      <c r="AN388" s="1"/>
+    </row>
+    <row r="389" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A389" s="1"/>
       <c r="B389" s="1"/>
       <c r="C389" s="1"/>
@@ -16535,8 +17376,10 @@
       <c r="AJ389" s="1"/>
       <c r="AK389" s="1"/>
       <c r="AL389" s="1"/>
-    </row>
-    <row r="390" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM389" s="1"/>
+      <c r="AN389" s="1"/>
+    </row>
+    <row r="390" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A390" s="1"/>
       <c r="B390" s="1"/>
       <c r="C390" s="1"/>
@@ -16575,8 +17418,10 @@
       <c r="AJ390" s="1"/>
       <c r="AK390" s="1"/>
       <c r="AL390" s="1"/>
-    </row>
-    <row r="391" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM390" s="1"/>
+      <c r="AN390" s="1"/>
+    </row>
+    <row r="391" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A391" s="1"/>
       <c r="B391" s="1"/>
       <c r="C391" s="1"/>
@@ -16615,8 +17460,10 @@
       <c r="AJ391" s="1"/>
       <c r="AK391" s="1"/>
       <c r="AL391" s="1"/>
-    </row>
-    <row r="392" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM391" s="1"/>
+      <c r="AN391" s="1"/>
+    </row>
+    <row r="392" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A392" s="1"/>
       <c r="B392" s="1"/>
       <c r="C392" s="1"/>
@@ -16655,8 +17502,10 @@
       <c r="AJ392" s="1"/>
       <c r="AK392" s="1"/>
       <c r="AL392" s="1"/>
-    </row>
-    <row r="393" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM392" s="1"/>
+      <c r="AN392" s="1"/>
+    </row>
+    <row r="393" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A393" s="1"/>
       <c r="B393" s="1"/>
       <c r="C393" s="1"/>
@@ -16695,8 +17544,10 @@
       <c r="AJ393" s="1"/>
       <c r="AK393" s="1"/>
       <c r="AL393" s="1"/>
-    </row>
-    <row r="394" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM393" s="1"/>
+      <c r="AN393" s="1"/>
+    </row>
+    <row r="394" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A394" s="1"/>
       <c r="B394" s="1"/>
       <c r="C394" s="1"/>
@@ -16735,8 +17586,10 @@
       <c r="AJ394" s="1"/>
       <c r="AK394" s="1"/>
       <c r="AL394" s="1"/>
-    </row>
-    <row r="395" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM394" s="1"/>
+      <c r="AN394" s="1"/>
+    </row>
+    <row r="395" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A395" s="1"/>
       <c r="B395" s="1"/>
       <c r="C395" s="1"/>
@@ -16775,8 +17628,10 @@
       <c r="AJ395" s="1"/>
       <c r="AK395" s="1"/>
       <c r="AL395" s="1"/>
-    </row>
-    <row r="396" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM395" s="1"/>
+      <c r="AN395" s="1"/>
+    </row>
+    <row r="396" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A396" s="1"/>
       <c r="B396" s="1"/>
       <c r="C396" s="1"/>
@@ -16815,8 +17670,10 @@
       <c r="AJ396" s="1"/>
       <c r="AK396" s="1"/>
       <c r="AL396" s="1"/>
-    </row>
-    <row r="397" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM396" s="1"/>
+      <c r="AN396" s="1"/>
+    </row>
+    <row r="397" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A397" s="1"/>
       <c r="B397" s="1"/>
       <c r="C397" s="1"/>
@@ -16855,8 +17712,10 @@
       <c r="AJ397" s="1"/>
       <c r="AK397" s="1"/>
       <c r="AL397" s="1"/>
-    </row>
-    <row r="398" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM397" s="1"/>
+      <c r="AN397" s="1"/>
+    </row>
+    <row r="398" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A398" s="1"/>
       <c r="B398" s="1"/>
       <c r="C398" s="1"/>
@@ -16895,8 +17754,10 @@
       <c r="AJ398" s="1"/>
       <c r="AK398" s="1"/>
       <c r="AL398" s="1"/>
-    </row>
-    <row r="399" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM398" s="1"/>
+      <c r="AN398" s="1"/>
+    </row>
+    <row r="399" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A399" s="1"/>
       <c r="B399" s="1"/>
       <c r="C399" s="1"/>
@@ -16935,8 +17796,10 @@
       <c r="AJ399" s="1"/>
       <c r="AK399" s="1"/>
       <c r="AL399" s="1"/>
-    </row>
-    <row r="400" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM399" s="1"/>
+      <c r="AN399" s="1"/>
+    </row>
+    <row r="400" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A400" s="1"/>
       <c r="B400" s="1"/>
       <c r="C400" s="1"/>
@@ -16975,8 +17838,10 @@
       <c r="AJ400" s="1"/>
       <c r="AK400" s="1"/>
       <c r="AL400" s="1"/>
-    </row>
-    <row r="401" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM400" s="1"/>
+      <c r="AN400" s="1"/>
+    </row>
+    <row r="401" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A401" s="1"/>
       <c r="B401" s="1"/>
       <c r="C401" s="1"/>
@@ -17015,8 +17880,10 @@
       <c r="AJ401" s="1"/>
       <c r="AK401" s="1"/>
       <c r="AL401" s="1"/>
-    </row>
-    <row r="402" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM401" s="1"/>
+      <c r="AN401" s="1"/>
+    </row>
+    <row r="402" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A402" s="1"/>
       <c r="B402" s="1"/>
       <c r="C402" s="1"/>
@@ -17055,8 +17922,10 @@
       <c r="AJ402" s="1"/>
       <c r="AK402" s="1"/>
       <c r="AL402" s="1"/>
-    </row>
-    <row r="403" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM402" s="1"/>
+      <c r="AN402" s="1"/>
+    </row>
+    <row r="403" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A403" s="1"/>
       <c r="B403" s="1"/>
       <c r="C403" s="1"/>
@@ -17095,8 +17964,10 @@
       <c r="AJ403" s="1"/>
       <c r="AK403" s="1"/>
       <c r="AL403" s="1"/>
-    </row>
-    <row r="404" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM403" s="1"/>
+      <c r="AN403" s="1"/>
+    </row>
+    <row r="404" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A404" s="1"/>
       <c r="B404" s="1"/>
       <c r="C404" s="1"/>
@@ -17135,8 +18006,10 @@
       <c r="AJ404" s="1"/>
       <c r="AK404" s="1"/>
       <c r="AL404" s="1"/>
-    </row>
-    <row r="405" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM404" s="1"/>
+      <c r="AN404" s="1"/>
+    </row>
+    <row r="405" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A405" s="1"/>
       <c r="B405" s="1"/>
       <c r="C405" s="1"/>
@@ -17175,8 +18048,10 @@
       <c r="AJ405" s="1"/>
       <c r="AK405" s="1"/>
       <c r="AL405" s="1"/>
-    </row>
-    <row r="406" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM405" s="1"/>
+      <c r="AN405" s="1"/>
+    </row>
+    <row r="406" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A406" s="1"/>
       <c r="B406" s="1"/>
       <c r="C406" s="1"/>
@@ -17215,8 +18090,10 @@
       <c r="AJ406" s="1"/>
       <c r="AK406" s="1"/>
       <c r="AL406" s="1"/>
-    </row>
-    <row r="407" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM406" s="1"/>
+      <c r="AN406" s="1"/>
+    </row>
+    <row r="407" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A407" s="1"/>
       <c r="B407" s="1"/>
       <c r="C407" s="1"/>
@@ -17255,8 +18132,10 @@
       <c r="AJ407" s="1"/>
       <c r="AK407" s="1"/>
       <c r="AL407" s="1"/>
-    </row>
-    <row r="408" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM407" s="1"/>
+      <c r="AN407" s="1"/>
+    </row>
+    <row r="408" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A408" s="1"/>
       <c r="B408" s="1"/>
       <c r="C408" s="1"/>
@@ -17295,8 +18174,10 @@
       <c r="AJ408" s="1"/>
       <c r="AK408" s="1"/>
       <c r="AL408" s="1"/>
-    </row>
-    <row r="409" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM408" s="1"/>
+      <c r="AN408" s="1"/>
+    </row>
+    <row r="409" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A409" s="1"/>
       <c r="B409" s="1"/>
       <c r="C409" s="1"/>
@@ -17335,8 +18216,10 @@
       <c r="AJ409" s="1"/>
       <c r="AK409" s="1"/>
       <c r="AL409" s="1"/>
-    </row>
-    <row r="410" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM409" s="1"/>
+      <c r="AN409" s="1"/>
+    </row>
+    <row r="410" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A410" s="1"/>
       <c r="B410" s="1"/>
       <c r="C410" s="1"/>
@@ -17375,8 +18258,10 @@
       <c r="AJ410" s="1"/>
       <c r="AK410" s="1"/>
       <c r="AL410" s="1"/>
-    </row>
-    <row r="411" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM410" s="1"/>
+      <c r="AN410" s="1"/>
+    </row>
+    <row r="411" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A411" s="1"/>
       <c r="B411" s="1"/>
       <c r="C411" s="1"/>
@@ -17415,8 +18300,10 @@
       <c r="AJ411" s="1"/>
       <c r="AK411" s="1"/>
       <c r="AL411" s="1"/>
-    </row>
-    <row r="412" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM411" s="1"/>
+      <c r="AN411" s="1"/>
+    </row>
+    <row r="412" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A412" s="1"/>
       <c r="B412" s="1"/>
       <c r="C412" s="1"/>
@@ -17455,8 +18342,10 @@
       <c r="AJ412" s="1"/>
       <c r="AK412" s="1"/>
       <c r="AL412" s="1"/>
-    </row>
-    <row r="413" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM412" s="1"/>
+      <c r="AN412" s="1"/>
+    </row>
+    <row r="413" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A413" s="1"/>
       <c r="B413" s="1"/>
       <c r="C413" s="1"/>
@@ -17495,8 +18384,10 @@
       <c r="AJ413" s="1"/>
       <c r="AK413" s="1"/>
       <c r="AL413" s="1"/>
-    </row>
-    <row r="414" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM413" s="1"/>
+      <c r="AN413" s="1"/>
+    </row>
+    <row r="414" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A414" s="1"/>
       <c r="B414" s="1"/>
       <c r="C414" s="1"/>
@@ -17535,8 +18426,10 @@
       <c r="AJ414" s="1"/>
       <c r="AK414" s="1"/>
       <c r="AL414" s="1"/>
-    </row>
-    <row r="415" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM414" s="1"/>
+      <c r="AN414" s="1"/>
+    </row>
+    <row r="415" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A415" s="1"/>
       <c r="B415" s="1"/>
       <c r="C415" s="1"/>
@@ -17575,8 +18468,10 @@
       <c r="AJ415" s="1"/>
       <c r="AK415" s="1"/>
       <c r="AL415" s="1"/>
-    </row>
-    <row r="416" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM415" s="1"/>
+      <c r="AN415" s="1"/>
+    </row>
+    <row r="416" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A416" s="1"/>
       <c r="B416" s="1"/>
       <c r="C416" s="1"/>
@@ -17615,8 +18510,10 @@
       <c r="AJ416" s="1"/>
       <c r="AK416" s="1"/>
       <c r="AL416" s="1"/>
-    </row>
-    <row r="417" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM416" s="1"/>
+      <c r="AN416" s="1"/>
+    </row>
+    <row r="417" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A417" s="1"/>
       <c r="B417" s="1"/>
       <c r="C417" s="1"/>
@@ -17655,8 +18552,10 @@
       <c r="AJ417" s="1"/>
       <c r="AK417" s="1"/>
       <c r="AL417" s="1"/>
-    </row>
-    <row r="418" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM417" s="1"/>
+      <c r="AN417" s="1"/>
+    </row>
+    <row r="418" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A418" s="1"/>
       <c r="B418" s="1"/>
       <c r="C418" s="1"/>
@@ -17695,8 +18594,10 @@
       <c r="AJ418" s="1"/>
       <c r="AK418" s="1"/>
       <c r="AL418" s="1"/>
-    </row>
-    <row r="419" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM418" s="1"/>
+      <c r="AN418" s="1"/>
+    </row>
+    <row r="419" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A419" s="1"/>
       <c r="B419" s="1"/>
       <c r="C419" s="1"/>
@@ -17735,8 +18636,10 @@
       <c r="AJ419" s="1"/>
       <c r="AK419" s="1"/>
       <c r="AL419" s="1"/>
-    </row>
-    <row r="420" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM419" s="1"/>
+      <c r="AN419" s="1"/>
+    </row>
+    <row r="420" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A420" s="1"/>
       <c r="B420" s="1"/>
       <c r="C420" s="1"/>
@@ -17775,8 +18678,10 @@
       <c r="AJ420" s="1"/>
       <c r="AK420" s="1"/>
       <c r="AL420" s="1"/>
-    </row>
-    <row r="421" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM420" s="1"/>
+      <c r="AN420" s="1"/>
+    </row>
+    <row r="421" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A421" s="1"/>
       <c r="B421" s="1"/>
       <c r="C421" s="1"/>
@@ -17815,8 +18720,10 @@
       <c r="AJ421" s="1"/>
       <c r="AK421" s="1"/>
       <c r="AL421" s="1"/>
-    </row>
-    <row r="422" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM421" s="1"/>
+      <c r="AN421" s="1"/>
+    </row>
+    <row r="422" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A422" s="1"/>
       <c r="B422" s="1"/>
       <c r="C422" s="1"/>
@@ -17855,8 +18762,10 @@
       <c r="AJ422" s="1"/>
       <c r="AK422" s="1"/>
       <c r="AL422" s="1"/>
-    </row>
-    <row r="423" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM422" s="1"/>
+      <c r="AN422" s="1"/>
+    </row>
+    <row r="423" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A423" s="1"/>
       <c r="B423" s="1"/>
       <c r="C423" s="1"/>
@@ -17895,8 +18804,10 @@
       <c r="AJ423" s="1"/>
       <c r="AK423" s="1"/>
       <c r="AL423" s="1"/>
-    </row>
-    <row r="424" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM423" s="1"/>
+      <c r="AN423" s="1"/>
+    </row>
+    <row r="424" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A424" s="1"/>
       <c r="B424" s="1"/>
       <c r="C424" s="1"/>
@@ -17935,8 +18846,10 @@
       <c r="AJ424" s="1"/>
       <c r="AK424" s="1"/>
       <c r="AL424" s="1"/>
-    </row>
-    <row r="425" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM424" s="1"/>
+      <c r="AN424" s="1"/>
+    </row>
+    <row r="425" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A425" s="1"/>
       <c r="B425" s="1"/>
       <c r="C425" s="1"/>
@@ -17975,8 +18888,10 @@
       <c r="AJ425" s="1"/>
       <c r="AK425" s="1"/>
       <c r="AL425" s="1"/>
-    </row>
-    <row r="426" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM425" s="1"/>
+      <c r="AN425" s="1"/>
+    </row>
+    <row r="426" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A426" s="1"/>
       <c r="B426" s="1"/>
       <c r="C426" s="1"/>
@@ -18015,8 +18930,10 @@
       <c r="AJ426" s="1"/>
       <c r="AK426" s="1"/>
       <c r="AL426" s="1"/>
-    </row>
-    <row r="427" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM426" s="1"/>
+      <c r="AN426" s="1"/>
+    </row>
+    <row r="427" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A427" s="1"/>
       <c r="B427" s="1"/>
       <c r="C427" s="1"/>
@@ -18055,8 +18972,10 @@
       <c r="AJ427" s="1"/>
       <c r="AK427" s="1"/>
       <c r="AL427" s="1"/>
-    </row>
-    <row r="428" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM427" s="1"/>
+      <c r="AN427" s="1"/>
+    </row>
+    <row r="428" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A428" s="1"/>
       <c r="B428" s="1"/>
       <c r="C428" s="1"/>
@@ -18095,8 +19014,10 @@
       <c r="AJ428" s="1"/>
       <c r="AK428" s="1"/>
       <c r="AL428" s="1"/>
-    </row>
-    <row r="429" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM428" s="1"/>
+      <c r="AN428" s="1"/>
+    </row>
+    <row r="429" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A429" s="1"/>
       <c r="B429" s="1"/>
       <c r="C429" s="1"/>
@@ -18135,8 +19056,10 @@
       <c r="AJ429" s="1"/>
       <c r="AK429" s="1"/>
       <c r="AL429" s="1"/>
-    </row>
-    <row r="430" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM429" s="1"/>
+      <c r="AN429" s="1"/>
+    </row>
+    <row r="430" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A430" s="1"/>
       <c r="B430" s="1"/>
       <c r="C430" s="1"/>
@@ -18175,8 +19098,10 @@
       <c r="AJ430" s="1"/>
       <c r="AK430" s="1"/>
       <c r="AL430" s="1"/>
-    </row>
-    <row r="431" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM430" s="1"/>
+      <c r="AN430" s="1"/>
+    </row>
+    <row r="431" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A431" s="1"/>
       <c r="B431" s="1"/>
       <c r="C431" s="1"/>
@@ -18215,8 +19140,10 @@
       <c r="AJ431" s="1"/>
       <c r="AK431" s="1"/>
       <c r="AL431" s="1"/>
-    </row>
-    <row r="432" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM431" s="1"/>
+      <c r="AN431" s="1"/>
+    </row>
+    <row r="432" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A432" s="1"/>
       <c r="B432" s="1"/>
       <c r="C432" s="1"/>
@@ -18255,8 +19182,10 @@
       <c r="AJ432" s="1"/>
       <c r="AK432" s="1"/>
       <c r="AL432" s="1"/>
-    </row>
-    <row r="433" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM432" s="1"/>
+      <c r="AN432" s="1"/>
+    </row>
+    <row r="433" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A433" s="1"/>
       <c r="B433" s="1"/>
       <c r="C433" s="1"/>
@@ -18295,8 +19224,10 @@
       <c r="AJ433" s="1"/>
       <c r="AK433" s="1"/>
       <c r="AL433" s="1"/>
-    </row>
-    <row r="434" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM433" s="1"/>
+      <c r="AN433" s="1"/>
+    </row>
+    <row r="434" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A434" s="1"/>
       <c r="B434" s="1"/>
       <c r="C434" s="1"/>
@@ -18335,8 +19266,10 @@
       <c r="AJ434" s="1"/>
       <c r="AK434" s="1"/>
       <c r="AL434" s="1"/>
-    </row>
-    <row r="435" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM434" s="1"/>
+      <c r="AN434" s="1"/>
+    </row>
+    <row r="435" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A435" s="1"/>
       <c r="B435" s="1"/>
       <c r="C435" s="1"/>
@@ -18375,8 +19308,10 @@
       <c r="AJ435" s="1"/>
       <c r="AK435" s="1"/>
       <c r="AL435" s="1"/>
-    </row>
-    <row r="436" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM435" s="1"/>
+      <c r="AN435" s="1"/>
+    </row>
+    <row r="436" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A436" s="1"/>
       <c r="B436" s="1"/>
       <c r="C436" s="1"/>
@@ -18415,8 +19350,10 @@
       <c r="AJ436" s="1"/>
       <c r="AK436" s="1"/>
       <c r="AL436" s="1"/>
-    </row>
-    <row r="437" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM436" s="1"/>
+      <c r="AN436" s="1"/>
+    </row>
+    <row r="437" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A437" s="1"/>
       <c r="B437" s="1"/>
       <c r="C437" s="1"/>
@@ -18455,8 +19392,10 @@
       <c r="AJ437" s="1"/>
       <c r="AK437" s="1"/>
       <c r="AL437" s="1"/>
-    </row>
-    <row r="438" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM437" s="1"/>
+      <c r="AN437" s="1"/>
+    </row>
+    <row r="438" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A438" s="1"/>
       <c r="B438" s="1"/>
       <c r="C438" s="1"/>
@@ -18495,8 +19434,10 @@
       <c r="AJ438" s="1"/>
       <c r="AK438" s="1"/>
       <c r="AL438" s="1"/>
-    </row>
-    <row r="439" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM438" s="1"/>
+      <c r="AN438" s="1"/>
+    </row>
+    <row r="439" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A439" s="1"/>
       <c r="B439" s="1"/>
       <c r="C439" s="1"/>
@@ -18535,8 +19476,10 @@
       <c r="AJ439" s="1"/>
       <c r="AK439" s="1"/>
       <c r="AL439" s="1"/>
-    </row>
-    <row r="440" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM439" s="1"/>
+      <c r="AN439" s="1"/>
+    </row>
+    <row r="440" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A440" s="1"/>
       <c r="B440" s="1"/>
       <c r="C440" s="1"/>
@@ -18575,8 +19518,10 @@
       <c r="AJ440" s="1"/>
       <c r="AK440" s="1"/>
       <c r="AL440" s="1"/>
-    </row>
-    <row r="441" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM440" s="1"/>
+      <c r="AN440" s="1"/>
+    </row>
+    <row r="441" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A441" s="1"/>
       <c r="B441" s="1"/>
       <c r="C441" s="1"/>
@@ -18615,8 +19560,10 @@
       <c r="AJ441" s="1"/>
       <c r="AK441" s="1"/>
       <c r="AL441" s="1"/>
-    </row>
-    <row r="442" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM441" s="1"/>
+      <c r="AN441" s="1"/>
+    </row>
+    <row r="442" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A442" s="1"/>
       <c r="B442" s="1"/>
       <c r="C442" s="1"/>
@@ -18655,8 +19602,10 @@
       <c r="AJ442" s="1"/>
       <c r="AK442" s="1"/>
       <c r="AL442" s="1"/>
-    </row>
-    <row r="443" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM442" s="1"/>
+      <c r="AN442" s="1"/>
+    </row>
+    <row r="443" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A443" s="1"/>
       <c r="B443" s="1"/>
       <c r="C443" s="1"/>
@@ -18695,8 +19644,10 @@
       <c r="AJ443" s="1"/>
       <c r="AK443" s="1"/>
       <c r="AL443" s="1"/>
-    </row>
-    <row r="444" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM443" s="1"/>
+      <c r="AN443" s="1"/>
+    </row>
+    <row r="444" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A444" s="1"/>
       <c r="B444" s="1"/>
       <c r="C444" s="1"/>
@@ -18735,8 +19686,10 @@
       <c r="AJ444" s="1"/>
       <c r="AK444" s="1"/>
       <c r="AL444" s="1"/>
-    </row>
-    <row r="445" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM444" s="1"/>
+      <c r="AN444" s="1"/>
+    </row>
+    <row r="445" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A445" s="1"/>
       <c r="B445" s="1"/>
       <c r="C445" s="1"/>
@@ -18775,8 +19728,10 @@
       <c r="AJ445" s="1"/>
       <c r="AK445" s="1"/>
       <c r="AL445" s="1"/>
-    </row>
-    <row r="446" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM445" s="1"/>
+      <c r="AN445" s="1"/>
+    </row>
+    <row r="446" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A446" s="1"/>
       <c r="B446" s="1"/>
       <c r="C446" s="1"/>
@@ -18815,8 +19770,10 @@
       <c r="AJ446" s="1"/>
       <c r="AK446" s="1"/>
       <c r="AL446" s="1"/>
-    </row>
-    <row r="447" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM446" s="1"/>
+      <c r="AN446" s="1"/>
+    </row>
+    <row r="447" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A447" s="1"/>
       <c r="B447" s="1"/>
       <c r="C447" s="1"/>
@@ -18855,8 +19812,10 @@
       <c r="AJ447" s="1"/>
       <c r="AK447" s="1"/>
       <c r="AL447" s="1"/>
-    </row>
-    <row r="448" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM447" s="1"/>
+      <c r="AN447" s="1"/>
+    </row>
+    <row r="448" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A448" s="1"/>
       <c r="B448" s="1"/>
       <c r="C448" s="1"/>
@@ -18895,8 +19854,10 @@
       <c r="AJ448" s="1"/>
       <c r="AK448" s="1"/>
       <c r="AL448" s="1"/>
-    </row>
-    <row r="449" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM448" s="1"/>
+      <c r="AN448" s="1"/>
+    </row>
+    <row r="449" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A449" s="1"/>
       <c r="B449" s="1"/>
       <c r="C449" s="1"/>
@@ -18935,8 +19896,10 @@
       <c r="AJ449" s="1"/>
       <c r="AK449" s="1"/>
       <c r="AL449" s="1"/>
-    </row>
-    <row r="450" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM449" s="1"/>
+      <c r="AN449" s="1"/>
+    </row>
+    <row r="450" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A450" s="1"/>
       <c r="B450" s="1"/>
       <c r="C450" s="1"/>
@@ -18975,8 +19938,10 @@
       <c r="AJ450" s="1"/>
       <c r="AK450" s="1"/>
       <c r="AL450" s="1"/>
-    </row>
-    <row r="451" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM450" s="1"/>
+      <c r="AN450" s="1"/>
+    </row>
+    <row r="451" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A451" s="1"/>
       <c r="B451" s="1"/>
       <c r="C451" s="1"/>
@@ -19015,8 +19980,10 @@
       <c r="AJ451" s="1"/>
       <c r="AK451" s="1"/>
       <c r="AL451" s="1"/>
-    </row>
-    <row r="452" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM451" s="1"/>
+      <c r="AN451" s="1"/>
+    </row>
+    <row r="452" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A452" s="1"/>
       <c r="B452" s="1"/>
       <c r="C452" s="1"/>
@@ -19055,8 +20022,10 @@
       <c r="AJ452" s="1"/>
       <c r="AK452" s="1"/>
       <c r="AL452" s="1"/>
-    </row>
-    <row r="453" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM452" s="1"/>
+      <c r="AN452" s="1"/>
+    </row>
+    <row r="453" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A453" s="1"/>
       <c r="B453" s="1"/>
       <c r="C453" s="1"/>
@@ -19095,8 +20064,10 @@
       <c r="AJ453" s="1"/>
       <c r="AK453" s="1"/>
       <c r="AL453" s="1"/>
-    </row>
-    <row r="454" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM453" s="1"/>
+      <c r="AN453" s="1"/>
+    </row>
+    <row r="454" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A454" s="1"/>
       <c r="B454" s="1"/>
       <c r="C454" s="1"/>
@@ -19135,8 +20106,10 @@
       <c r="AJ454" s="1"/>
       <c r="AK454" s="1"/>
       <c r="AL454" s="1"/>
-    </row>
-    <row r="455" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM454" s="1"/>
+      <c r="AN454" s="1"/>
+    </row>
+    <row r="455" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A455" s="1"/>
       <c r="B455" s="1"/>
       <c r="C455" s="1"/>
@@ -19175,8 +20148,10 @@
       <c r="AJ455" s="1"/>
       <c r="AK455" s="1"/>
       <c r="AL455" s="1"/>
-    </row>
-    <row r="456" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM455" s="1"/>
+      <c r="AN455" s="1"/>
+    </row>
+    <row r="456" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A456" s="1"/>
       <c r="B456" s="1"/>
       <c r="C456" s="1"/>
@@ -19215,8 +20190,10 @@
       <c r="AJ456" s="1"/>
       <c r="AK456" s="1"/>
       <c r="AL456" s="1"/>
-    </row>
-    <row r="457" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM456" s="1"/>
+      <c r="AN456" s="1"/>
+    </row>
+    <row r="457" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A457" s="1"/>
       <c r="B457" s="1"/>
       <c r="C457" s="1"/>
@@ -19255,8 +20232,10 @@
       <c r="AJ457" s="1"/>
       <c r="AK457" s="1"/>
       <c r="AL457" s="1"/>
-    </row>
-    <row r="458" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM457" s="1"/>
+      <c r="AN457" s="1"/>
+    </row>
+    <row r="458" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A458" s="1"/>
       <c r="B458" s="1"/>
       <c r="C458" s="1"/>
@@ -19295,8 +20274,10 @@
       <c r="AJ458" s="1"/>
       <c r="AK458" s="1"/>
       <c r="AL458" s="1"/>
-    </row>
-    <row r="459" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM458" s="1"/>
+      <c r="AN458" s="1"/>
+    </row>
+    <row r="459" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A459" s="1"/>
       <c r="B459" s="1"/>
       <c r="C459" s="1"/>
@@ -19335,8 +20316,10 @@
       <c r="AJ459" s="1"/>
       <c r="AK459" s="1"/>
       <c r="AL459" s="1"/>
-    </row>
-    <row r="460" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM459" s="1"/>
+      <c r="AN459" s="1"/>
+    </row>
+    <row r="460" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A460" s="1"/>
       <c r="B460" s="1"/>
       <c r="C460" s="1"/>
@@ -19375,8 +20358,10 @@
       <c r="AJ460" s="1"/>
       <c r="AK460" s="1"/>
       <c r="AL460" s="1"/>
-    </row>
-    <row r="461" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM460" s="1"/>
+      <c r="AN460" s="1"/>
+    </row>
+    <row r="461" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A461" s="1"/>
       <c r="B461" s="1"/>
       <c r="C461" s="1"/>
@@ -19415,8 +20400,10 @@
       <c r="AJ461" s="1"/>
       <c r="AK461" s="1"/>
       <c r="AL461" s="1"/>
-    </row>
-    <row r="462" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM461" s="1"/>
+      <c r="AN461" s="1"/>
+    </row>
+    <row r="462" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A462" s="1"/>
       <c r="B462" s="1"/>
       <c r="C462" s="1"/>
@@ -19455,8 +20442,10 @@
       <c r="AJ462" s="1"/>
       <c r="AK462" s="1"/>
       <c r="AL462" s="1"/>
-    </row>
-    <row r="463" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM462" s="1"/>
+      <c r="AN462" s="1"/>
+    </row>
+    <row r="463" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A463" s="1"/>
       <c r="B463" s="1"/>
       <c r="C463" s="1"/>
@@ -19495,8 +20484,10 @@
       <c r="AJ463" s="1"/>
       <c r="AK463" s="1"/>
       <c r="AL463" s="1"/>
-    </row>
-    <row r="464" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM463" s="1"/>
+      <c r="AN463" s="1"/>
+    </row>
+    <row r="464" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A464" s="1"/>
       <c r="B464" s="1"/>
       <c r="C464" s="1"/>
@@ -19535,8 +20526,10 @@
       <c r="AJ464" s="1"/>
       <c r="AK464" s="1"/>
       <c r="AL464" s="1"/>
-    </row>
-    <row r="465" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM464" s="1"/>
+      <c r="AN464" s="1"/>
+    </row>
+    <row r="465" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A465" s="1"/>
       <c r="B465" s="1"/>
       <c r="C465" s="1"/>
@@ -19575,8 +20568,10 @@
       <c r="AJ465" s="1"/>
       <c r="AK465" s="1"/>
       <c r="AL465" s="1"/>
-    </row>
-    <row r="466" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM465" s="1"/>
+      <c r="AN465" s="1"/>
+    </row>
+    <row r="466" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A466" s="1"/>
       <c r="B466" s="1"/>
       <c r="C466" s="1"/>
@@ -19615,8 +20610,10 @@
       <c r="AJ466" s="1"/>
       <c r="AK466" s="1"/>
       <c r="AL466" s="1"/>
-    </row>
-    <row r="467" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM466" s="1"/>
+      <c r="AN466" s="1"/>
+    </row>
+    <row r="467" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A467" s="1"/>
       <c r="B467" s="1"/>
       <c r="C467" s="1"/>
@@ -19655,8 +20652,10 @@
       <c r="AJ467" s="1"/>
       <c r="AK467" s="1"/>
       <c r="AL467" s="1"/>
-    </row>
-    <row r="468" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM467" s="1"/>
+      <c r="AN467" s="1"/>
+    </row>
+    <row r="468" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A468" s="1"/>
       <c r="B468" s="1"/>
       <c r="C468" s="1"/>
@@ -19695,8 +20694,10 @@
       <c r="AJ468" s="1"/>
       <c r="AK468" s="1"/>
       <c r="AL468" s="1"/>
-    </row>
-    <row r="469" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM468" s="1"/>
+      <c r="AN468" s="1"/>
+    </row>
+    <row r="469" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A469" s="1"/>
       <c r="B469" s="1"/>
       <c r="C469" s="1"/>
@@ -19735,8 +20736,10 @@
       <c r="AJ469" s="1"/>
       <c r="AK469" s="1"/>
       <c r="AL469" s="1"/>
-    </row>
-    <row r="470" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM469" s="1"/>
+      <c r="AN469" s="1"/>
+    </row>
+    <row r="470" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A470" s="1"/>
       <c r="B470" s="1"/>
       <c r="C470" s="1"/>
@@ -19775,8 +20778,10 @@
       <c r="AJ470" s="1"/>
       <c r="AK470" s="1"/>
       <c r="AL470" s="1"/>
-    </row>
-    <row r="471" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM470" s="1"/>
+      <c r="AN470" s="1"/>
+    </row>
+    <row r="471" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A471" s="1"/>
       <c r="B471" s="1"/>
       <c r="C471" s="1"/>
@@ -19815,8 +20820,10 @@
       <c r="AJ471" s="1"/>
       <c r="AK471" s="1"/>
       <c r="AL471" s="1"/>
-    </row>
-    <row r="472" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM471" s="1"/>
+      <c r="AN471" s="1"/>
+    </row>
+    <row r="472" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A472" s="1"/>
       <c r="B472" s="1"/>
       <c r="C472" s="1"/>
@@ -19855,8 +20862,10 @@
       <c r="AJ472" s="1"/>
       <c r="AK472" s="1"/>
       <c r="AL472" s="1"/>
-    </row>
-    <row r="473" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM472" s="1"/>
+      <c r="AN472" s="1"/>
+    </row>
+    <row r="473" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A473" s="1"/>
       <c r="B473" s="1"/>
       <c r="C473" s="1"/>
@@ -19895,8 +20904,10 @@
       <c r="AJ473" s="1"/>
       <c r="AK473" s="1"/>
       <c r="AL473" s="1"/>
-    </row>
-    <row r="474" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM473" s="1"/>
+      <c r="AN473" s="1"/>
+    </row>
+    <row r="474" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A474" s="1"/>
       <c r="B474" s="1"/>
       <c r="C474" s="1"/>
@@ -19935,8 +20946,10 @@
       <c r="AJ474" s="1"/>
       <c r="AK474" s="1"/>
       <c r="AL474" s="1"/>
-    </row>
-    <row r="475" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM474" s="1"/>
+      <c r="AN474" s="1"/>
+    </row>
+    <row r="475" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A475" s="1"/>
       <c r="B475" s="1"/>
       <c r="C475" s="1"/>
@@ -19975,8 +20988,10 @@
       <c r="AJ475" s="1"/>
       <c r="AK475" s="1"/>
       <c r="AL475" s="1"/>
-    </row>
-    <row r="476" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM475" s="1"/>
+      <c r="AN475" s="1"/>
+    </row>
+    <row r="476" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A476" s="1"/>
       <c r="B476" s="1"/>
       <c r="C476" s="1"/>
@@ -20015,8 +21030,10 @@
       <c r="AJ476" s="1"/>
       <c r="AK476" s="1"/>
       <c r="AL476" s="1"/>
-    </row>
-    <row r="477" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM476" s="1"/>
+      <c r="AN476" s="1"/>
+    </row>
+    <row r="477" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A477" s="1"/>
       <c r="B477" s="1"/>
       <c r="C477" s="1"/>
@@ -20055,8 +21072,10 @@
       <c r="AJ477" s="1"/>
       <c r="AK477" s="1"/>
       <c r="AL477" s="1"/>
-    </row>
-    <row r="478" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM477" s="1"/>
+      <c r="AN477" s="1"/>
+    </row>
+    <row r="478" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A478" s="1"/>
       <c r="B478" s="1"/>
       <c r="C478" s="1"/>
@@ -20095,8 +21114,10 @@
       <c r="AJ478" s="1"/>
       <c r="AK478" s="1"/>
       <c r="AL478" s="1"/>
-    </row>
-    <row r="479" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM478" s="1"/>
+      <c r="AN478" s="1"/>
+    </row>
+    <row r="479" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A479" s="1"/>
       <c r="B479" s="1"/>
       <c r="C479" s="1"/>
@@ -20135,8 +21156,10 @@
       <c r="AJ479" s="1"/>
       <c r="AK479" s="1"/>
       <c r="AL479" s="1"/>
-    </row>
-    <row r="480" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM479" s="1"/>
+      <c r="AN479" s="1"/>
+    </row>
+    <row r="480" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A480" s="1"/>
       <c r="B480" s="1"/>
       <c r="C480" s="1"/>
@@ -20175,8 +21198,10 @@
       <c r="AJ480" s="1"/>
       <c r="AK480" s="1"/>
       <c r="AL480" s="1"/>
-    </row>
-    <row r="481" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM480" s="1"/>
+      <c r="AN480" s="1"/>
+    </row>
+    <row r="481" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A481" s="1"/>
       <c r="B481" s="1"/>
       <c r="C481" s="1"/>
@@ -20215,8 +21240,10 @@
       <c r="AJ481" s="1"/>
       <c r="AK481" s="1"/>
       <c r="AL481" s="1"/>
-    </row>
-    <row r="482" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM481" s="1"/>
+      <c r="AN481" s="1"/>
+    </row>
+    <row r="482" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A482" s="1"/>
       <c r="B482" s="1"/>
       <c r="C482" s="1"/>
@@ -20255,8 +21282,10 @@
       <c r="AJ482" s="1"/>
       <c r="AK482" s="1"/>
       <c r="AL482" s="1"/>
-    </row>
-    <row r="483" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM482" s="1"/>
+      <c r="AN482" s="1"/>
+    </row>
+    <row r="483" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A483" s="1"/>
       <c r="B483" s="1"/>
       <c r="C483" s="1"/>
@@ -20295,8 +21324,10 @@
       <c r="AJ483" s="1"/>
       <c r="AK483" s="1"/>
       <c r="AL483" s="1"/>
-    </row>
-    <row r="484" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM483" s="1"/>
+      <c r="AN483" s="1"/>
+    </row>
+    <row r="484" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A484" s="1"/>
       <c r="B484" s="1"/>
       <c r="C484" s="1"/>
@@ -20335,8 +21366,10 @@
       <c r="AJ484" s="1"/>
       <c r="AK484" s="1"/>
       <c r="AL484" s="1"/>
-    </row>
-    <row r="485" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM484" s="1"/>
+      <c r="AN484" s="1"/>
+    </row>
+    <row r="485" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A485" s="1"/>
       <c r="B485" s="1"/>
       <c r="C485" s="1"/>
@@ -20375,8 +21408,10 @@
       <c r="AJ485" s="1"/>
       <c r="AK485" s="1"/>
       <c r="AL485" s="1"/>
-    </row>
-    <row r="486" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM485" s="1"/>
+      <c r="AN485" s="1"/>
+    </row>
+    <row r="486" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A486" s="1"/>
       <c r="B486" s="1"/>
       <c r="C486" s="1"/>
@@ -20415,8 +21450,10 @@
       <c r="AJ486" s="1"/>
       <c r="AK486" s="1"/>
       <c r="AL486" s="1"/>
-    </row>
-    <row r="487" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM486" s="1"/>
+      <c r="AN486" s="1"/>
+    </row>
+    <row r="487" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A487" s="1"/>
       <c r="B487" s="1"/>
       <c r="C487" s="1"/>
@@ -20455,8 +21492,10 @@
       <c r="AJ487" s="1"/>
       <c r="AK487" s="1"/>
       <c r="AL487" s="1"/>
-    </row>
-    <row r="488" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM487" s="1"/>
+      <c r="AN487" s="1"/>
+    </row>
+    <row r="488" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A488" s="1"/>
       <c r="B488" s="1"/>
       <c r="C488" s="1"/>
@@ -20495,8 +21534,10 @@
       <c r="AJ488" s="1"/>
       <c r="AK488" s="1"/>
       <c r="AL488" s="1"/>
-    </row>
-    <row r="489" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM488" s="1"/>
+      <c r="AN488" s="1"/>
+    </row>
+    <row r="489" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A489" s="1"/>
       <c r="B489" s="1"/>
       <c r="C489" s="1"/>
@@ -20535,8 +21576,10 @@
       <c r="AJ489" s="1"/>
       <c r="AK489" s="1"/>
       <c r="AL489" s="1"/>
-    </row>
-    <row r="490" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM489" s="1"/>
+      <c r="AN489" s="1"/>
+    </row>
+    <row r="490" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A490" s="1"/>
       <c r="B490" s="1"/>
       <c r="C490" s="1"/>
@@ -20575,8 +21618,10 @@
       <c r="AJ490" s="1"/>
       <c r="AK490" s="1"/>
       <c r="AL490" s="1"/>
-    </row>
-    <row r="491" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM490" s="1"/>
+      <c r="AN490" s="1"/>
+    </row>
+    <row r="491" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A491" s="1"/>
       <c r="B491" s="1"/>
       <c r="C491" s="1"/>
@@ -20615,8 +21660,10 @@
       <c r="AJ491" s="1"/>
       <c r="AK491" s="1"/>
       <c r="AL491" s="1"/>
-    </row>
-    <row r="492" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM491" s="1"/>
+      <c r="AN491" s="1"/>
+    </row>
+    <row r="492" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A492" s="1"/>
       <c r="B492" s="1"/>
       <c r="C492" s="1"/>
@@ -20655,8 +21702,10 @@
       <c r="AJ492" s="1"/>
       <c r="AK492" s="1"/>
       <c r="AL492" s="1"/>
-    </row>
-    <row r="493" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM492" s="1"/>
+      <c r="AN492" s="1"/>
+    </row>
+    <row r="493" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A493" s="1"/>
       <c r="B493" s="1"/>
       <c r="C493" s="1"/>
@@ -20695,8 +21744,10 @@
       <c r="AJ493" s="1"/>
       <c r="AK493" s="1"/>
       <c r="AL493" s="1"/>
-    </row>
-    <row r="494" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM493" s="1"/>
+      <c r="AN493" s="1"/>
+    </row>
+    <row r="494" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A494" s="1"/>
       <c r="B494" s="1"/>
       <c r="C494" s="1"/>
@@ -20735,8 +21786,10 @@
       <c r="AJ494" s="1"/>
       <c r="AK494" s="1"/>
       <c r="AL494" s="1"/>
-    </row>
-    <row r="495" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM494" s="1"/>
+      <c r="AN494" s="1"/>
+    </row>
+    <row r="495" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A495" s="1"/>
       <c r="B495" s="1"/>
       <c r="C495" s="1"/>
@@ -20775,8 +21828,10 @@
       <c r="AJ495" s="1"/>
       <c r="AK495" s="1"/>
       <c r="AL495" s="1"/>
-    </row>
-    <row r="496" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM495" s="1"/>
+      <c r="AN495" s="1"/>
+    </row>
+    <row r="496" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A496" s="1"/>
       <c r="B496" s="1"/>
       <c r="C496" s="1"/>
@@ -20815,8 +21870,10 @@
       <c r="AJ496" s="1"/>
       <c r="AK496" s="1"/>
       <c r="AL496" s="1"/>
-    </row>
-    <row r="497" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM496" s="1"/>
+      <c r="AN496" s="1"/>
+    </row>
+    <row r="497" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A497" s="1"/>
       <c r="B497" s="1"/>
       <c r="C497" s="1"/>
@@ -20855,8 +21912,10 @@
       <c r="AJ497" s="1"/>
       <c r="AK497" s="1"/>
       <c r="AL497" s="1"/>
-    </row>
-    <row r="498" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM497" s="1"/>
+      <c r="AN497" s="1"/>
+    </row>
+    <row r="498" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A498" s="1"/>
       <c r="B498" s="1"/>
       <c r="C498" s="1"/>
@@ -20895,8 +21954,10 @@
       <c r="AJ498" s="1"/>
       <c r="AK498" s="1"/>
       <c r="AL498" s="1"/>
-    </row>
-    <row r="499" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM498" s="1"/>
+      <c r="AN498" s="1"/>
+    </row>
+    <row r="499" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A499" s="1"/>
       <c r="B499" s="1"/>
       <c r="C499" s="1"/>
@@ -20935,8 +21996,10 @@
       <c r="AJ499" s="1"/>
       <c r="AK499" s="1"/>
       <c r="AL499" s="1"/>
-    </row>
-    <row r="500" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="AM499" s="1"/>
+      <c r="AN499" s="1"/>
+    </row>
+    <row r="500" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A500" s="1"/>
       <c r="B500" s="1"/>
       <c r="C500" s="1"/>
@@ -20975,6 +22038,8 @@
       <c r="AJ500" s="1"/>
       <c r="AK500" s="1"/>
       <c r="AL500" s="1"/>
+      <c r="AM500" s="1"/>
+      <c r="AN500" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
